--- a/templates/FAR_master_v1.xlsx
+++ b/templates/FAR_master_v1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" codeName="현재_통합_문서" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843AC6D4-BAF0-44ED-8523-8D2E238C0075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EB52D3F-E424-433D-910C-CBFD483E940C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="789" xr2:uid="{DF1BC0A9-5276-4427-9274-D60DAF0ED6B0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="789" xr2:uid="{DF1BC0A9-5276-4427-9274-D60DAF0ED6B0}"/>
   </bookViews>
   <sheets>
     <sheet name="사용안내" sheetId="18" r:id="rId1"/>
@@ -29,20 +29,7 @@
     <definedName name="_xlnm.Print_Titles">#N/A</definedName>
     <definedName name="PriorMonths">FAR!$P$6</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -5437,9 +5424,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3906603-090D-41CF-9DF4-E81750788EE7}">
   <dimension ref="A1:A16"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="140.625" customWidth="1"/>
+    <col min="1" max="1" width="140.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -5534,19 +5521,19 @@
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:I46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="34.75" style="134" customWidth="1"/>
+    <col min="1" max="1" width="34.69921875" style="134" customWidth="1"/>
     <col min="2" max="2" width="16.5" style="134" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.125" style="134" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.375" style="134" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" style="134" customWidth="1"/>
-    <col min="6" max="6" width="16.875" style="134" customWidth="1"/>
-    <col min="7" max="7" width="2.25" style="134" customWidth="1"/>
-    <col min="8" max="8" width="15.375" style="134" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.375" style="134" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.625" style="134" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.75" style="134" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.09765625" style="134" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.3984375" style="134" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.19921875" style="134" customWidth="1"/>
+    <col min="6" max="6" width="16.8984375" style="134" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" style="134" customWidth="1"/>
+    <col min="8" max="8" width="15.3984375" style="134" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.3984375" style="134" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.59765625" style="134" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.69921875" style="134" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="134"/>
   </cols>
   <sheetData>
@@ -5830,7 +5817,7 @@
       </c>
       <c r="F19" s="140"/>
     </row>
-    <row r="20" spans="1:9" ht="17.45" customHeight="1">
+    <row r="20" spans="1:9" ht="17.399999999999999" customHeight="1">
       <c r="A20" s="141" t="s">
         <v>66</v>
       </c>
@@ -6326,20 +6313,20 @@
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="27.625" style="134" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.375" style="134" customWidth="1"/>
-    <col min="4" max="4" width="14.25" style="134" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.25" style="134" customWidth="1"/>
-    <col min="7" max="7" width="1.75" style="134" customWidth="1"/>
-    <col min="8" max="8" width="12.375" style="134" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="1.75" style="134" customWidth="1"/>
-    <col min="10" max="10" width="13.875" style="134" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.625" style="134" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.75" style="134" customWidth="1"/>
-    <col min="13" max="13" width="18.75" style="134" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.75" style="134" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.59765625" style="134" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.3984375" style="134" customWidth="1"/>
+    <col min="4" max="4" width="14.19921875" style="134" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.19921875" style="134" customWidth="1"/>
+    <col min="7" max="7" width="1.69921875" style="134" customWidth="1"/>
+    <col min="8" max="8" width="12.3984375" style="134" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="1.69921875" style="134" customWidth="1"/>
+    <col min="10" max="10" width="13.8984375" style="134" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.59765625" style="134" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.69921875" style="134" customWidth="1"/>
+    <col min="13" max="13" width="18.69921875" style="134" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.69921875" style="134" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="134"/>
   </cols>
   <sheetData>
@@ -6550,7 +6537,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="145"/>
-      <c r="E12" s="379"/>
+      <c r="E12" s="140">
+        <f>SUMIF(FAR!C:C,공시IS!A12,FAR!K:K)</f>
+        <v>0</v>
+      </c>
       <c r="F12" s="140"/>
       <c r="K12" s="379"/>
       <c r="L12" s="140">
@@ -6574,7 +6564,10 @@
         <v>0</v>
       </c>
       <c r="D13" s="145"/>
-      <c r="E13" s="379"/>
+      <c r="E13" s="140">
+        <f>SUMIF(FAR!C:C,공시IS!A13,FAR!K:K)</f>
+        <v>0</v>
+      </c>
       <c r="F13" s="140"/>
       <c r="K13" s="379"/>
       <c r="L13" s="140">
@@ -6640,7 +6633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="27">
+    <row r="16" spans="1:13" ht="31.2">
       <c r="A16" s="149" t="s">
         <v>584</v>
       </c>
@@ -6652,7 +6645,10 @@
         <v>0</v>
       </c>
       <c r="D16" s="145"/>
-      <c r="E16" s="379"/>
+      <c r="E16" s="140">
+        <f>SUMIF(FAR!C:C,공시IS!A16,FAR!K:K)</f>
+        <v>0</v>
+      </c>
       <c r="F16" s="140"/>
       <c r="K16" s="379"/>
       <c r="L16" s="140">
@@ -6791,7 +6787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="27">
+    <row r="21" spans="1:13" ht="31.2">
       <c r="A21" s="139" t="s">
         <v>240</v>
       </c>
@@ -6846,7 +6842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="27">
+    <row r="23" spans="1:13" ht="31.2">
       <c r="A23" s="139" t="s">
         <v>186</v>
       </c>
@@ -7011,7 +7007,7 @@
     <mergeCell ref="E6:F6"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A1:XFD26 A27:L27 N27:XFD27 A28:XFD28 A29:J29 N29:XFD29 A30:XFD1048576">
+  <conditionalFormatting sqref="A27:L27 N27:XFD27 A28:XFD28 A29:J29 N29:XFD29 A30:XFD1048576 A1:XFD26">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",A1)))</formula>
     </cfRule>
@@ -7030,10 +7026,10 @@
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="29.25" style="134" customWidth="1"/>
-    <col min="2" max="7" width="19.125" style="134" customWidth="1"/>
+    <col min="1" max="1" width="29.19921875" style="134" customWidth="1"/>
+    <col min="2" max="7" width="19.09765625" style="134" customWidth="1"/>
     <col min="8" max="8" width="12" style="134" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="134"/>
   </cols>
@@ -7078,7 +7074,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="6" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A6" s="155" t="s">
         <v>156</v>
       </c>
@@ -7101,7 +7097,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="7" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A7" s="223" t="s">
         <v>589</v>
       </c>
@@ -7112,7 +7108,7 @@
       <c r="F7" s="380"/>
       <c r="G7" s="380"/>
     </row>
-    <row r="8" spans="1:7" s="146" customFormat="1" ht="13.5">
+    <row r="8" spans="1:7" s="146" customFormat="1" ht="15.6">
       <c r="A8" s="139" t="s">
         <v>592</v>
       </c>
@@ -7126,7 +7122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="146" customFormat="1" ht="13.5">
+    <row r="9" spans="1:7" s="146" customFormat="1" ht="15.6">
       <c r="A9" s="223" t="s">
         <v>593</v>
       </c>
@@ -7155,7 +7151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="10" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A10" s="139" t="s">
         <v>195</v>
       </c>
@@ -7172,7 +7168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="11" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A11" s="139" t="s">
         <v>196</v>
       </c>
@@ -7183,7 +7179,7 @@
       <c r="F11" s="140"/>
       <c r="G11" s="140"/>
     </row>
-    <row r="12" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="12" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A12" s="156" t="s">
         <v>256</v>
       </c>
@@ -7197,7 +7193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="13" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A13" s="156" t="s">
         <v>594</v>
       </c>
@@ -7211,7 +7207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="14" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A14" s="156" t="s">
         <v>595</v>
       </c>
@@ -7228,7 +7224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="15" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A15" s="156" t="s">
         <v>596</v>
       </c>
@@ -7257,7 +7253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="16" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A16" s="139" t="s">
         <v>198</v>
       </c>
@@ -7271,7 +7267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="17" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A17" s="156" t="s">
         <v>257</v>
       </c>
@@ -7285,7 +7281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="18" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A18" s="156" t="s">
         <v>597</v>
       </c>
@@ -7299,7 +7295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="19" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A19" s="223" t="s">
         <v>598</v>
       </c>
@@ -7328,7 +7324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="20" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A20" s="223" t="s">
         <v>599</v>
       </c>
@@ -7342,7 +7338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="21" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A21" s="139" t="s">
         <v>195</v>
       </c>
@@ -7359,7 +7355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="22" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A22" s="139" t="s">
         <v>196</v>
       </c>
@@ -7373,7 +7369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="23" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A23" s="139" t="s">
         <v>256</v>
       </c>
@@ -7390,7 +7386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="24" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A24" s="139" t="s">
         <v>197</v>
       </c>
@@ -7407,7 +7403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="25" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A25" s="139" t="s">
         <v>600</v>
       </c>
@@ -7421,7 +7417,7 @@
       </c>
       <c r="G25" s="140"/>
     </row>
-    <row r="26" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="26" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A26" s="139" t="s">
         <v>596</v>
       </c>
@@ -7450,7 +7446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="27" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A27" s="139" t="s">
         <v>198</v>
       </c>
@@ -7464,7 +7460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="28" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A28" s="156" t="s">
         <v>199</v>
       </c>
@@ -7478,7 +7474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="29" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A29" s="156" t="s">
         <v>354</v>
       </c>
@@ -7492,7 +7488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" s="154" customFormat="1" ht="13.5">
+    <row r="30" spans="1:7" s="154" customFormat="1" ht="15.6">
       <c r="A30" s="223" t="s">
         <v>200</v>
       </c>
@@ -7521,7 +7517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" s="146" customFormat="1" ht="13.5">
+    <row r="31" spans="1:7" s="146" customFormat="1" ht="15.6">
       <c r="B31" s="146" t="b">
         <f>B30=공시BS!D39</f>
         <v>1</v>
@@ -7568,15 +7564,15 @@
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="B1:F64"/>
-  <sheetFormatPr defaultColWidth="28.25" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="28.19921875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="2.5" style="159" customWidth="1"/>
-    <col min="2" max="2" width="38.25" style="159" customWidth="1"/>
-    <col min="3" max="3" width="14.625" style="159" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.25" style="159" customWidth="1"/>
-    <col min="5" max="6" width="14.625" style="159" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.625" style="159" customWidth="1"/>
-    <col min="8" max="16384" width="28.25" style="159"/>
+    <col min="2" max="2" width="38.19921875" style="159" customWidth="1"/>
+    <col min="3" max="3" width="14.59765625" style="159" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.19921875" style="159" customWidth="1"/>
+    <col min="5" max="6" width="14.59765625" style="159" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.59765625" style="159" customWidth="1"/>
+    <col min="8" max="16384" width="28.19921875" style="159"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
@@ -8213,788 +8209,788 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:O67"/>
-  <sheetFormatPr defaultColWidth="7" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="7" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="1.125" style="188" customWidth="1"/>
+    <col min="1" max="1" width="1.09765625" style="188" customWidth="1"/>
     <col min="2" max="2" width="4" style="188" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="188" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="188" customWidth="1"/>
     <col min="4" max="4" width="4" style="188" customWidth="1"/>
-    <col min="5" max="5" width="12.75" style="188" customWidth="1"/>
-    <col min="6" max="6" width="12.75" style="188" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.75" style="188" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.25" style="188" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="15.75" style="188" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.75" style="188" customWidth="1"/>
-    <col min="12" max="13" width="12.625" style="188" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" style="188" customWidth="1"/>
+    <col min="6" max="6" width="12.69921875" style="188" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.69921875" style="188" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.19921875" style="188" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="15.69921875" style="188" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.69921875" style="188" customWidth="1"/>
+    <col min="12" max="13" width="12.59765625" style="188" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="1" style="188" customWidth="1"/>
-    <col min="15" max="15" width="6.25" style="188" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.125" style="188" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.19921875" style="188" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.09765625" style="188" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16.5" style="188" customWidth="1"/>
     <col min="18" max="18" width="13.5" style="188" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.75" style="188" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="15.625" style="188" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.69921875" style="188" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="15.59765625" style="188" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11.5" style="188" bestFit="1" customWidth="1"/>
-    <col min="23" max="26" width="15.125" style="188" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="15.09765625" style="188" bestFit="1" customWidth="1"/>
     <col min="27" max="253" width="7" style="188"/>
-    <col min="254" max="254" width="9.625" style="188" customWidth="1"/>
+    <col min="254" max="254" width="9.59765625" style="188" customWidth="1"/>
     <col min="255" max="255" width="4" style="188" customWidth="1"/>
-    <col min="256" max="256" width="11.25" style="188" customWidth="1"/>
+    <col min="256" max="256" width="11.19921875" style="188" customWidth="1"/>
     <col min="257" max="257" width="4" style="188" customWidth="1"/>
-    <col min="258" max="258" width="11.625" style="188" customWidth="1"/>
+    <col min="258" max="258" width="11.59765625" style="188" customWidth="1"/>
     <col min="259" max="259" width="4" style="188" customWidth="1"/>
-    <col min="260" max="263" width="17.25" style="188" customWidth="1"/>
-    <col min="264" max="264" width="6.75" style="188" customWidth="1"/>
-    <col min="265" max="265" width="8.75" style="188" customWidth="1"/>
+    <col min="260" max="263" width="17.19921875" style="188" customWidth="1"/>
+    <col min="264" max="264" width="6.69921875" style="188" customWidth="1"/>
+    <col min="265" max="265" width="8.69921875" style="188" customWidth="1"/>
     <col min="266" max="266" width="7" style="188" customWidth="1"/>
-    <col min="267" max="267" width="12.125" style="188" customWidth="1"/>
+    <col min="267" max="267" width="12.09765625" style="188" customWidth="1"/>
     <col min="268" max="509" width="7" style="188"/>
-    <col min="510" max="510" width="9.625" style="188" customWidth="1"/>
+    <col min="510" max="510" width="9.59765625" style="188" customWidth="1"/>
     <col min="511" max="511" width="4" style="188" customWidth="1"/>
-    <col min="512" max="512" width="11.25" style="188" customWidth="1"/>
+    <col min="512" max="512" width="11.19921875" style="188" customWidth="1"/>
     <col min="513" max="513" width="4" style="188" customWidth="1"/>
-    <col min="514" max="514" width="11.625" style="188" customWidth="1"/>
+    <col min="514" max="514" width="11.59765625" style="188" customWidth="1"/>
     <col min="515" max="515" width="4" style="188" customWidth="1"/>
-    <col min="516" max="519" width="17.25" style="188" customWidth="1"/>
-    <col min="520" max="520" width="6.75" style="188" customWidth="1"/>
-    <col min="521" max="521" width="8.75" style="188" customWidth="1"/>
+    <col min="516" max="519" width="17.19921875" style="188" customWidth="1"/>
+    <col min="520" max="520" width="6.69921875" style="188" customWidth="1"/>
+    <col min="521" max="521" width="8.69921875" style="188" customWidth="1"/>
     <col min="522" max="522" width="7" style="188" customWidth="1"/>
-    <col min="523" max="523" width="12.125" style="188" customWidth="1"/>
+    <col min="523" max="523" width="12.09765625" style="188" customWidth="1"/>
     <col min="524" max="765" width="7" style="188"/>
-    <col min="766" max="766" width="9.625" style="188" customWidth="1"/>
+    <col min="766" max="766" width="9.59765625" style="188" customWidth="1"/>
     <col min="767" max="767" width="4" style="188" customWidth="1"/>
-    <col min="768" max="768" width="11.25" style="188" customWidth="1"/>
+    <col min="768" max="768" width="11.19921875" style="188" customWidth="1"/>
     <col min="769" max="769" width="4" style="188" customWidth="1"/>
-    <col min="770" max="770" width="11.625" style="188" customWidth="1"/>
+    <col min="770" max="770" width="11.59765625" style="188" customWidth="1"/>
     <col min="771" max="771" width="4" style="188" customWidth="1"/>
-    <col min="772" max="775" width="17.25" style="188" customWidth="1"/>
-    <col min="776" max="776" width="6.75" style="188" customWidth="1"/>
-    <col min="777" max="777" width="8.75" style="188" customWidth="1"/>
+    <col min="772" max="775" width="17.19921875" style="188" customWidth="1"/>
+    <col min="776" max="776" width="6.69921875" style="188" customWidth="1"/>
+    <col min="777" max="777" width="8.69921875" style="188" customWidth="1"/>
     <col min="778" max="778" width="7" style="188" customWidth="1"/>
-    <col min="779" max="779" width="12.125" style="188" customWidth="1"/>
+    <col min="779" max="779" width="12.09765625" style="188" customWidth="1"/>
     <col min="780" max="1021" width="7" style="188"/>
-    <col min="1022" max="1022" width="9.625" style="188" customWidth="1"/>
+    <col min="1022" max="1022" width="9.59765625" style="188" customWidth="1"/>
     <col min="1023" max="1023" width="4" style="188" customWidth="1"/>
-    <col min="1024" max="1024" width="11.25" style="188" customWidth="1"/>
+    <col min="1024" max="1024" width="11.19921875" style="188" customWidth="1"/>
     <col min="1025" max="1025" width="4" style="188" customWidth="1"/>
-    <col min="1026" max="1026" width="11.625" style="188" customWidth="1"/>
+    <col min="1026" max="1026" width="11.59765625" style="188" customWidth="1"/>
     <col min="1027" max="1027" width="4" style="188" customWidth="1"/>
-    <col min="1028" max="1031" width="17.25" style="188" customWidth="1"/>
-    <col min="1032" max="1032" width="6.75" style="188" customWidth="1"/>
-    <col min="1033" max="1033" width="8.75" style="188" customWidth="1"/>
+    <col min="1028" max="1031" width="17.19921875" style="188" customWidth="1"/>
+    <col min="1032" max="1032" width="6.69921875" style="188" customWidth="1"/>
+    <col min="1033" max="1033" width="8.69921875" style="188" customWidth="1"/>
     <col min="1034" max="1034" width="7" style="188" customWidth="1"/>
-    <col min="1035" max="1035" width="12.125" style="188" customWidth="1"/>
+    <col min="1035" max="1035" width="12.09765625" style="188" customWidth="1"/>
     <col min="1036" max="1277" width="7" style="188"/>
-    <col min="1278" max="1278" width="9.625" style="188" customWidth="1"/>
+    <col min="1278" max="1278" width="9.59765625" style="188" customWidth="1"/>
     <col min="1279" max="1279" width="4" style="188" customWidth="1"/>
-    <col min="1280" max="1280" width="11.25" style="188" customWidth="1"/>
+    <col min="1280" max="1280" width="11.19921875" style="188" customWidth="1"/>
     <col min="1281" max="1281" width="4" style="188" customWidth="1"/>
-    <col min="1282" max="1282" width="11.625" style="188" customWidth="1"/>
+    <col min="1282" max="1282" width="11.59765625" style="188" customWidth="1"/>
     <col min="1283" max="1283" width="4" style="188" customWidth="1"/>
-    <col min="1284" max="1287" width="17.25" style="188" customWidth="1"/>
-    <col min="1288" max="1288" width="6.75" style="188" customWidth="1"/>
-    <col min="1289" max="1289" width="8.75" style="188" customWidth="1"/>
+    <col min="1284" max="1287" width="17.19921875" style="188" customWidth="1"/>
+    <col min="1288" max="1288" width="6.69921875" style="188" customWidth="1"/>
+    <col min="1289" max="1289" width="8.69921875" style="188" customWidth="1"/>
     <col min="1290" max="1290" width="7" style="188" customWidth="1"/>
-    <col min="1291" max="1291" width="12.125" style="188" customWidth="1"/>
+    <col min="1291" max="1291" width="12.09765625" style="188" customWidth="1"/>
     <col min="1292" max="1533" width="7" style="188"/>
-    <col min="1534" max="1534" width="9.625" style="188" customWidth="1"/>
+    <col min="1534" max="1534" width="9.59765625" style="188" customWidth="1"/>
     <col min="1535" max="1535" width="4" style="188" customWidth="1"/>
-    <col min="1536" max="1536" width="11.25" style="188" customWidth="1"/>
+    <col min="1536" max="1536" width="11.19921875" style="188" customWidth="1"/>
     <col min="1537" max="1537" width="4" style="188" customWidth="1"/>
-    <col min="1538" max="1538" width="11.625" style="188" customWidth="1"/>
+    <col min="1538" max="1538" width="11.59765625" style="188" customWidth="1"/>
     <col min="1539" max="1539" width="4" style="188" customWidth="1"/>
-    <col min="1540" max="1543" width="17.25" style="188" customWidth="1"/>
-    <col min="1544" max="1544" width="6.75" style="188" customWidth="1"/>
-    <col min="1545" max="1545" width="8.75" style="188" customWidth="1"/>
+    <col min="1540" max="1543" width="17.19921875" style="188" customWidth="1"/>
+    <col min="1544" max="1544" width="6.69921875" style="188" customWidth="1"/>
+    <col min="1545" max="1545" width="8.69921875" style="188" customWidth="1"/>
     <col min="1546" max="1546" width="7" style="188" customWidth="1"/>
-    <col min="1547" max="1547" width="12.125" style="188" customWidth="1"/>
+    <col min="1547" max="1547" width="12.09765625" style="188" customWidth="1"/>
     <col min="1548" max="1789" width="7" style="188"/>
-    <col min="1790" max="1790" width="9.625" style="188" customWidth="1"/>
+    <col min="1790" max="1790" width="9.59765625" style="188" customWidth="1"/>
     <col min="1791" max="1791" width="4" style="188" customWidth="1"/>
-    <col min="1792" max="1792" width="11.25" style="188" customWidth="1"/>
+    <col min="1792" max="1792" width="11.19921875" style="188" customWidth="1"/>
     <col min="1793" max="1793" width="4" style="188" customWidth="1"/>
-    <col min="1794" max="1794" width="11.625" style="188" customWidth="1"/>
+    <col min="1794" max="1794" width="11.59765625" style="188" customWidth="1"/>
     <col min="1795" max="1795" width="4" style="188" customWidth="1"/>
-    <col min="1796" max="1799" width="17.25" style="188" customWidth="1"/>
-    <col min="1800" max="1800" width="6.75" style="188" customWidth="1"/>
-    <col min="1801" max="1801" width="8.75" style="188" customWidth="1"/>
+    <col min="1796" max="1799" width="17.19921875" style="188" customWidth="1"/>
+    <col min="1800" max="1800" width="6.69921875" style="188" customWidth="1"/>
+    <col min="1801" max="1801" width="8.69921875" style="188" customWidth="1"/>
     <col min="1802" max="1802" width="7" style="188" customWidth="1"/>
-    <col min="1803" max="1803" width="12.125" style="188" customWidth="1"/>
+    <col min="1803" max="1803" width="12.09765625" style="188" customWidth="1"/>
     <col min="1804" max="2045" width="7" style="188"/>
-    <col min="2046" max="2046" width="9.625" style="188" customWidth="1"/>
+    <col min="2046" max="2046" width="9.59765625" style="188" customWidth="1"/>
     <col min="2047" max="2047" width="4" style="188" customWidth="1"/>
-    <col min="2048" max="2048" width="11.25" style="188" customWidth="1"/>
+    <col min="2048" max="2048" width="11.19921875" style="188" customWidth="1"/>
     <col min="2049" max="2049" width="4" style="188" customWidth="1"/>
-    <col min="2050" max="2050" width="11.625" style="188" customWidth="1"/>
+    <col min="2050" max="2050" width="11.59765625" style="188" customWidth="1"/>
     <col min="2051" max="2051" width="4" style="188" customWidth="1"/>
-    <col min="2052" max="2055" width="17.25" style="188" customWidth="1"/>
-    <col min="2056" max="2056" width="6.75" style="188" customWidth="1"/>
-    <col min="2057" max="2057" width="8.75" style="188" customWidth="1"/>
+    <col min="2052" max="2055" width="17.19921875" style="188" customWidth="1"/>
+    <col min="2056" max="2056" width="6.69921875" style="188" customWidth="1"/>
+    <col min="2057" max="2057" width="8.69921875" style="188" customWidth="1"/>
     <col min="2058" max="2058" width="7" style="188" customWidth="1"/>
-    <col min="2059" max="2059" width="12.125" style="188" customWidth="1"/>
+    <col min="2059" max="2059" width="12.09765625" style="188" customWidth="1"/>
     <col min="2060" max="2301" width="7" style="188"/>
-    <col min="2302" max="2302" width="9.625" style="188" customWidth="1"/>
+    <col min="2302" max="2302" width="9.59765625" style="188" customWidth="1"/>
     <col min="2303" max="2303" width="4" style="188" customWidth="1"/>
-    <col min="2304" max="2304" width="11.25" style="188" customWidth="1"/>
+    <col min="2304" max="2304" width="11.19921875" style="188" customWidth="1"/>
     <col min="2305" max="2305" width="4" style="188" customWidth="1"/>
-    <col min="2306" max="2306" width="11.625" style="188" customWidth="1"/>
+    <col min="2306" max="2306" width="11.59765625" style="188" customWidth="1"/>
     <col min="2307" max="2307" width="4" style="188" customWidth="1"/>
-    <col min="2308" max="2311" width="17.25" style="188" customWidth="1"/>
-    <col min="2312" max="2312" width="6.75" style="188" customWidth="1"/>
-    <col min="2313" max="2313" width="8.75" style="188" customWidth="1"/>
+    <col min="2308" max="2311" width="17.19921875" style="188" customWidth="1"/>
+    <col min="2312" max="2312" width="6.69921875" style="188" customWidth="1"/>
+    <col min="2313" max="2313" width="8.69921875" style="188" customWidth="1"/>
     <col min="2314" max="2314" width="7" style="188" customWidth="1"/>
-    <col min="2315" max="2315" width="12.125" style="188" customWidth="1"/>
+    <col min="2315" max="2315" width="12.09765625" style="188" customWidth="1"/>
     <col min="2316" max="2557" width="7" style="188"/>
-    <col min="2558" max="2558" width="9.625" style="188" customWidth="1"/>
+    <col min="2558" max="2558" width="9.59765625" style="188" customWidth="1"/>
     <col min="2559" max="2559" width="4" style="188" customWidth="1"/>
-    <col min="2560" max="2560" width="11.25" style="188" customWidth="1"/>
+    <col min="2560" max="2560" width="11.19921875" style="188" customWidth="1"/>
     <col min="2561" max="2561" width="4" style="188" customWidth="1"/>
-    <col min="2562" max="2562" width="11.625" style="188" customWidth="1"/>
+    <col min="2562" max="2562" width="11.59765625" style="188" customWidth="1"/>
     <col min="2563" max="2563" width="4" style="188" customWidth="1"/>
-    <col min="2564" max="2567" width="17.25" style="188" customWidth="1"/>
-    <col min="2568" max="2568" width="6.75" style="188" customWidth="1"/>
-    <col min="2569" max="2569" width="8.75" style="188" customWidth="1"/>
+    <col min="2564" max="2567" width="17.19921875" style="188" customWidth="1"/>
+    <col min="2568" max="2568" width="6.69921875" style="188" customWidth="1"/>
+    <col min="2569" max="2569" width="8.69921875" style="188" customWidth="1"/>
     <col min="2570" max="2570" width="7" style="188" customWidth="1"/>
-    <col min="2571" max="2571" width="12.125" style="188" customWidth="1"/>
+    <col min="2571" max="2571" width="12.09765625" style="188" customWidth="1"/>
     <col min="2572" max="2813" width="7" style="188"/>
-    <col min="2814" max="2814" width="9.625" style="188" customWidth="1"/>
+    <col min="2814" max="2814" width="9.59765625" style="188" customWidth="1"/>
     <col min="2815" max="2815" width="4" style="188" customWidth="1"/>
-    <col min="2816" max="2816" width="11.25" style="188" customWidth="1"/>
+    <col min="2816" max="2816" width="11.19921875" style="188" customWidth="1"/>
     <col min="2817" max="2817" width="4" style="188" customWidth="1"/>
-    <col min="2818" max="2818" width="11.625" style="188" customWidth="1"/>
+    <col min="2818" max="2818" width="11.59765625" style="188" customWidth="1"/>
     <col min="2819" max="2819" width="4" style="188" customWidth="1"/>
-    <col min="2820" max="2823" width="17.25" style="188" customWidth="1"/>
-    <col min="2824" max="2824" width="6.75" style="188" customWidth="1"/>
-    <col min="2825" max="2825" width="8.75" style="188" customWidth="1"/>
+    <col min="2820" max="2823" width="17.19921875" style="188" customWidth="1"/>
+    <col min="2824" max="2824" width="6.69921875" style="188" customWidth="1"/>
+    <col min="2825" max="2825" width="8.69921875" style="188" customWidth="1"/>
     <col min="2826" max="2826" width="7" style="188" customWidth="1"/>
-    <col min="2827" max="2827" width="12.125" style="188" customWidth="1"/>
+    <col min="2827" max="2827" width="12.09765625" style="188" customWidth="1"/>
     <col min="2828" max="3069" width="7" style="188"/>
-    <col min="3070" max="3070" width="9.625" style="188" customWidth="1"/>
+    <col min="3070" max="3070" width="9.59765625" style="188" customWidth="1"/>
     <col min="3071" max="3071" width="4" style="188" customWidth="1"/>
-    <col min="3072" max="3072" width="11.25" style="188" customWidth="1"/>
+    <col min="3072" max="3072" width="11.19921875" style="188" customWidth="1"/>
     <col min="3073" max="3073" width="4" style="188" customWidth="1"/>
-    <col min="3074" max="3074" width="11.625" style="188" customWidth="1"/>
+    <col min="3074" max="3074" width="11.59765625" style="188" customWidth="1"/>
     <col min="3075" max="3075" width="4" style="188" customWidth="1"/>
-    <col min="3076" max="3079" width="17.25" style="188" customWidth="1"/>
-    <col min="3080" max="3080" width="6.75" style="188" customWidth="1"/>
-    <col min="3081" max="3081" width="8.75" style="188" customWidth="1"/>
+    <col min="3076" max="3079" width="17.19921875" style="188" customWidth="1"/>
+    <col min="3080" max="3080" width="6.69921875" style="188" customWidth="1"/>
+    <col min="3081" max="3081" width="8.69921875" style="188" customWidth="1"/>
     <col min="3082" max="3082" width="7" style="188" customWidth="1"/>
-    <col min="3083" max="3083" width="12.125" style="188" customWidth="1"/>
+    <col min="3083" max="3083" width="12.09765625" style="188" customWidth="1"/>
     <col min="3084" max="3325" width="7" style="188"/>
-    <col min="3326" max="3326" width="9.625" style="188" customWidth="1"/>
+    <col min="3326" max="3326" width="9.59765625" style="188" customWidth="1"/>
     <col min="3327" max="3327" width="4" style="188" customWidth="1"/>
-    <col min="3328" max="3328" width="11.25" style="188" customWidth="1"/>
+    <col min="3328" max="3328" width="11.19921875" style="188" customWidth="1"/>
     <col min="3329" max="3329" width="4" style="188" customWidth="1"/>
-    <col min="3330" max="3330" width="11.625" style="188" customWidth="1"/>
+    <col min="3330" max="3330" width="11.59765625" style="188" customWidth="1"/>
     <col min="3331" max="3331" width="4" style="188" customWidth="1"/>
-    <col min="3332" max="3335" width="17.25" style="188" customWidth="1"/>
-    <col min="3336" max="3336" width="6.75" style="188" customWidth="1"/>
-    <col min="3337" max="3337" width="8.75" style="188" customWidth="1"/>
+    <col min="3332" max="3335" width="17.19921875" style="188" customWidth="1"/>
+    <col min="3336" max="3336" width="6.69921875" style="188" customWidth="1"/>
+    <col min="3337" max="3337" width="8.69921875" style="188" customWidth="1"/>
     <col min="3338" max="3338" width="7" style="188" customWidth="1"/>
-    <col min="3339" max="3339" width="12.125" style="188" customWidth="1"/>
+    <col min="3339" max="3339" width="12.09765625" style="188" customWidth="1"/>
     <col min="3340" max="3581" width="7" style="188"/>
-    <col min="3582" max="3582" width="9.625" style="188" customWidth="1"/>
+    <col min="3582" max="3582" width="9.59765625" style="188" customWidth="1"/>
     <col min="3583" max="3583" width="4" style="188" customWidth="1"/>
-    <col min="3584" max="3584" width="11.25" style="188" customWidth="1"/>
+    <col min="3584" max="3584" width="11.19921875" style="188" customWidth="1"/>
     <col min="3585" max="3585" width="4" style="188" customWidth="1"/>
-    <col min="3586" max="3586" width="11.625" style="188" customWidth="1"/>
+    <col min="3586" max="3586" width="11.59765625" style="188" customWidth="1"/>
     <col min="3587" max="3587" width="4" style="188" customWidth="1"/>
-    <col min="3588" max="3591" width="17.25" style="188" customWidth="1"/>
-    <col min="3592" max="3592" width="6.75" style="188" customWidth="1"/>
-    <col min="3593" max="3593" width="8.75" style="188" customWidth="1"/>
+    <col min="3588" max="3591" width="17.19921875" style="188" customWidth="1"/>
+    <col min="3592" max="3592" width="6.69921875" style="188" customWidth="1"/>
+    <col min="3593" max="3593" width="8.69921875" style="188" customWidth="1"/>
     <col min="3594" max="3594" width="7" style="188" customWidth="1"/>
-    <col min="3595" max="3595" width="12.125" style="188" customWidth="1"/>
+    <col min="3595" max="3595" width="12.09765625" style="188" customWidth="1"/>
     <col min="3596" max="3837" width="7" style="188"/>
-    <col min="3838" max="3838" width="9.625" style="188" customWidth="1"/>
+    <col min="3838" max="3838" width="9.59765625" style="188" customWidth="1"/>
     <col min="3839" max="3839" width="4" style="188" customWidth="1"/>
-    <col min="3840" max="3840" width="11.25" style="188" customWidth="1"/>
+    <col min="3840" max="3840" width="11.19921875" style="188" customWidth="1"/>
     <col min="3841" max="3841" width="4" style="188" customWidth="1"/>
-    <col min="3842" max="3842" width="11.625" style="188" customWidth="1"/>
+    <col min="3842" max="3842" width="11.59765625" style="188" customWidth="1"/>
     <col min="3843" max="3843" width="4" style="188" customWidth="1"/>
-    <col min="3844" max="3847" width="17.25" style="188" customWidth="1"/>
-    <col min="3848" max="3848" width="6.75" style="188" customWidth="1"/>
-    <col min="3849" max="3849" width="8.75" style="188" customWidth="1"/>
+    <col min="3844" max="3847" width="17.19921875" style="188" customWidth="1"/>
+    <col min="3848" max="3848" width="6.69921875" style="188" customWidth="1"/>
+    <col min="3849" max="3849" width="8.69921875" style="188" customWidth="1"/>
     <col min="3850" max="3850" width="7" style="188" customWidth="1"/>
-    <col min="3851" max="3851" width="12.125" style="188" customWidth="1"/>
+    <col min="3851" max="3851" width="12.09765625" style="188" customWidth="1"/>
     <col min="3852" max="4093" width="7" style="188"/>
-    <col min="4094" max="4094" width="9.625" style="188" customWidth="1"/>
+    <col min="4094" max="4094" width="9.59765625" style="188" customWidth="1"/>
     <col min="4095" max="4095" width="4" style="188" customWidth="1"/>
-    <col min="4096" max="4096" width="11.25" style="188" customWidth="1"/>
+    <col min="4096" max="4096" width="11.19921875" style="188" customWidth="1"/>
     <col min="4097" max="4097" width="4" style="188" customWidth="1"/>
-    <col min="4098" max="4098" width="11.625" style="188" customWidth="1"/>
+    <col min="4098" max="4098" width="11.59765625" style="188" customWidth="1"/>
     <col min="4099" max="4099" width="4" style="188" customWidth="1"/>
-    <col min="4100" max="4103" width="17.25" style="188" customWidth="1"/>
-    <col min="4104" max="4104" width="6.75" style="188" customWidth="1"/>
-    <col min="4105" max="4105" width="8.75" style="188" customWidth="1"/>
+    <col min="4100" max="4103" width="17.19921875" style="188" customWidth="1"/>
+    <col min="4104" max="4104" width="6.69921875" style="188" customWidth="1"/>
+    <col min="4105" max="4105" width="8.69921875" style="188" customWidth="1"/>
     <col min="4106" max="4106" width="7" style="188" customWidth="1"/>
-    <col min="4107" max="4107" width="12.125" style="188" customWidth="1"/>
+    <col min="4107" max="4107" width="12.09765625" style="188" customWidth="1"/>
     <col min="4108" max="4349" width="7" style="188"/>
-    <col min="4350" max="4350" width="9.625" style="188" customWidth="1"/>
+    <col min="4350" max="4350" width="9.59765625" style="188" customWidth="1"/>
     <col min="4351" max="4351" width="4" style="188" customWidth="1"/>
-    <col min="4352" max="4352" width="11.25" style="188" customWidth="1"/>
+    <col min="4352" max="4352" width="11.19921875" style="188" customWidth="1"/>
     <col min="4353" max="4353" width="4" style="188" customWidth="1"/>
-    <col min="4354" max="4354" width="11.625" style="188" customWidth="1"/>
+    <col min="4354" max="4354" width="11.59765625" style="188" customWidth="1"/>
     <col min="4355" max="4355" width="4" style="188" customWidth="1"/>
-    <col min="4356" max="4359" width="17.25" style="188" customWidth="1"/>
-    <col min="4360" max="4360" width="6.75" style="188" customWidth="1"/>
-    <col min="4361" max="4361" width="8.75" style="188" customWidth="1"/>
+    <col min="4356" max="4359" width="17.19921875" style="188" customWidth="1"/>
+    <col min="4360" max="4360" width="6.69921875" style="188" customWidth="1"/>
+    <col min="4361" max="4361" width="8.69921875" style="188" customWidth="1"/>
     <col min="4362" max="4362" width="7" style="188" customWidth="1"/>
-    <col min="4363" max="4363" width="12.125" style="188" customWidth="1"/>
+    <col min="4363" max="4363" width="12.09765625" style="188" customWidth="1"/>
     <col min="4364" max="4605" width="7" style="188"/>
-    <col min="4606" max="4606" width="9.625" style="188" customWidth="1"/>
+    <col min="4606" max="4606" width="9.59765625" style="188" customWidth="1"/>
     <col min="4607" max="4607" width="4" style="188" customWidth="1"/>
-    <col min="4608" max="4608" width="11.25" style="188" customWidth="1"/>
+    <col min="4608" max="4608" width="11.19921875" style="188" customWidth="1"/>
     <col min="4609" max="4609" width="4" style="188" customWidth="1"/>
-    <col min="4610" max="4610" width="11.625" style="188" customWidth="1"/>
+    <col min="4610" max="4610" width="11.59765625" style="188" customWidth="1"/>
     <col min="4611" max="4611" width="4" style="188" customWidth="1"/>
-    <col min="4612" max="4615" width="17.25" style="188" customWidth="1"/>
-    <col min="4616" max="4616" width="6.75" style="188" customWidth="1"/>
-    <col min="4617" max="4617" width="8.75" style="188" customWidth="1"/>
+    <col min="4612" max="4615" width="17.19921875" style="188" customWidth="1"/>
+    <col min="4616" max="4616" width="6.69921875" style="188" customWidth="1"/>
+    <col min="4617" max="4617" width="8.69921875" style="188" customWidth="1"/>
     <col min="4618" max="4618" width="7" style="188" customWidth="1"/>
-    <col min="4619" max="4619" width="12.125" style="188" customWidth="1"/>
+    <col min="4619" max="4619" width="12.09765625" style="188" customWidth="1"/>
     <col min="4620" max="4861" width="7" style="188"/>
-    <col min="4862" max="4862" width="9.625" style="188" customWidth="1"/>
+    <col min="4862" max="4862" width="9.59765625" style="188" customWidth="1"/>
     <col min="4863" max="4863" width="4" style="188" customWidth="1"/>
-    <col min="4864" max="4864" width="11.25" style="188" customWidth="1"/>
+    <col min="4864" max="4864" width="11.19921875" style="188" customWidth="1"/>
     <col min="4865" max="4865" width="4" style="188" customWidth="1"/>
-    <col min="4866" max="4866" width="11.625" style="188" customWidth="1"/>
+    <col min="4866" max="4866" width="11.59765625" style="188" customWidth="1"/>
     <col min="4867" max="4867" width="4" style="188" customWidth="1"/>
-    <col min="4868" max="4871" width="17.25" style="188" customWidth="1"/>
-    <col min="4872" max="4872" width="6.75" style="188" customWidth="1"/>
-    <col min="4873" max="4873" width="8.75" style="188" customWidth="1"/>
+    <col min="4868" max="4871" width="17.19921875" style="188" customWidth="1"/>
+    <col min="4872" max="4872" width="6.69921875" style="188" customWidth="1"/>
+    <col min="4873" max="4873" width="8.69921875" style="188" customWidth="1"/>
     <col min="4874" max="4874" width="7" style="188" customWidth="1"/>
-    <col min="4875" max="4875" width="12.125" style="188" customWidth="1"/>
+    <col min="4875" max="4875" width="12.09765625" style="188" customWidth="1"/>
     <col min="4876" max="5117" width="7" style="188"/>
-    <col min="5118" max="5118" width="9.625" style="188" customWidth="1"/>
+    <col min="5118" max="5118" width="9.59765625" style="188" customWidth="1"/>
     <col min="5119" max="5119" width="4" style="188" customWidth="1"/>
-    <col min="5120" max="5120" width="11.25" style="188" customWidth="1"/>
+    <col min="5120" max="5120" width="11.19921875" style="188" customWidth="1"/>
     <col min="5121" max="5121" width="4" style="188" customWidth="1"/>
-    <col min="5122" max="5122" width="11.625" style="188" customWidth="1"/>
+    <col min="5122" max="5122" width="11.59765625" style="188" customWidth="1"/>
     <col min="5123" max="5123" width="4" style="188" customWidth="1"/>
-    <col min="5124" max="5127" width="17.25" style="188" customWidth="1"/>
-    <col min="5128" max="5128" width="6.75" style="188" customWidth="1"/>
-    <col min="5129" max="5129" width="8.75" style="188" customWidth="1"/>
+    <col min="5124" max="5127" width="17.19921875" style="188" customWidth="1"/>
+    <col min="5128" max="5128" width="6.69921875" style="188" customWidth="1"/>
+    <col min="5129" max="5129" width="8.69921875" style="188" customWidth="1"/>
     <col min="5130" max="5130" width="7" style="188" customWidth="1"/>
-    <col min="5131" max="5131" width="12.125" style="188" customWidth="1"/>
+    <col min="5131" max="5131" width="12.09765625" style="188" customWidth="1"/>
     <col min="5132" max="5373" width="7" style="188"/>
-    <col min="5374" max="5374" width="9.625" style="188" customWidth="1"/>
+    <col min="5374" max="5374" width="9.59765625" style="188" customWidth="1"/>
     <col min="5375" max="5375" width="4" style="188" customWidth="1"/>
-    <col min="5376" max="5376" width="11.25" style="188" customWidth="1"/>
+    <col min="5376" max="5376" width="11.19921875" style="188" customWidth="1"/>
     <col min="5377" max="5377" width="4" style="188" customWidth="1"/>
-    <col min="5378" max="5378" width="11.625" style="188" customWidth="1"/>
+    <col min="5378" max="5378" width="11.59765625" style="188" customWidth="1"/>
     <col min="5379" max="5379" width="4" style="188" customWidth="1"/>
-    <col min="5380" max="5383" width="17.25" style="188" customWidth="1"/>
-    <col min="5384" max="5384" width="6.75" style="188" customWidth="1"/>
-    <col min="5385" max="5385" width="8.75" style="188" customWidth="1"/>
+    <col min="5380" max="5383" width="17.19921875" style="188" customWidth="1"/>
+    <col min="5384" max="5384" width="6.69921875" style="188" customWidth="1"/>
+    <col min="5385" max="5385" width="8.69921875" style="188" customWidth="1"/>
     <col min="5386" max="5386" width="7" style="188" customWidth="1"/>
-    <col min="5387" max="5387" width="12.125" style="188" customWidth="1"/>
+    <col min="5387" max="5387" width="12.09765625" style="188" customWidth="1"/>
     <col min="5388" max="5629" width="7" style="188"/>
-    <col min="5630" max="5630" width="9.625" style="188" customWidth="1"/>
+    <col min="5630" max="5630" width="9.59765625" style="188" customWidth="1"/>
     <col min="5631" max="5631" width="4" style="188" customWidth="1"/>
-    <col min="5632" max="5632" width="11.25" style="188" customWidth="1"/>
+    <col min="5632" max="5632" width="11.19921875" style="188" customWidth="1"/>
     <col min="5633" max="5633" width="4" style="188" customWidth="1"/>
-    <col min="5634" max="5634" width="11.625" style="188" customWidth="1"/>
+    <col min="5634" max="5634" width="11.59765625" style="188" customWidth="1"/>
     <col min="5635" max="5635" width="4" style="188" customWidth="1"/>
-    <col min="5636" max="5639" width="17.25" style="188" customWidth="1"/>
-    <col min="5640" max="5640" width="6.75" style="188" customWidth="1"/>
-    <col min="5641" max="5641" width="8.75" style="188" customWidth="1"/>
+    <col min="5636" max="5639" width="17.19921875" style="188" customWidth="1"/>
+    <col min="5640" max="5640" width="6.69921875" style="188" customWidth="1"/>
+    <col min="5641" max="5641" width="8.69921875" style="188" customWidth="1"/>
     <col min="5642" max="5642" width="7" style="188" customWidth="1"/>
-    <col min="5643" max="5643" width="12.125" style="188" customWidth="1"/>
+    <col min="5643" max="5643" width="12.09765625" style="188" customWidth="1"/>
     <col min="5644" max="5885" width="7" style="188"/>
-    <col min="5886" max="5886" width="9.625" style="188" customWidth="1"/>
+    <col min="5886" max="5886" width="9.59765625" style="188" customWidth="1"/>
     <col min="5887" max="5887" width="4" style="188" customWidth="1"/>
-    <col min="5888" max="5888" width="11.25" style="188" customWidth="1"/>
+    <col min="5888" max="5888" width="11.19921875" style="188" customWidth="1"/>
     <col min="5889" max="5889" width="4" style="188" customWidth="1"/>
-    <col min="5890" max="5890" width="11.625" style="188" customWidth="1"/>
+    <col min="5890" max="5890" width="11.59765625" style="188" customWidth="1"/>
     <col min="5891" max="5891" width="4" style="188" customWidth="1"/>
-    <col min="5892" max="5895" width="17.25" style="188" customWidth="1"/>
-    <col min="5896" max="5896" width="6.75" style="188" customWidth="1"/>
-    <col min="5897" max="5897" width="8.75" style="188" customWidth="1"/>
+    <col min="5892" max="5895" width="17.19921875" style="188" customWidth="1"/>
+    <col min="5896" max="5896" width="6.69921875" style="188" customWidth="1"/>
+    <col min="5897" max="5897" width="8.69921875" style="188" customWidth="1"/>
     <col min="5898" max="5898" width="7" style="188" customWidth="1"/>
-    <col min="5899" max="5899" width="12.125" style="188" customWidth="1"/>
+    <col min="5899" max="5899" width="12.09765625" style="188" customWidth="1"/>
     <col min="5900" max="6141" width="7" style="188"/>
-    <col min="6142" max="6142" width="9.625" style="188" customWidth="1"/>
+    <col min="6142" max="6142" width="9.59765625" style="188" customWidth="1"/>
     <col min="6143" max="6143" width="4" style="188" customWidth="1"/>
-    <col min="6144" max="6144" width="11.25" style="188" customWidth="1"/>
+    <col min="6144" max="6144" width="11.19921875" style="188" customWidth="1"/>
     <col min="6145" max="6145" width="4" style="188" customWidth="1"/>
-    <col min="6146" max="6146" width="11.625" style="188" customWidth="1"/>
+    <col min="6146" max="6146" width="11.59765625" style="188" customWidth="1"/>
     <col min="6147" max="6147" width="4" style="188" customWidth="1"/>
-    <col min="6148" max="6151" width="17.25" style="188" customWidth="1"/>
-    <col min="6152" max="6152" width="6.75" style="188" customWidth="1"/>
-    <col min="6153" max="6153" width="8.75" style="188" customWidth="1"/>
+    <col min="6148" max="6151" width="17.19921875" style="188" customWidth="1"/>
+    <col min="6152" max="6152" width="6.69921875" style="188" customWidth="1"/>
+    <col min="6153" max="6153" width="8.69921875" style="188" customWidth="1"/>
     <col min="6154" max="6154" width="7" style="188" customWidth="1"/>
-    <col min="6155" max="6155" width="12.125" style="188" customWidth="1"/>
+    <col min="6155" max="6155" width="12.09765625" style="188" customWidth="1"/>
     <col min="6156" max="6397" width="7" style="188"/>
-    <col min="6398" max="6398" width="9.625" style="188" customWidth="1"/>
+    <col min="6398" max="6398" width="9.59765625" style="188" customWidth="1"/>
     <col min="6399" max="6399" width="4" style="188" customWidth="1"/>
-    <col min="6400" max="6400" width="11.25" style="188" customWidth="1"/>
+    <col min="6400" max="6400" width="11.19921875" style="188" customWidth="1"/>
     <col min="6401" max="6401" width="4" style="188" customWidth="1"/>
-    <col min="6402" max="6402" width="11.625" style="188" customWidth="1"/>
+    <col min="6402" max="6402" width="11.59765625" style="188" customWidth="1"/>
     <col min="6403" max="6403" width="4" style="188" customWidth="1"/>
-    <col min="6404" max="6407" width="17.25" style="188" customWidth="1"/>
-    <col min="6408" max="6408" width="6.75" style="188" customWidth="1"/>
-    <col min="6409" max="6409" width="8.75" style="188" customWidth="1"/>
+    <col min="6404" max="6407" width="17.19921875" style="188" customWidth="1"/>
+    <col min="6408" max="6408" width="6.69921875" style="188" customWidth="1"/>
+    <col min="6409" max="6409" width="8.69921875" style="188" customWidth="1"/>
     <col min="6410" max="6410" width="7" style="188" customWidth="1"/>
-    <col min="6411" max="6411" width="12.125" style="188" customWidth="1"/>
+    <col min="6411" max="6411" width="12.09765625" style="188" customWidth="1"/>
     <col min="6412" max="6653" width="7" style="188"/>
-    <col min="6654" max="6654" width="9.625" style="188" customWidth="1"/>
+    <col min="6654" max="6654" width="9.59765625" style="188" customWidth="1"/>
     <col min="6655" max="6655" width="4" style="188" customWidth="1"/>
-    <col min="6656" max="6656" width="11.25" style="188" customWidth="1"/>
+    <col min="6656" max="6656" width="11.19921875" style="188" customWidth="1"/>
     <col min="6657" max="6657" width="4" style="188" customWidth="1"/>
-    <col min="6658" max="6658" width="11.625" style="188" customWidth="1"/>
+    <col min="6658" max="6658" width="11.59765625" style="188" customWidth="1"/>
     <col min="6659" max="6659" width="4" style="188" customWidth="1"/>
-    <col min="6660" max="6663" width="17.25" style="188" customWidth="1"/>
-    <col min="6664" max="6664" width="6.75" style="188" customWidth="1"/>
-    <col min="6665" max="6665" width="8.75" style="188" customWidth="1"/>
+    <col min="6660" max="6663" width="17.19921875" style="188" customWidth="1"/>
+    <col min="6664" max="6664" width="6.69921875" style="188" customWidth="1"/>
+    <col min="6665" max="6665" width="8.69921875" style="188" customWidth="1"/>
     <col min="6666" max="6666" width="7" style="188" customWidth="1"/>
-    <col min="6667" max="6667" width="12.125" style="188" customWidth="1"/>
+    <col min="6667" max="6667" width="12.09765625" style="188" customWidth="1"/>
     <col min="6668" max="6909" width="7" style="188"/>
-    <col min="6910" max="6910" width="9.625" style="188" customWidth="1"/>
+    <col min="6910" max="6910" width="9.59765625" style="188" customWidth="1"/>
     <col min="6911" max="6911" width="4" style="188" customWidth="1"/>
-    <col min="6912" max="6912" width="11.25" style="188" customWidth="1"/>
+    <col min="6912" max="6912" width="11.19921875" style="188" customWidth="1"/>
     <col min="6913" max="6913" width="4" style="188" customWidth="1"/>
-    <col min="6914" max="6914" width="11.625" style="188" customWidth="1"/>
+    <col min="6914" max="6914" width="11.59765625" style="188" customWidth="1"/>
     <col min="6915" max="6915" width="4" style="188" customWidth="1"/>
-    <col min="6916" max="6919" width="17.25" style="188" customWidth="1"/>
-    <col min="6920" max="6920" width="6.75" style="188" customWidth="1"/>
-    <col min="6921" max="6921" width="8.75" style="188" customWidth="1"/>
+    <col min="6916" max="6919" width="17.19921875" style="188" customWidth="1"/>
+    <col min="6920" max="6920" width="6.69921875" style="188" customWidth="1"/>
+    <col min="6921" max="6921" width="8.69921875" style="188" customWidth="1"/>
     <col min="6922" max="6922" width="7" style="188" customWidth="1"/>
-    <col min="6923" max="6923" width="12.125" style="188" customWidth="1"/>
+    <col min="6923" max="6923" width="12.09765625" style="188" customWidth="1"/>
     <col min="6924" max="7165" width="7" style="188"/>
-    <col min="7166" max="7166" width="9.625" style="188" customWidth="1"/>
+    <col min="7166" max="7166" width="9.59765625" style="188" customWidth="1"/>
     <col min="7167" max="7167" width="4" style="188" customWidth="1"/>
-    <col min="7168" max="7168" width="11.25" style="188" customWidth="1"/>
+    <col min="7168" max="7168" width="11.19921875" style="188" customWidth="1"/>
     <col min="7169" max="7169" width="4" style="188" customWidth="1"/>
-    <col min="7170" max="7170" width="11.625" style="188" customWidth="1"/>
+    <col min="7170" max="7170" width="11.59765625" style="188" customWidth="1"/>
     <col min="7171" max="7171" width="4" style="188" customWidth="1"/>
-    <col min="7172" max="7175" width="17.25" style="188" customWidth="1"/>
-    <col min="7176" max="7176" width="6.75" style="188" customWidth="1"/>
-    <col min="7177" max="7177" width="8.75" style="188" customWidth="1"/>
+    <col min="7172" max="7175" width="17.19921875" style="188" customWidth="1"/>
+    <col min="7176" max="7176" width="6.69921875" style="188" customWidth="1"/>
+    <col min="7177" max="7177" width="8.69921875" style="188" customWidth="1"/>
     <col min="7178" max="7178" width="7" style="188" customWidth="1"/>
-    <col min="7179" max="7179" width="12.125" style="188" customWidth="1"/>
+    <col min="7179" max="7179" width="12.09765625" style="188" customWidth="1"/>
     <col min="7180" max="7421" width="7" style="188"/>
-    <col min="7422" max="7422" width="9.625" style="188" customWidth="1"/>
+    <col min="7422" max="7422" width="9.59765625" style="188" customWidth="1"/>
     <col min="7423" max="7423" width="4" style="188" customWidth="1"/>
-    <col min="7424" max="7424" width="11.25" style="188" customWidth="1"/>
+    <col min="7424" max="7424" width="11.19921875" style="188" customWidth="1"/>
     <col min="7425" max="7425" width="4" style="188" customWidth="1"/>
-    <col min="7426" max="7426" width="11.625" style="188" customWidth="1"/>
+    <col min="7426" max="7426" width="11.59765625" style="188" customWidth="1"/>
     <col min="7427" max="7427" width="4" style="188" customWidth="1"/>
-    <col min="7428" max="7431" width="17.25" style="188" customWidth="1"/>
-    <col min="7432" max="7432" width="6.75" style="188" customWidth="1"/>
-    <col min="7433" max="7433" width="8.75" style="188" customWidth="1"/>
+    <col min="7428" max="7431" width="17.19921875" style="188" customWidth="1"/>
+    <col min="7432" max="7432" width="6.69921875" style="188" customWidth="1"/>
+    <col min="7433" max="7433" width="8.69921875" style="188" customWidth="1"/>
     <col min="7434" max="7434" width="7" style="188" customWidth="1"/>
-    <col min="7435" max="7435" width="12.125" style="188" customWidth="1"/>
+    <col min="7435" max="7435" width="12.09765625" style="188" customWidth="1"/>
     <col min="7436" max="7677" width="7" style="188"/>
-    <col min="7678" max="7678" width="9.625" style="188" customWidth="1"/>
+    <col min="7678" max="7678" width="9.59765625" style="188" customWidth="1"/>
     <col min="7679" max="7679" width="4" style="188" customWidth="1"/>
-    <col min="7680" max="7680" width="11.25" style="188" customWidth="1"/>
+    <col min="7680" max="7680" width="11.19921875" style="188" customWidth="1"/>
     <col min="7681" max="7681" width="4" style="188" customWidth="1"/>
-    <col min="7682" max="7682" width="11.625" style="188" customWidth="1"/>
+    <col min="7682" max="7682" width="11.59765625" style="188" customWidth="1"/>
     <col min="7683" max="7683" width="4" style="188" customWidth="1"/>
-    <col min="7684" max="7687" width="17.25" style="188" customWidth="1"/>
-    <col min="7688" max="7688" width="6.75" style="188" customWidth="1"/>
-    <col min="7689" max="7689" width="8.75" style="188" customWidth="1"/>
+    <col min="7684" max="7687" width="17.19921875" style="188" customWidth="1"/>
+    <col min="7688" max="7688" width="6.69921875" style="188" customWidth="1"/>
+    <col min="7689" max="7689" width="8.69921875" style="188" customWidth="1"/>
     <col min="7690" max="7690" width="7" style="188" customWidth="1"/>
-    <col min="7691" max="7691" width="12.125" style="188" customWidth="1"/>
+    <col min="7691" max="7691" width="12.09765625" style="188" customWidth="1"/>
     <col min="7692" max="7933" width="7" style="188"/>
-    <col min="7934" max="7934" width="9.625" style="188" customWidth="1"/>
+    <col min="7934" max="7934" width="9.59765625" style="188" customWidth="1"/>
     <col min="7935" max="7935" width="4" style="188" customWidth="1"/>
-    <col min="7936" max="7936" width="11.25" style="188" customWidth="1"/>
+    <col min="7936" max="7936" width="11.19921875" style="188" customWidth="1"/>
     <col min="7937" max="7937" width="4" style="188" customWidth="1"/>
-    <col min="7938" max="7938" width="11.625" style="188" customWidth="1"/>
+    <col min="7938" max="7938" width="11.59765625" style="188" customWidth="1"/>
     <col min="7939" max="7939" width="4" style="188" customWidth="1"/>
-    <col min="7940" max="7943" width="17.25" style="188" customWidth="1"/>
-    <col min="7944" max="7944" width="6.75" style="188" customWidth="1"/>
-    <col min="7945" max="7945" width="8.75" style="188" customWidth="1"/>
+    <col min="7940" max="7943" width="17.19921875" style="188" customWidth="1"/>
+    <col min="7944" max="7944" width="6.69921875" style="188" customWidth="1"/>
+    <col min="7945" max="7945" width="8.69921875" style="188" customWidth="1"/>
     <col min="7946" max="7946" width="7" style="188" customWidth="1"/>
-    <col min="7947" max="7947" width="12.125" style="188" customWidth="1"/>
+    <col min="7947" max="7947" width="12.09765625" style="188" customWidth="1"/>
     <col min="7948" max="8189" width="7" style="188"/>
-    <col min="8190" max="8190" width="9.625" style="188" customWidth="1"/>
+    <col min="8190" max="8190" width="9.59765625" style="188" customWidth="1"/>
     <col min="8191" max="8191" width="4" style="188" customWidth="1"/>
-    <col min="8192" max="8192" width="11.25" style="188" customWidth="1"/>
+    <col min="8192" max="8192" width="11.19921875" style="188" customWidth="1"/>
     <col min="8193" max="8193" width="4" style="188" customWidth="1"/>
-    <col min="8194" max="8194" width="11.625" style="188" customWidth="1"/>
+    <col min="8194" max="8194" width="11.59765625" style="188" customWidth="1"/>
     <col min="8195" max="8195" width="4" style="188" customWidth="1"/>
-    <col min="8196" max="8199" width="17.25" style="188" customWidth="1"/>
-    <col min="8200" max="8200" width="6.75" style="188" customWidth="1"/>
-    <col min="8201" max="8201" width="8.75" style="188" customWidth="1"/>
+    <col min="8196" max="8199" width="17.19921875" style="188" customWidth="1"/>
+    <col min="8200" max="8200" width="6.69921875" style="188" customWidth="1"/>
+    <col min="8201" max="8201" width="8.69921875" style="188" customWidth="1"/>
     <col min="8202" max="8202" width="7" style="188" customWidth="1"/>
-    <col min="8203" max="8203" width="12.125" style="188" customWidth="1"/>
+    <col min="8203" max="8203" width="12.09765625" style="188" customWidth="1"/>
     <col min="8204" max="8445" width="7" style="188"/>
-    <col min="8446" max="8446" width="9.625" style="188" customWidth="1"/>
+    <col min="8446" max="8446" width="9.59765625" style="188" customWidth="1"/>
     <col min="8447" max="8447" width="4" style="188" customWidth="1"/>
-    <col min="8448" max="8448" width="11.25" style="188" customWidth="1"/>
+    <col min="8448" max="8448" width="11.19921875" style="188" customWidth="1"/>
     <col min="8449" max="8449" width="4" style="188" customWidth="1"/>
-    <col min="8450" max="8450" width="11.625" style="188" customWidth="1"/>
+    <col min="8450" max="8450" width="11.59765625" style="188" customWidth="1"/>
     <col min="8451" max="8451" width="4" style="188" customWidth="1"/>
-    <col min="8452" max="8455" width="17.25" style="188" customWidth="1"/>
-    <col min="8456" max="8456" width="6.75" style="188" customWidth="1"/>
-    <col min="8457" max="8457" width="8.75" style="188" customWidth="1"/>
+    <col min="8452" max="8455" width="17.19921875" style="188" customWidth="1"/>
+    <col min="8456" max="8456" width="6.69921875" style="188" customWidth="1"/>
+    <col min="8457" max="8457" width="8.69921875" style="188" customWidth="1"/>
     <col min="8458" max="8458" width="7" style="188" customWidth="1"/>
-    <col min="8459" max="8459" width="12.125" style="188" customWidth="1"/>
+    <col min="8459" max="8459" width="12.09765625" style="188" customWidth="1"/>
     <col min="8460" max="8701" width="7" style="188"/>
-    <col min="8702" max="8702" width="9.625" style="188" customWidth="1"/>
+    <col min="8702" max="8702" width="9.59765625" style="188" customWidth="1"/>
     <col min="8703" max="8703" width="4" style="188" customWidth="1"/>
-    <col min="8704" max="8704" width="11.25" style="188" customWidth="1"/>
+    <col min="8704" max="8704" width="11.19921875" style="188" customWidth="1"/>
     <col min="8705" max="8705" width="4" style="188" customWidth="1"/>
-    <col min="8706" max="8706" width="11.625" style="188" customWidth="1"/>
+    <col min="8706" max="8706" width="11.59765625" style="188" customWidth="1"/>
     <col min="8707" max="8707" width="4" style="188" customWidth="1"/>
-    <col min="8708" max="8711" width="17.25" style="188" customWidth="1"/>
-    <col min="8712" max="8712" width="6.75" style="188" customWidth="1"/>
-    <col min="8713" max="8713" width="8.75" style="188" customWidth="1"/>
+    <col min="8708" max="8711" width="17.19921875" style="188" customWidth="1"/>
+    <col min="8712" max="8712" width="6.69921875" style="188" customWidth="1"/>
+    <col min="8713" max="8713" width="8.69921875" style="188" customWidth="1"/>
     <col min="8714" max="8714" width="7" style="188" customWidth="1"/>
-    <col min="8715" max="8715" width="12.125" style="188" customWidth="1"/>
+    <col min="8715" max="8715" width="12.09765625" style="188" customWidth="1"/>
     <col min="8716" max="8957" width="7" style="188"/>
-    <col min="8958" max="8958" width="9.625" style="188" customWidth="1"/>
+    <col min="8958" max="8958" width="9.59765625" style="188" customWidth="1"/>
     <col min="8959" max="8959" width="4" style="188" customWidth="1"/>
-    <col min="8960" max="8960" width="11.25" style="188" customWidth="1"/>
+    <col min="8960" max="8960" width="11.19921875" style="188" customWidth="1"/>
     <col min="8961" max="8961" width="4" style="188" customWidth="1"/>
-    <col min="8962" max="8962" width="11.625" style="188" customWidth="1"/>
+    <col min="8962" max="8962" width="11.59765625" style="188" customWidth="1"/>
     <col min="8963" max="8963" width="4" style="188" customWidth="1"/>
-    <col min="8964" max="8967" width="17.25" style="188" customWidth="1"/>
-    <col min="8968" max="8968" width="6.75" style="188" customWidth="1"/>
-    <col min="8969" max="8969" width="8.75" style="188" customWidth="1"/>
+    <col min="8964" max="8967" width="17.19921875" style="188" customWidth="1"/>
+    <col min="8968" max="8968" width="6.69921875" style="188" customWidth="1"/>
+    <col min="8969" max="8969" width="8.69921875" style="188" customWidth="1"/>
     <col min="8970" max="8970" width="7" style="188" customWidth="1"/>
-    <col min="8971" max="8971" width="12.125" style="188" customWidth="1"/>
+    <col min="8971" max="8971" width="12.09765625" style="188" customWidth="1"/>
     <col min="8972" max="9213" width="7" style="188"/>
-    <col min="9214" max="9214" width="9.625" style="188" customWidth="1"/>
+    <col min="9214" max="9214" width="9.59765625" style="188" customWidth="1"/>
     <col min="9215" max="9215" width="4" style="188" customWidth="1"/>
-    <col min="9216" max="9216" width="11.25" style="188" customWidth="1"/>
+    <col min="9216" max="9216" width="11.19921875" style="188" customWidth="1"/>
     <col min="9217" max="9217" width="4" style="188" customWidth="1"/>
-    <col min="9218" max="9218" width="11.625" style="188" customWidth="1"/>
+    <col min="9218" max="9218" width="11.59765625" style="188" customWidth="1"/>
     <col min="9219" max="9219" width="4" style="188" customWidth="1"/>
-    <col min="9220" max="9223" width="17.25" style="188" customWidth="1"/>
-    <col min="9224" max="9224" width="6.75" style="188" customWidth="1"/>
-    <col min="9225" max="9225" width="8.75" style="188" customWidth="1"/>
+    <col min="9220" max="9223" width="17.19921875" style="188" customWidth="1"/>
+    <col min="9224" max="9224" width="6.69921875" style="188" customWidth="1"/>
+    <col min="9225" max="9225" width="8.69921875" style="188" customWidth="1"/>
     <col min="9226" max="9226" width="7" style="188" customWidth="1"/>
-    <col min="9227" max="9227" width="12.125" style="188" customWidth="1"/>
+    <col min="9227" max="9227" width="12.09765625" style="188" customWidth="1"/>
     <col min="9228" max="9469" width="7" style="188"/>
-    <col min="9470" max="9470" width="9.625" style="188" customWidth="1"/>
+    <col min="9470" max="9470" width="9.59765625" style="188" customWidth="1"/>
     <col min="9471" max="9471" width="4" style="188" customWidth="1"/>
-    <col min="9472" max="9472" width="11.25" style="188" customWidth="1"/>
+    <col min="9472" max="9472" width="11.19921875" style="188" customWidth="1"/>
     <col min="9473" max="9473" width="4" style="188" customWidth="1"/>
-    <col min="9474" max="9474" width="11.625" style="188" customWidth="1"/>
+    <col min="9474" max="9474" width="11.59765625" style="188" customWidth="1"/>
     <col min="9475" max="9475" width="4" style="188" customWidth="1"/>
-    <col min="9476" max="9479" width="17.25" style="188" customWidth="1"/>
-    <col min="9480" max="9480" width="6.75" style="188" customWidth="1"/>
-    <col min="9481" max="9481" width="8.75" style="188" customWidth="1"/>
+    <col min="9476" max="9479" width="17.19921875" style="188" customWidth="1"/>
+    <col min="9480" max="9480" width="6.69921875" style="188" customWidth="1"/>
+    <col min="9481" max="9481" width="8.69921875" style="188" customWidth="1"/>
     <col min="9482" max="9482" width="7" style="188" customWidth="1"/>
-    <col min="9483" max="9483" width="12.125" style="188" customWidth="1"/>
+    <col min="9483" max="9483" width="12.09765625" style="188" customWidth="1"/>
     <col min="9484" max="9725" width="7" style="188"/>
-    <col min="9726" max="9726" width="9.625" style="188" customWidth="1"/>
+    <col min="9726" max="9726" width="9.59765625" style="188" customWidth="1"/>
     <col min="9727" max="9727" width="4" style="188" customWidth="1"/>
-    <col min="9728" max="9728" width="11.25" style="188" customWidth="1"/>
+    <col min="9728" max="9728" width="11.19921875" style="188" customWidth="1"/>
     <col min="9729" max="9729" width="4" style="188" customWidth="1"/>
-    <col min="9730" max="9730" width="11.625" style="188" customWidth="1"/>
+    <col min="9730" max="9730" width="11.59765625" style="188" customWidth="1"/>
     <col min="9731" max="9731" width="4" style="188" customWidth="1"/>
-    <col min="9732" max="9735" width="17.25" style="188" customWidth="1"/>
-    <col min="9736" max="9736" width="6.75" style="188" customWidth="1"/>
-    <col min="9737" max="9737" width="8.75" style="188" customWidth="1"/>
+    <col min="9732" max="9735" width="17.19921875" style="188" customWidth="1"/>
+    <col min="9736" max="9736" width="6.69921875" style="188" customWidth="1"/>
+    <col min="9737" max="9737" width="8.69921875" style="188" customWidth="1"/>
     <col min="9738" max="9738" width="7" style="188" customWidth="1"/>
-    <col min="9739" max="9739" width="12.125" style="188" customWidth="1"/>
+    <col min="9739" max="9739" width="12.09765625" style="188" customWidth="1"/>
     <col min="9740" max="9981" width="7" style="188"/>
-    <col min="9982" max="9982" width="9.625" style="188" customWidth="1"/>
+    <col min="9982" max="9982" width="9.59765625" style="188" customWidth="1"/>
     <col min="9983" max="9983" width="4" style="188" customWidth="1"/>
-    <col min="9984" max="9984" width="11.25" style="188" customWidth="1"/>
+    <col min="9984" max="9984" width="11.19921875" style="188" customWidth="1"/>
     <col min="9985" max="9985" width="4" style="188" customWidth="1"/>
-    <col min="9986" max="9986" width="11.625" style="188" customWidth="1"/>
+    <col min="9986" max="9986" width="11.59765625" style="188" customWidth="1"/>
     <col min="9987" max="9987" width="4" style="188" customWidth="1"/>
-    <col min="9988" max="9991" width="17.25" style="188" customWidth="1"/>
-    <col min="9992" max="9992" width="6.75" style="188" customWidth="1"/>
-    <col min="9993" max="9993" width="8.75" style="188" customWidth="1"/>
+    <col min="9988" max="9991" width="17.19921875" style="188" customWidth="1"/>
+    <col min="9992" max="9992" width="6.69921875" style="188" customWidth="1"/>
+    <col min="9993" max="9993" width="8.69921875" style="188" customWidth="1"/>
     <col min="9994" max="9994" width="7" style="188" customWidth="1"/>
-    <col min="9995" max="9995" width="12.125" style="188" customWidth="1"/>
+    <col min="9995" max="9995" width="12.09765625" style="188" customWidth="1"/>
     <col min="9996" max="10237" width="7" style="188"/>
-    <col min="10238" max="10238" width="9.625" style="188" customWidth="1"/>
+    <col min="10238" max="10238" width="9.59765625" style="188" customWidth="1"/>
     <col min="10239" max="10239" width="4" style="188" customWidth="1"/>
-    <col min="10240" max="10240" width="11.25" style="188" customWidth="1"/>
+    <col min="10240" max="10240" width="11.19921875" style="188" customWidth="1"/>
     <col min="10241" max="10241" width="4" style="188" customWidth="1"/>
-    <col min="10242" max="10242" width="11.625" style="188" customWidth="1"/>
+    <col min="10242" max="10242" width="11.59765625" style="188" customWidth="1"/>
     <col min="10243" max="10243" width="4" style="188" customWidth="1"/>
-    <col min="10244" max="10247" width="17.25" style="188" customWidth="1"/>
-    <col min="10248" max="10248" width="6.75" style="188" customWidth="1"/>
-    <col min="10249" max="10249" width="8.75" style="188" customWidth="1"/>
+    <col min="10244" max="10247" width="17.19921875" style="188" customWidth="1"/>
+    <col min="10248" max="10248" width="6.69921875" style="188" customWidth="1"/>
+    <col min="10249" max="10249" width="8.69921875" style="188" customWidth="1"/>
     <col min="10250" max="10250" width="7" style="188" customWidth="1"/>
-    <col min="10251" max="10251" width="12.125" style="188" customWidth="1"/>
+    <col min="10251" max="10251" width="12.09765625" style="188" customWidth="1"/>
     <col min="10252" max="10493" width="7" style="188"/>
-    <col min="10494" max="10494" width="9.625" style="188" customWidth="1"/>
+    <col min="10494" max="10494" width="9.59765625" style="188" customWidth="1"/>
     <col min="10495" max="10495" width="4" style="188" customWidth="1"/>
-    <col min="10496" max="10496" width="11.25" style="188" customWidth="1"/>
+    <col min="10496" max="10496" width="11.19921875" style="188" customWidth="1"/>
     <col min="10497" max="10497" width="4" style="188" customWidth="1"/>
-    <col min="10498" max="10498" width="11.625" style="188" customWidth="1"/>
+    <col min="10498" max="10498" width="11.59765625" style="188" customWidth="1"/>
     <col min="10499" max="10499" width="4" style="188" customWidth="1"/>
-    <col min="10500" max="10503" width="17.25" style="188" customWidth="1"/>
-    <col min="10504" max="10504" width="6.75" style="188" customWidth="1"/>
-    <col min="10505" max="10505" width="8.75" style="188" customWidth="1"/>
+    <col min="10500" max="10503" width="17.19921875" style="188" customWidth="1"/>
+    <col min="10504" max="10504" width="6.69921875" style="188" customWidth="1"/>
+    <col min="10505" max="10505" width="8.69921875" style="188" customWidth="1"/>
     <col min="10506" max="10506" width="7" style="188" customWidth="1"/>
-    <col min="10507" max="10507" width="12.125" style="188" customWidth="1"/>
+    <col min="10507" max="10507" width="12.09765625" style="188" customWidth="1"/>
     <col min="10508" max="10749" width="7" style="188"/>
-    <col min="10750" max="10750" width="9.625" style="188" customWidth="1"/>
+    <col min="10750" max="10750" width="9.59765625" style="188" customWidth="1"/>
     <col min="10751" max="10751" width="4" style="188" customWidth="1"/>
-    <col min="10752" max="10752" width="11.25" style="188" customWidth="1"/>
+    <col min="10752" max="10752" width="11.19921875" style="188" customWidth="1"/>
     <col min="10753" max="10753" width="4" style="188" customWidth="1"/>
-    <col min="10754" max="10754" width="11.625" style="188" customWidth="1"/>
+    <col min="10754" max="10754" width="11.59765625" style="188" customWidth="1"/>
     <col min="10755" max="10755" width="4" style="188" customWidth="1"/>
-    <col min="10756" max="10759" width="17.25" style="188" customWidth="1"/>
-    <col min="10760" max="10760" width="6.75" style="188" customWidth="1"/>
-    <col min="10761" max="10761" width="8.75" style="188" customWidth="1"/>
+    <col min="10756" max="10759" width="17.19921875" style="188" customWidth="1"/>
+    <col min="10760" max="10760" width="6.69921875" style="188" customWidth="1"/>
+    <col min="10761" max="10761" width="8.69921875" style="188" customWidth="1"/>
     <col min="10762" max="10762" width="7" style="188" customWidth="1"/>
-    <col min="10763" max="10763" width="12.125" style="188" customWidth="1"/>
+    <col min="10763" max="10763" width="12.09765625" style="188" customWidth="1"/>
     <col min="10764" max="11005" width="7" style="188"/>
-    <col min="11006" max="11006" width="9.625" style="188" customWidth="1"/>
+    <col min="11006" max="11006" width="9.59765625" style="188" customWidth="1"/>
     <col min="11007" max="11007" width="4" style="188" customWidth="1"/>
-    <col min="11008" max="11008" width="11.25" style="188" customWidth="1"/>
+    <col min="11008" max="11008" width="11.19921875" style="188" customWidth="1"/>
     <col min="11009" max="11009" width="4" style="188" customWidth="1"/>
-    <col min="11010" max="11010" width="11.625" style="188" customWidth="1"/>
+    <col min="11010" max="11010" width="11.59765625" style="188" customWidth="1"/>
     <col min="11011" max="11011" width="4" style="188" customWidth="1"/>
-    <col min="11012" max="11015" width="17.25" style="188" customWidth="1"/>
-    <col min="11016" max="11016" width="6.75" style="188" customWidth="1"/>
-    <col min="11017" max="11017" width="8.75" style="188" customWidth="1"/>
+    <col min="11012" max="11015" width="17.19921875" style="188" customWidth="1"/>
+    <col min="11016" max="11016" width="6.69921875" style="188" customWidth="1"/>
+    <col min="11017" max="11017" width="8.69921875" style="188" customWidth="1"/>
     <col min="11018" max="11018" width="7" style="188" customWidth="1"/>
-    <col min="11019" max="11019" width="12.125" style="188" customWidth="1"/>
+    <col min="11019" max="11019" width="12.09765625" style="188" customWidth="1"/>
     <col min="11020" max="11261" width="7" style="188"/>
-    <col min="11262" max="11262" width="9.625" style="188" customWidth="1"/>
+    <col min="11262" max="11262" width="9.59765625" style="188" customWidth="1"/>
     <col min="11263" max="11263" width="4" style="188" customWidth="1"/>
-    <col min="11264" max="11264" width="11.25" style="188" customWidth="1"/>
+    <col min="11264" max="11264" width="11.19921875" style="188" customWidth="1"/>
     <col min="11265" max="11265" width="4" style="188" customWidth="1"/>
-    <col min="11266" max="11266" width="11.625" style="188" customWidth="1"/>
+    <col min="11266" max="11266" width="11.59765625" style="188" customWidth="1"/>
     <col min="11267" max="11267" width="4" style="188" customWidth="1"/>
-    <col min="11268" max="11271" width="17.25" style="188" customWidth="1"/>
-    <col min="11272" max="11272" width="6.75" style="188" customWidth="1"/>
-    <col min="11273" max="11273" width="8.75" style="188" customWidth="1"/>
+    <col min="11268" max="11271" width="17.19921875" style="188" customWidth="1"/>
+    <col min="11272" max="11272" width="6.69921875" style="188" customWidth="1"/>
+    <col min="11273" max="11273" width="8.69921875" style="188" customWidth="1"/>
     <col min="11274" max="11274" width="7" style="188" customWidth="1"/>
-    <col min="11275" max="11275" width="12.125" style="188" customWidth="1"/>
+    <col min="11275" max="11275" width="12.09765625" style="188" customWidth="1"/>
     <col min="11276" max="11517" width="7" style="188"/>
-    <col min="11518" max="11518" width="9.625" style="188" customWidth="1"/>
+    <col min="11518" max="11518" width="9.59765625" style="188" customWidth="1"/>
     <col min="11519" max="11519" width="4" style="188" customWidth="1"/>
-    <col min="11520" max="11520" width="11.25" style="188" customWidth="1"/>
+    <col min="11520" max="11520" width="11.19921875" style="188" customWidth="1"/>
     <col min="11521" max="11521" width="4" style="188" customWidth="1"/>
-    <col min="11522" max="11522" width="11.625" style="188" customWidth="1"/>
+    <col min="11522" max="11522" width="11.59765625" style="188" customWidth="1"/>
     <col min="11523" max="11523" width="4" style="188" customWidth="1"/>
-    <col min="11524" max="11527" width="17.25" style="188" customWidth="1"/>
-    <col min="11528" max="11528" width="6.75" style="188" customWidth="1"/>
-    <col min="11529" max="11529" width="8.75" style="188" customWidth="1"/>
+    <col min="11524" max="11527" width="17.19921875" style="188" customWidth="1"/>
+    <col min="11528" max="11528" width="6.69921875" style="188" customWidth="1"/>
+    <col min="11529" max="11529" width="8.69921875" style="188" customWidth="1"/>
     <col min="11530" max="11530" width="7" style="188" customWidth="1"/>
-    <col min="11531" max="11531" width="12.125" style="188" customWidth="1"/>
+    <col min="11531" max="11531" width="12.09765625" style="188" customWidth="1"/>
     <col min="11532" max="11773" width="7" style="188"/>
-    <col min="11774" max="11774" width="9.625" style="188" customWidth="1"/>
+    <col min="11774" max="11774" width="9.59765625" style="188" customWidth="1"/>
     <col min="11775" max="11775" width="4" style="188" customWidth="1"/>
-    <col min="11776" max="11776" width="11.25" style="188" customWidth="1"/>
+    <col min="11776" max="11776" width="11.19921875" style="188" customWidth="1"/>
     <col min="11777" max="11777" width="4" style="188" customWidth="1"/>
-    <col min="11778" max="11778" width="11.625" style="188" customWidth="1"/>
+    <col min="11778" max="11778" width="11.59765625" style="188" customWidth="1"/>
     <col min="11779" max="11779" width="4" style="188" customWidth="1"/>
-    <col min="11780" max="11783" width="17.25" style="188" customWidth="1"/>
-    <col min="11784" max="11784" width="6.75" style="188" customWidth="1"/>
-    <col min="11785" max="11785" width="8.75" style="188" customWidth="1"/>
+    <col min="11780" max="11783" width="17.19921875" style="188" customWidth="1"/>
+    <col min="11784" max="11784" width="6.69921875" style="188" customWidth="1"/>
+    <col min="11785" max="11785" width="8.69921875" style="188" customWidth="1"/>
     <col min="11786" max="11786" width="7" style="188" customWidth="1"/>
-    <col min="11787" max="11787" width="12.125" style="188" customWidth="1"/>
+    <col min="11787" max="11787" width="12.09765625" style="188" customWidth="1"/>
     <col min="11788" max="12029" width="7" style="188"/>
-    <col min="12030" max="12030" width="9.625" style="188" customWidth="1"/>
+    <col min="12030" max="12030" width="9.59765625" style="188" customWidth="1"/>
     <col min="12031" max="12031" width="4" style="188" customWidth="1"/>
-    <col min="12032" max="12032" width="11.25" style="188" customWidth="1"/>
+    <col min="12032" max="12032" width="11.19921875" style="188" customWidth="1"/>
     <col min="12033" max="12033" width="4" style="188" customWidth="1"/>
-    <col min="12034" max="12034" width="11.625" style="188" customWidth="1"/>
+    <col min="12034" max="12034" width="11.59765625" style="188" customWidth="1"/>
     <col min="12035" max="12035" width="4" style="188" customWidth="1"/>
-    <col min="12036" max="12039" width="17.25" style="188" customWidth="1"/>
-    <col min="12040" max="12040" width="6.75" style="188" customWidth="1"/>
-    <col min="12041" max="12041" width="8.75" style="188" customWidth="1"/>
+    <col min="12036" max="12039" width="17.19921875" style="188" customWidth="1"/>
+    <col min="12040" max="12040" width="6.69921875" style="188" customWidth="1"/>
+    <col min="12041" max="12041" width="8.69921875" style="188" customWidth="1"/>
     <col min="12042" max="12042" width="7" style="188" customWidth="1"/>
-    <col min="12043" max="12043" width="12.125" style="188" customWidth="1"/>
+    <col min="12043" max="12043" width="12.09765625" style="188" customWidth="1"/>
     <col min="12044" max="12285" width="7" style="188"/>
-    <col min="12286" max="12286" width="9.625" style="188" customWidth="1"/>
+    <col min="12286" max="12286" width="9.59765625" style="188" customWidth="1"/>
     <col min="12287" max="12287" width="4" style="188" customWidth="1"/>
-    <col min="12288" max="12288" width="11.25" style="188" customWidth="1"/>
+    <col min="12288" max="12288" width="11.19921875" style="188" customWidth="1"/>
     <col min="12289" max="12289" width="4" style="188" customWidth="1"/>
-    <col min="12290" max="12290" width="11.625" style="188" customWidth="1"/>
+    <col min="12290" max="12290" width="11.59765625" style="188" customWidth="1"/>
     <col min="12291" max="12291" width="4" style="188" customWidth="1"/>
-    <col min="12292" max="12295" width="17.25" style="188" customWidth="1"/>
-    <col min="12296" max="12296" width="6.75" style="188" customWidth="1"/>
-    <col min="12297" max="12297" width="8.75" style="188" customWidth="1"/>
+    <col min="12292" max="12295" width="17.19921875" style="188" customWidth="1"/>
+    <col min="12296" max="12296" width="6.69921875" style="188" customWidth="1"/>
+    <col min="12297" max="12297" width="8.69921875" style="188" customWidth="1"/>
     <col min="12298" max="12298" width="7" style="188" customWidth="1"/>
-    <col min="12299" max="12299" width="12.125" style="188" customWidth="1"/>
+    <col min="12299" max="12299" width="12.09765625" style="188" customWidth="1"/>
     <col min="12300" max="12541" width="7" style="188"/>
-    <col min="12542" max="12542" width="9.625" style="188" customWidth="1"/>
+    <col min="12542" max="12542" width="9.59765625" style="188" customWidth="1"/>
     <col min="12543" max="12543" width="4" style="188" customWidth="1"/>
-    <col min="12544" max="12544" width="11.25" style="188" customWidth="1"/>
+    <col min="12544" max="12544" width="11.19921875" style="188" customWidth="1"/>
     <col min="12545" max="12545" width="4" style="188" customWidth="1"/>
-    <col min="12546" max="12546" width="11.625" style="188" customWidth="1"/>
+    <col min="12546" max="12546" width="11.59765625" style="188" customWidth="1"/>
     <col min="12547" max="12547" width="4" style="188" customWidth="1"/>
-    <col min="12548" max="12551" width="17.25" style="188" customWidth="1"/>
-    <col min="12552" max="12552" width="6.75" style="188" customWidth="1"/>
-    <col min="12553" max="12553" width="8.75" style="188" customWidth="1"/>
+    <col min="12548" max="12551" width="17.19921875" style="188" customWidth="1"/>
+    <col min="12552" max="12552" width="6.69921875" style="188" customWidth="1"/>
+    <col min="12553" max="12553" width="8.69921875" style="188" customWidth="1"/>
     <col min="12554" max="12554" width="7" style="188" customWidth="1"/>
-    <col min="12555" max="12555" width="12.125" style="188" customWidth="1"/>
+    <col min="12555" max="12555" width="12.09765625" style="188" customWidth="1"/>
     <col min="12556" max="12797" width="7" style="188"/>
-    <col min="12798" max="12798" width="9.625" style="188" customWidth="1"/>
+    <col min="12798" max="12798" width="9.59765625" style="188" customWidth="1"/>
     <col min="12799" max="12799" width="4" style="188" customWidth="1"/>
-    <col min="12800" max="12800" width="11.25" style="188" customWidth="1"/>
+    <col min="12800" max="12800" width="11.19921875" style="188" customWidth="1"/>
     <col min="12801" max="12801" width="4" style="188" customWidth="1"/>
-    <col min="12802" max="12802" width="11.625" style="188" customWidth="1"/>
+    <col min="12802" max="12802" width="11.59765625" style="188" customWidth="1"/>
     <col min="12803" max="12803" width="4" style="188" customWidth="1"/>
-    <col min="12804" max="12807" width="17.25" style="188" customWidth="1"/>
-    <col min="12808" max="12808" width="6.75" style="188" customWidth="1"/>
-    <col min="12809" max="12809" width="8.75" style="188" customWidth="1"/>
+    <col min="12804" max="12807" width="17.19921875" style="188" customWidth="1"/>
+    <col min="12808" max="12808" width="6.69921875" style="188" customWidth="1"/>
+    <col min="12809" max="12809" width="8.69921875" style="188" customWidth="1"/>
     <col min="12810" max="12810" width="7" style="188" customWidth="1"/>
-    <col min="12811" max="12811" width="12.125" style="188" customWidth="1"/>
+    <col min="12811" max="12811" width="12.09765625" style="188" customWidth="1"/>
     <col min="12812" max="13053" width="7" style="188"/>
-    <col min="13054" max="13054" width="9.625" style="188" customWidth="1"/>
+    <col min="13054" max="13054" width="9.59765625" style="188" customWidth="1"/>
     <col min="13055" max="13055" width="4" style="188" customWidth="1"/>
-    <col min="13056" max="13056" width="11.25" style="188" customWidth="1"/>
+    <col min="13056" max="13056" width="11.19921875" style="188" customWidth="1"/>
     <col min="13057" max="13057" width="4" style="188" customWidth="1"/>
-    <col min="13058" max="13058" width="11.625" style="188" customWidth="1"/>
+    <col min="13058" max="13058" width="11.59765625" style="188" customWidth="1"/>
     <col min="13059" max="13059" width="4" style="188" customWidth="1"/>
-    <col min="13060" max="13063" width="17.25" style="188" customWidth="1"/>
-    <col min="13064" max="13064" width="6.75" style="188" customWidth="1"/>
-    <col min="13065" max="13065" width="8.75" style="188" customWidth="1"/>
+    <col min="13060" max="13063" width="17.19921875" style="188" customWidth="1"/>
+    <col min="13064" max="13064" width="6.69921875" style="188" customWidth="1"/>
+    <col min="13065" max="13065" width="8.69921875" style="188" customWidth="1"/>
     <col min="13066" max="13066" width="7" style="188" customWidth="1"/>
-    <col min="13067" max="13067" width="12.125" style="188" customWidth="1"/>
+    <col min="13067" max="13067" width="12.09765625" style="188" customWidth="1"/>
     <col min="13068" max="13309" width="7" style="188"/>
-    <col min="13310" max="13310" width="9.625" style="188" customWidth="1"/>
+    <col min="13310" max="13310" width="9.59765625" style="188" customWidth="1"/>
     <col min="13311" max="13311" width="4" style="188" customWidth="1"/>
-    <col min="13312" max="13312" width="11.25" style="188" customWidth="1"/>
+    <col min="13312" max="13312" width="11.19921875" style="188" customWidth="1"/>
     <col min="13313" max="13313" width="4" style="188" customWidth="1"/>
-    <col min="13314" max="13314" width="11.625" style="188" customWidth="1"/>
+    <col min="13314" max="13314" width="11.59765625" style="188" customWidth="1"/>
     <col min="13315" max="13315" width="4" style="188" customWidth="1"/>
-    <col min="13316" max="13319" width="17.25" style="188" customWidth="1"/>
-    <col min="13320" max="13320" width="6.75" style="188" customWidth="1"/>
-    <col min="13321" max="13321" width="8.75" style="188" customWidth="1"/>
+    <col min="13316" max="13319" width="17.19921875" style="188" customWidth="1"/>
+    <col min="13320" max="13320" width="6.69921875" style="188" customWidth="1"/>
+    <col min="13321" max="13321" width="8.69921875" style="188" customWidth="1"/>
     <col min="13322" max="13322" width="7" style="188" customWidth="1"/>
-    <col min="13323" max="13323" width="12.125" style="188" customWidth="1"/>
+    <col min="13323" max="13323" width="12.09765625" style="188" customWidth="1"/>
     <col min="13324" max="13565" width="7" style="188"/>
-    <col min="13566" max="13566" width="9.625" style="188" customWidth="1"/>
+    <col min="13566" max="13566" width="9.59765625" style="188" customWidth="1"/>
     <col min="13567" max="13567" width="4" style="188" customWidth="1"/>
-    <col min="13568" max="13568" width="11.25" style="188" customWidth="1"/>
+    <col min="13568" max="13568" width="11.19921875" style="188" customWidth="1"/>
     <col min="13569" max="13569" width="4" style="188" customWidth="1"/>
-    <col min="13570" max="13570" width="11.625" style="188" customWidth="1"/>
+    <col min="13570" max="13570" width="11.59765625" style="188" customWidth="1"/>
     <col min="13571" max="13571" width="4" style="188" customWidth="1"/>
-    <col min="13572" max="13575" width="17.25" style="188" customWidth="1"/>
-    <col min="13576" max="13576" width="6.75" style="188" customWidth="1"/>
-    <col min="13577" max="13577" width="8.75" style="188" customWidth="1"/>
+    <col min="13572" max="13575" width="17.19921875" style="188" customWidth="1"/>
+    <col min="13576" max="13576" width="6.69921875" style="188" customWidth="1"/>
+    <col min="13577" max="13577" width="8.69921875" style="188" customWidth="1"/>
     <col min="13578" max="13578" width="7" style="188" customWidth="1"/>
-    <col min="13579" max="13579" width="12.125" style="188" customWidth="1"/>
+    <col min="13579" max="13579" width="12.09765625" style="188" customWidth="1"/>
     <col min="13580" max="13821" width="7" style="188"/>
-    <col min="13822" max="13822" width="9.625" style="188" customWidth="1"/>
+    <col min="13822" max="13822" width="9.59765625" style="188" customWidth="1"/>
     <col min="13823" max="13823" width="4" style="188" customWidth="1"/>
-    <col min="13824" max="13824" width="11.25" style="188" customWidth="1"/>
+    <col min="13824" max="13824" width="11.19921875" style="188" customWidth="1"/>
     <col min="13825" max="13825" width="4" style="188" customWidth="1"/>
-    <col min="13826" max="13826" width="11.625" style="188" customWidth="1"/>
+    <col min="13826" max="13826" width="11.59765625" style="188" customWidth="1"/>
     <col min="13827" max="13827" width="4" style="188" customWidth="1"/>
-    <col min="13828" max="13831" width="17.25" style="188" customWidth="1"/>
-    <col min="13832" max="13832" width="6.75" style="188" customWidth="1"/>
-    <col min="13833" max="13833" width="8.75" style="188" customWidth="1"/>
+    <col min="13828" max="13831" width="17.19921875" style="188" customWidth="1"/>
+    <col min="13832" max="13832" width="6.69921875" style="188" customWidth="1"/>
+    <col min="13833" max="13833" width="8.69921875" style="188" customWidth="1"/>
     <col min="13834" max="13834" width="7" style="188" customWidth="1"/>
-    <col min="13835" max="13835" width="12.125" style="188" customWidth="1"/>
+    <col min="13835" max="13835" width="12.09765625" style="188" customWidth="1"/>
     <col min="13836" max="14077" width="7" style="188"/>
-    <col min="14078" max="14078" width="9.625" style="188" customWidth="1"/>
+    <col min="14078" max="14078" width="9.59765625" style="188" customWidth="1"/>
     <col min="14079" max="14079" width="4" style="188" customWidth="1"/>
-    <col min="14080" max="14080" width="11.25" style="188" customWidth="1"/>
+    <col min="14080" max="14080" width="11.19921875" style="188" customWidth="1"/>
     <col min="14081" max="14081" width="4" style="188" customWidth="1"/>
-    <col min="14082" max="14082" width="11.625" style="188" customWidth="1"/>
+    <col min="14082" max="14082" width="11.59765625" style="188" customWidth="1"/>
     <col min="14083" max="14083" width="4" style="188" customWidth="1"/>
-    <col min="14084" max="14087" width="17.25" style="188" customWidth="1"/>
-    <col min="14088" max="14088" width="6.75" style="188" customWidth="1"/>
-    <col min="14089" max="14089" width="8.75" style="188" customWidth="1"/>
+    <col min="14084" max="14087" width="17.19921875" style="188" customWidth="1"/>
+    <col min="14088" max="14088" width="6.69921875" style="188" customWidth="1"/>
+    <col min="14089" max="14089" width="8.69921875" style="188" customWidth="1"/>
     <col min="14090" max="14090" width="7" style="188" customWidth="1"/>
-    <col min="14091" max="14091" width="12.125" style="188" customWidth="1"/>
+    <col min="14091" max="14091" width="12.09765625" style="188" customWidth="1"/>
     <col min="14092" max="14333" width="7" style="188"/>
-    <col min="14334" max="14334" width="9.625" style="188" customWidth="1"/>
+    <col min="14334" max="14334" width="9.59765625" style="188" customWidth="1"/>
     <col min="14335" max="14335" width="4" style="188" customWidth="1"/>
-    <col min="14336" max="14336" width="11.25" style="188" customWidth="1"/>
+    <col min="14336" max="14336" width="11.19921875" style="188" customWidth="1"/>
     <col min="14337" max="14337" width="4" style="188" customWidth="1"/>
-    <col min="14338" max="14338" width="11.625" style="188" customWidth="1"/>
+    <col min="14338" max="14338" width="11.59765625" style="188" customWidth="1"/>
     <col min="14339" max="14339" width="4" style="188" customWidth="1"/>
-    <col min="14340" max="14343" width="17.25" style="188" customWidth="1"/>
-    <col min="14344" max="14344" width="6.75" style="188" customWidth="1"/>
-    <col min="14345" max="14345" width="8.75" style="188" customWidth="1"/>
+    <col min="14340" max="14343" width="17.19921875" style="188" customWidth="1"/>
+    <col min="14344" max="14344" width="6.69921875" style="188" customWidth="1"/>
+    <col min="14345" max="14345" width="8.69921875" style="188" customWidth="1"/>
     <col min="14346" max="14346" width="7" style="188" customWidth="1"/>
-    <col min="14347" max="14347" width="12.125" style="188" customWidth="1"/>
+    <col min="14347" max="14347" width="12.09765625" style="188" customWidth="1"/>
     <col min="14348" max="14589" width="7" style="188"/>
-    <col min="14590" max="14590" width="9.625" style="188" customWidth="1"/>
+    <col min="14590" max="14590" width="9.59765625" style="188" customWidth="1"/>
     <col min="14591" max="14591" width="4" style="188" customWidth="1"/>
-    <col min="14592" max="14592" width="11.25" style="188" customWidth="1"/>
+    <col min="14592" max="14592" width="11.19921875" style="188" customWidth="1"/>
     <col min="14593" max="14593" width="4" style="188" customWidth="1"/>
-    <col min="14594" max="14594" width="11.625" style="188" customWidth="1"/>
+    <col min="14594" max="14594" width="11.59765625" style="188" customWidth="1"/>
     <col min="14595" max="14595" width="4" style="188" customWidth="1"/>
-    <col min="14596" max="14599" width="17.25" style="188" customWidth="1"/>
-    <col min="14600" max="14600" width="6.75" style="188" customWidth="1"/>
-    <col min="14601" max="14601" width="8.75" style="188" customWidth="1"/>
+    <col min="14596" max="14599" width="17.19921875" style="188" customWidth="1"/>
+    <col min="14600" max="14600" width="6.69921875" style="188" customWidth="1"/>
+    <col min="14601" max="14601" width="8.69921875" style="188" customWidth="1"/>
     <col min="14602" max="14602" width="7" style="188" customWidth="1"/>
-    <col min="14603" max="14603" width="12.125" style="188" customWidth="1"/>
+    <col min="14603" max="14603" width="12.09765625" style="188" customWidth="1"/>
     <col min="14604" max="14845" width="7" style="188"/>
-    <col min="14846" max="14846" width="9.625" style="188" customWidth="1"/>
+    <col min="14846" max="14846" width="9.59765625" style="188" customWidth="1"/>
     <col min="14847" max="14847" width="4" style="188" customWidth="1"/>
-    <col min="14848" max="14848" width="11.25" style="188" customWidth="1"/>
+    <col min="14848" max="14848" width="11.19921875" style="188" customWidth="1"/>
     <col min="14849" max="14849" width="4" style="188" customWidth="1"/>
-    <col min="14850" max="14850" width="11.625" style="188" customWidth="1"/>
+    <col min="14850" max="14850" width="11.59765625" style="188" customWidth="1"/>
     <col min="14851" max="14851" width="4" style="188" customWidth="1"/>
-    <col min="14852" max="14855" width="17.25" style="188" customWidth="1"/>
-    <col min="14856" max="14856" width="6.75" style="188" customWidth="1"/>
-    <col min="14857" max="14857" width="8.75" style="188" customWidth="1"/>
+    <col min="14852" max="14855" width="17.19921875" style="188" customWidth="1"/>
+    <col min="14856" max="14856" width="6.69921875" style="188" customWidth="1"/>
+    <col min="14857" max="14857" width="8.69921875" style="188" customWidth="1"/>
     <col min="14858" max="14858" width="7" style="188" customWidth="1"/>
-    <col min="14859" max="14859" width="12.125" style="188" customWidth="1"/>
+    <col min="14859" max="14859" width="12.09765625" style="188" customWidth="1"/>
     <col min="14860" max="15101" width="7" style="188"/>
-    <col min="15102" max="15102" width="9.625" style="188" customWidth="1"/>
+    <col min="15102" max="15102" width="9.59765625" style="188" customWidth="1"/>
     <col min="15103" max="15103" width="4" style="188" customWidth="1"/>
-    <col min="15104" max="15104" width="11.25" style="188" customWidth="1"/>
+    <col min="15104" max="15104" width="11.19921875" style="188" customWidth="1"/>
     <col min="15105" max="15105" width="4" style="188" customWidth="1"/>
-    <col min="15106" max="15106" width="11.625" style="188" customWidth="1"/>
+    <col min="15106" max="15106" width="11.59765625" style="188" customWidth="1"/>
     <col min="15107" max="15107" width="4" style="188" customWidth="1"/>
-    <col min="15108" max="15111" width="17.25" style="188" customWidth="1"/>
-    <col min="15112" max="15112" width="6.75" style="188" customWidth="1"/>
-    <col min="15113" max="15113" width="8.75" style="188" customWidth="1"/>
+    <col min="15108" max="15111" width="17.19921875" style="188" customWidth="1"/>
+    <col min="15112" max="15112" width="6.69921875" style="188" customWidth="1"/>
+    <col min="15113" max="15113" width="8.69921875" style="188" customWidth="1"/>
     <col min="15114" max="15114" width="7" style="188" customWidth="1"/>
-    <col min="15115" max="15115" width="12.125" style="188" customWidth="1"/>
+    <col min="15115" max="15115" width="12.09765625" style="188" customWidth="1"/>
     <col min="15116" max="15357" width="7" style="188"/>
-    <col min="15358" max="15358" width="9.625" style="188" customWidth="1"/>
+    <col min="15358" max="15358" width="9.59765625" style="188" customWidth="1"/>
     <col min="15359" max="15359" width="4" style="188" customWidth="1"/>
-    <col min="15360" max="15360" width="11.25" style="188" customWidth="1"/>
+    <col min="15360" max="15360" width="11.19921875" style="188" customWidth="1"/>
     <col min="15361" max="15361" width="4" style="188" customWidth="1"/>
-    <col min="15362" max="15362" width="11.625" style="188" customWidth="1"/>
+    <col min="15362" max="15362" width="11.59765625" style="188" customWidth="1"/>
     <col min="15363" max="15363" width="4" style="188" customWidth="1"/>
-    <col min="15364" max="15367" width="17.25" style="188" customWidth="1"/>
-    <col min="15368" max="15368" width="6.75" style="188" customWidth="1"/>
-    <col min="15369" max="15369" width="8.75" style="188" customWidth="1"/>
+    <col min="15364" max="15367" width="17.19921875" style="188" customWidth="1"/>
+    <col min="15368" max="15368" width="6.69921875" style="188" customWidth="1"/>
+    <col min="15369" max="15369" width="8.69921875" style="188" customWidth="1"/>
     <col min="15370" max="15370" width="7" style="188" customWidth="1"/>
-    <col min="15371" max="15371" width="12.125" style="188" customWidth="1"/>
+    <col min="15371" max="15371" width="12.09765625" style="188" customWidth="1"/>
     <col min="15372" max="15613" width="7" style="188"/>
-    <col min="15614" max="15614" width="9.625" style="188" customWidth="1"/>
+    <col min="15614" max="15614" width="9.59765625" style="188" customWidth="1"/>
     <col min="15615" max="15615" width="4" style="188" customWidth="1"/>
-    <col min="15616" max="15616" width="11.25" style="188" customWidth="1"/>
+    <col min="15616" max="15616" width="11.19921875" style="188" customWidth="1"/>
     <col min="15617" max="15617" width="4" style="188" customWidth="1"/>
-    <col min="15618" max="15618" width="11.625" style="188" customWidth="1"/>
+    <col min="15618" max="15618" width="11.59765625" style="188" customWidth="1"/>
     <col min="15619" max="15619" width="4" style="188" customWidth="1"/>
-    <col min="15620" max="15623" width="17.25" style="188" customWidth="1"/>
-    <col min="15624" max="15624" width="6.75" style="188" customWidth="1"/>
-    <col min="15625" max="15625" width="8.75" style="188" customWidth="1"/>
+    <col min="15620" max="15623" width="17.19921875" style="188" customWidth="1"/>
+    <col min="15624" max="15624" width="6.69921875" style="188" customWidth="1"/>
+    <col min="15625" max="15625" width="8.69921875" style="188" customWidth="1"/>
     <col min="15626" max="15626" width="7" style="188" customWidth="1"/>
-    <col min="15627" max="15627" width="12.125" style="188" customWidth="1"/>
+    <col min="15627" max="15627" width="12.09765625" style="188" customWidth="1"/>
     <col min="15628" max="15869" width="7" style="188"/>
-    <col min="15870" max="15870" width="9.625" style="188" customWidth="1"/>
+    <col min="15870" max="15870" width="9.59765625" style="188" customWidth="1"/>
     <col min="15871" max="15871" width="4" style="188" customWidth="1"/>
-    <col min="15872" max="15872" width="11.25" style="188" customWidth="1"/>
+    <col min="15872" max="15872" width="11.19921875" style="188" customWidth="1"/>
     <col min="15873" max="15873" width="4" style="188" customWidth="1"/>
-    <col min="15874" max="15874" width="11.625" style="188" customWidth="1"/>
+    <col min="15874" max="15874" width="11.59765625" style="188" customWidth="1"/>
     <col min="15875" max="15875" width="4" style="188" customWidth="1"/>
-    <col min="15876" max="15879" width="17.25" style="188" customWidth="1"/>
-    <col min="15880" max="15880" width="6.75" style="188" customWidth="1"/>
-    <col min="15881" max="15881" width="8.75" style="188" customWidth="1"/>
+    <col min="15876" max="15879" width="17.19921875" style="188" customWidth="1"/>
+    <col min="15880" max="15880" width="6.69921875" style="188" customWidth="1"/>
+    <col min="15881" max="15881" width="8.69921875" style="188" customWidth="1"/>
     <col min="15882" max="15882" width="7" style="188" customWidth="1"/>
-    <col min="15883" max="15883" width="12.125" style="188" customWidth="1"/>
+    <col min="15883" max="15883" width="12.09765625" style="188" customWidth="1"/>
     <col min="15884" max="16125" width="7" style="188"/>
-    <col min="16126" max="16126" width="9.625" style="188" customWidth="1"/>
+    <col min="16126" max="16126" width="9.59765625" style="188" customWidth="1"/>
     <col min="16127" max="16127" width="4" style="188" customWidth="1"/>
-    <col min="16128" max="16128" width="11.25" style="188" customWidth="1"/>
+    <col min="16128" max="16128" width="11.19921875" style="188" customWidth="1"/>
     <col min="16129" max="16129" width="4" style="188" customWidth="1"/>
-    <col min="16130" max="16130" width="11.625" style="188" customWidth="1"/>
+    <col min="16130" max="16130" width="11.59765625" style="188" customWidth="1"/>
     <col min="16131" max="16131" width="4" style="188" customWidth="1"/>
-    <col min="16132" max="16135" width="17.25" style="188" customWidth="1"/>
-    <col min="16136" max="16136" width="6.75" style="188" customWidth="1"/>
-    <col min="16137" max="16137" width="8.75" style="188" customWidth="1"/>
+    <col min="16132" max="16135" width="17.19921875" style="188" customWidth="1"/>
+    <col min="16136" max="16136" width="6.69921875" style="188" customWidth="1"/>
+    <col min="16137" max="16137" width="8.69921875" style="188" customWidth="1"/>
     <col min="16138" max="16138" width="7" style="188" customWidth="1"/>
-    <col min="16139" max="16139" width="12.125" style="188" customWidth="1"/>
+    <col min="16139" max="16139" width="12.09765625" style="188" customWidth="1"/>
     <col min="16140" max="16384" width="7" style="188"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" s="171" customFormat="1" ht="26.25">
+    <row r="1" spans="2:14" s="171" customFormat="1" ht="25.2">
       <c r="B1" s="167"/>
       <c r="C1" s="167"/>
       <c r="D1" s="167"/>
@@ -9858,32 +9854,32 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:V525"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="11.875" style="10" customWidth="1"/>
-    <col min="2" max="3" width="16.25" style="10" customWidth="1" outlineLevel="1"/>
+    <col min="1" max="1" width="11.8984375" style="10" customWidth="1"/>
+    <col min="2" max="3" width="16.19921875" style="10" customWidth="1" outlineLevel="1"/>
     <col min="4" max="5" width="2" style="10" customWidth="1"/>
     <col min="6" max="6" width="26" style="10" customWidth="1"/>
-    <col min="7" max="9" width="16.25" style="10" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="16.25" style="10" customWidth="1"/>
+    <col min="7" max="9" width="16.19921875" style="10" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="16.19921875" style="10" customWidth="1"/>
     <col min="11" max="13" width="17" style="10" customWidth="1"/>
-    <col min="14" max="17" width="16.25" style="10" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="12.75" style="10" customWidth="1" collapsed="1"/>
+    <col min="14" max="17" width="16.19921875" style="10" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="12.69921875" style="10" customWidth="1" collapsed="1"/>
     <col min="19" max="19" width="63" style="10" customWidth="1"/>
-    <col min="20" max="20" width="40.75" style="10" customWidth="1"/>
-    <col min="21" max="22" width="16.625" style="10" customWidth="1"/>
-    <col min="23" max="23" width="25.25" style="29" customWidth="1"/>
-    <col min="24" max="24" width="17.125" style="29" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.75" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17.125" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="40.69921875" style="10" customWidth="1"/>
+    <col min="21" max="22" width="16.59765625" style="10" customWidth="1"/>
+    <col min="23" max="23" width="25.19921875" style="29" customWidth="1"/>
+    <col min="24" max="24" width="17.09765625" style="29" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.69921875" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.09765625" style="29" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="22" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="13.375" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="20.125" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="17.25" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="13.3984375" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="20.09765625" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17.19921875" style="29" bestFit="1" customWidth="1"/>
     <col min="32" max="16384" width="9" style="29"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:22" s="3" customFormat="1" ht="20.25">
+    <row r="2" spans="1:22" s="3" customFormat="1" ht="21">
       <c r="A2" s="1"/>
       <c r="D2" s="2" t="s">
         <v>138</v>
@@ -9903,7 +9899,7 @@
       <c r="U2" s="5"/>
       <c r="V2" s="5"/>
     </row>
-    <row r="3" spans="1:22" s="9" customFormat="1" ht="21" thickBot="1">
+    <row r="3" spans="1:22" s="9" customFormat="1" ht="21.6" thickBot="1">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -9920,7 +9916,7 @@
       <c r="N3" s="8"/>
       <c r="O3" s="5"/>
     </row>
-    <row r="4" spans="1:22" s="14" customFormat="1" ht="21" thickBot="1">
+    <row r="4" spans="1:22" s="14" customFormat="1" ht="21.6" thickBot="1">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -9937,7 +9933,7 @@
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
     </row>
-    <row r="5" spans="1:22" s="14" customFormat="1" ht="21" thickBot="1">
+    <row r="5" spans="1:22" s="14" customFormat="1" ht="21.6" thickBot="1">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -9969,7 +9965,7 @@
         <v>※ 기간(개월) 입력 필요 (Q5, Q6)</v>
       </c>
     </row>
-    <row r="6" spans="1:22" s="14" customFormat="1" ht="21" thickBot="1">
+    <row r="6" spans="1:22" s="14" customFormat="1" ht="21.6" thickBot="1">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -9991,7 +9987,7 @@
       </c>
       <c r="P6" s="387"/>
     </row>
-    <row r="7" spans="1:22" s="14" customFormat="1" ht="21" thickBot="1">
+    <row r="7" spans="1:22" s="14" customFormat="1" ht="21.6" thickBot="1">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -10013,7 +10009,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:22" s="14" customFormat="1" ht="21" thickBot="1">
+    <row r="8" spans="1:22" s="14" customFormat="1" ht="21.6" thickBot="1">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -10037,7 +10033,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="9" spans="1:22" s="14" customFormat="1" ht="20.25">
+    <row r="9" spans="1:22" s="14" customFormat="1" ht="21">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -18791,33 +18787,33 @@
       <c r="H194" s="360"/>
       <c r="I194" s="360"/>
       <c r="J194" s="315">
-        <f>G194+I194-H194</f>
+        <f t="shared" ref="J194:J199" si="144">G194+I194-H194</f>
         <v>0</v>
       </c>
       <c r="K194" s="360"/>
       <c r="L194" s="315">
-        <f t="shared" ref="L194:L197" si="144">J194-K194</f>
+        <f t="shared" ref="L194:L197" si="145">J194-K194</f>
         <v>0</v>
       </c>
       <c r="M194" s="56" t="e">
-        <f t="shared" ref="M194:M197" si="145">L194/K194</f>
+        <f t="shared" ref="M194:M197" si="146">L194/K194</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N194" s="56" t="e">
-        <f t="shared" ref="N194:N199" si="146">G194/$N$12</f>
+        <f t="shared" ref="N194:N199" si="147">G194/$N$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O194" s="56" t="e">
-        <f t="shared" ref="O194:O199" si="147">G194/$O$12</f>
+        <f t="shared" ref="O194:O199" si="148">G194/$O$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P194" s="305" t="e">
-        <f t="shared" ref="P194:P199" si="148">IF(ABS(O194)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P194:P199" si="149">IF(ABS(O194)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q194" s="359"/>
       <c r="R194" s="305" t="e">
-        <f t="shared" ref="R194:R199" si="149">IF(P194="O","O",IF(Q194="O","O","X"))</f>
+        <f t="shared" ref="R194:R199" si="150">IF(P194="O","O",IF(Q194="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S194" s="94"/>
@@ -18839,33 +18835,33 @@
       <c r="H195" s="360"/>
       <c r="I195" s="360"/>
       <c r="J195" s="315">
-        <f>G195+I195-H195</f>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="K195" s="360"/>
       <c r="L195" s="315">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0</v>
       </c>
       <c r="M195" s="56" t="e">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N195" s="56" t="e">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O195" s="56" t="e">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P195" s="305" t="e">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q195" s="359"/>
       <c r="R195" s="305" t="e">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S195" s="94"/>
@@ -18887,33 +18883,33 @@
       <c r="H196" s="360"/>
       <c r="I196" s="360"/>
       <c r="J196" s="315">
-        <f>G196+I196-H196</f>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="K196" s="360"/>
       <c r="L196" s="315">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0</v>
       </c>
       <c r="M196" s="56" t="e">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N196" s="56" t="e">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O196" s="56" t="e">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P196" s="305" t="e">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q196" s="359"/>
       <c r="R196" s="305" t="e">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S196" s="94"/>
@@ -18941,33 +18937,33 @@
         <v>0</v>
       </c>
       <c r="J197" s="315">
-        <f>G197+I197-H197</f>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="K197" s="360"/>
       <c r="L197" s="315">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0</v>
       </c>
       <c r="M197" s="56" t="e">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N197" s="56" t="e">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O197" s="56" t="e">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P197" s="305" t="e">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q197" s="359"/>
       <c r="R197" s="305" t="e">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S197" s="94"/>
@@ -18987,27 +18983,27 @@
       <c r="H198" s="360"/>
       <c r="I198" s="360"/>
       <c r="J198" s="315">
-        <f>G198+I198-H198</f>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="K198" s="360"/>
       <c r="L198" s="315"/>
       <c r="M198" s="56"/>
       <c r="N198" s="56" t="e">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O198" s="56" t="e">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P198" s="305" t="e">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q198" s="359"/>
       <c r="R198" s="305" t="e">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S198" s="94"/>
@@ -19027,27 +19023,27 @@
       <c r="H199" s="360"/>
       <c r="I199" s="360"/>
       <c r="J199" s="315">
-        <f>G199+I199-H199</f>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="K199" s="360"/>
       <c r="L199" s="315"/>
       <c r="M199" s="56"/>
       <c r="N199" s="56" t="e">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O199" s="56" t="e">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P199" s="305" t="e">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q199" s="359"/>
       <c r="R199" s="305" t="e">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S199" s="94"/>
@@ -19071,15 +19067,15 @@
       <c r="H200" s="332"/>
       <c r="I200" s="332"/>
       <c r="J200" s="332">
-        <f t="shared" ref="J200:L200" si="150">J179+J181+J184+J189+J193</f>
+        <f t="shared" ref="J200:L200" si="151">J179+J181+J184+J189+J193</f>
         <v>0</v>
       </c>
       <c r="K200" s="332">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>0</v>
       </c>
       <c r="L200" s="332">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>0</v>
       </c>
       <c r="M200" s="333"/>
@@ -19109,15 +19105,15 @@
       <c r="H201" s="332"/>
       <c r="I201" s="332"/>
       <c r="J201" s="332">
-        <f t="shared" ref="J201:L201" si="151">J200+J177</f>
+        <f t="shared" ref="J201:L201" si="152">J200+J177</f>
         <v>0</v>
       </c>
       <c r="K201" s="332">
-        <f t="shared" si="151"/>
+        <f t="shared" si="152"/>
         <v>0</v>
       </c>
       <c r="L201" s="332">
-        <f t="shared" si="151"/>
+        <f t="shared" si="152"/>
         <v>0</v>
       </c>
       <c r="M201" s="333"/>
@@ -19350,7 +19346,7 @@
         <v>0</v>
       </c>
       <c r="M207" s="333" t="e">
-        <f t="shared" ref="M207:M225" si="152">L207/K207</f>
+        <f t="shared" ref="M207:M225" si="153">L207/K207</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N207" s="47"/>
@@ -19385,11 +19381,11 @@
       </c>
       <c r="K208" s="358"/>
       <c r="L208" s="55">
-        <f t="shared" ref="L208:L209" si="153">J208-K208</f>
+        <f t="shared" ref="L208:L209" si="154">J208-K208</f>
         <v>0</v>
       </c>
       <c r="M208" s="56" t="e">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N208" s="57" t="e">
@@ -19401,12 +19397,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="P208" s="58" t="e">
-        <f t="shared" ref="P208:P209" si="154">IF(ABS(O208)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P208:P209" si="155">IF(ABS(O208)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q208" s="367"/>
       <c r="R208" s="59" t="e">
-        <f t="shared" ref="R208:R209" si="155">IF(P208="O","O",IF(Q208="O","O","X"))</f>
+        <f t="shared" ref="R208:R209" si="156">IF(P208="O","O",IF(Q208="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S208" s="133"/>
@@ -19432,11 +19428,11 @@
       </c>
       <c r="K209" s="358"/>
       <c r="L209" s="55">
+        <f t="shared" si="154"/>
+        <v>0</v>
+      </c>
+      <c r="M209" s="56" t="e">
         <f t="shared" si="153"/>
-        <v>0</v>
-      </c>
-      <c r="M209" s="56" t="e">
-        <f t="shared" si="152"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N209" s="57" t="e">
@@ -19448,12 +19444,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="P209" s="58" t="e">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q209" s="367"/>
       <c r="R209" s="59" t="e">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S209" s="133"/>
@@ -19488,7 +19484,7 @@
         <v>0</v>
       </c>
       <c r="M210" s="333" t="e">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N210" s="47"/>
@@ -19558,12 +19554,12 @@
       <c r="H212" s="358"/>
       <c r="I212" s="368"/>
       <c r="J212" s="55">
-        <f t="shared" ref="J212:J217" si="156">G212+H212-I212</f>
+        <f t="shared" ref="J212:J217" si="157">G212+H212-I212</f>
         <v>0</v>
       </c>
       <c r="K212" s="358"/>
       <c r="L212" s="55">
-        <f t="shared" ref="L212:L217" si="157">J212-K212</f>
+        <f t="shared" ref="L212:L217" si="158">J212-K212</f>
         <v>0</v>
       </c>
       <c r="M212" s="56" t="e">
@@ -19571,20 +19567,20 @@
         <v>#DIV/0!</v>
       </c>
       <c r="N212" s="57" t="e">
-        <f t="shared" ref="N212:N217" si="158">G212/$N$12</f>
+        <f t="shared" ref="N212:N217" si="159">G212/$N$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O212" s="57" t="e">
-        <f t="shared" ref="O212:O217" si="159">G212*12/CurMonths/$O$12</f>
+        <f t="shared" ref="O212:O217" si="160">G212*12/CurMonths/$O$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P212" s="58" t="e">
-        <f t="shared" ref="P212:P217" si="160">IF(ABS(O212)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P212:P217" si="161">IF(ABS(O212)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q212" s="367"/>
       <c r="R212" s="59" t="e">
-        <f t="shared" ref="R212:R217" si="161">IF(P212="O","O",IF(Q212="O","O","X"))</f>
+        <f t="shared" ref="R212:R217" si="162">IF(P212="O","O",IF(Q212="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S212" s="129"/>
@@ -19604,12 +19600,12 @@
       <c r="H213" s="358"/>
       <c r="I213" s="358"/>
       <c r="J213" s="55">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>0</v>
       </c>
       <c r="K213" s="358"/>
       <c r="L213" s="55">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>0</v>
       </c>
       <c r="M213" s="56" t="e">
@@ -19617,20 +19613,20 @@
         <v>#DIV/0!</v>
       </c>
       <c r="N213" s="57" t="e">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O213" s="57" t="e">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P213" s="58" t="e">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q213" s="367"/>
       <c r="R213" s="59" t="e">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S213" s="336"/>
@@ -19650,33 +19646,33 @@
       <c r="H214" s="358"/>
       <c r="I214" s="358"/>
       <c r="J214" s="55">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>0</v>
       </c>
       <c r="K214" s="358"/>
       <c r="L214" s="55">
-        <f t="shared" ref="L214:L216" si="162">J214-K214</f>
+        <f t="shared" ref="L214:L216" si="163">J214-K214</f>
         <v>0</v>
       </c>
       <c r="M214" s="56" t="e">
-        <f t="shared" ref="M214:M216" si="163">L214/K214</f>
+        <f t="shared" ref="M214:M216" si="164">L214/K214</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N214" s="57" t="e">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O214" s="57" t="e">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P214" s="58" t="e">
-        <f t="shared" ref="P214:P216" si="164">IF(ABS(O214)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P214:P216" si="165">IF(ABS(O214)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q214" s="367"/>
       <c r="R214" s="59" t="e">
-        <f t="shared" ref="R214:R216" si="165">IF(P214="O","O",IF(Q214="O","O","X"))</f>
+        <f t="shared" ref="R214:R216" si="166">IF(P214="O","O",IF(Q214="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S214" s="336"/>
@@ -19696,33 +19692,33 @@
       <c r="H215" s="358"/>
       <c r="I215" s="358"/>
       <c r="J215" s="55">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>0</v>
       </c>
       <c r="K215" s="358"/>
       <c r="L215" s="55">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>0</v>
       </c>
       <c r="M215" s="56" t="e">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N215" s="57" t="e">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O215" s="57" t="e">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P215" s="58" t="e">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q215" s="367"/>
       <c r="R215" s="59" t="e">
-        <f t="shared" si="165"/>
+        <f t="shared" si="166"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S215" s="336"/>
@@ -19742,33 +19738,33 @@
       <c r="H216" s="358"/>
       <c r="I216" s="358"/>
       <c r="J216" s="55">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>0</v>
       </c>
       <c r="K216" s="358"/>
       <c r="L216" s="55">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>0</v>
       </c>
       <c r="M216" s="56" t="e">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N216" s="57" t="e">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O216" s="57" t="e">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P216" s="58" t="e">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q216" s="367"/>
       <c r="R216" s="59" t="e">
-        <f t="shared" si="165"/>
+        <f t="shared" si="166"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S216" s="336"/>
@@ -19788,12 +19784,12 @@
       <c r="H217" s="358"/>
       <c r="I217" s="358"/>
       <c r="J217" s="55">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>0</v>
       </c>
       <c r="K217" s="358"/>
       <c r="L217" s="55">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>0</v>
       </c>
       <c r="M217" s="56" t="e">
@@ -19801,20 +19797,20 @@
         <v>#DIV/0!</v>
       </c>
       <c r="N217" s="57" t="e">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O217" s="57" t="e">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P217" s="58" t="e">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q217" s="367"/>
       <c r="R217" s="59" t="e">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S217" s="129"/>
@@ -19854,7 +19850,7 @@
         <v>0</v>
       </c>
       <c r="M218" s="335" t="e">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N218" s="47"/>
@@ -19882,33 +19878,33 @@
       <c r="H219" s="358"/>
       <c r="I219" s="358"/>
       <c r="J219" s="55">
-        <f t="shared" ref="J219:J224" si="166">G219+H219-I219</f>
+        <f t="shared" ref="J219:J224" si="167">G219+H219-I219</f>
         <v>0</v>
       </c>
       <c r="K219" s="358"/>
       <c r="L219" s="55">
-        <f t="shared" ref="L219:L224" si="167">J219-K219</f>
+        <f t="shared" ref="L219:L224" si="168">J219-K219</f>
         <v>0</v>
       </c>
       <c r="M219" s="56" t="e">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N219" s="57" t="e">
-        <f t="shared" ref="N219:N224" si="168">G219/$N$12</f>
+        <f t="shared" ref="N219:N224" si="169">G219/$N$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O219" s="57" t="e">
-        <f t="shared" ref="O219:O224" si="169">G219*12/CurMonths/$O$12</f>
+        <f t="shared" ref="O219:O224" si="170">G219*12/CurMonths/$O$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P219" s="58" t="e">
-        <f t="shared" ref="P219:P224" si="170">IF(ABS(O219)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P219:P224" si="171">IF(ABS(O219)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q219" s="367"/>
       <c r="R219" s="59" t="e">
-        <f t="shared" ref="R219:R224" si="171">IF(P219="O","O",IF(Q219="O","O","X"))</f>
+        <f t="shared" ref="R219:R224" si="172">IF(P219="O","O",IF(Q219="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S219" s="133"/>
@@ -19931,33 +19927,33 @@
       <c r="H220" s="358"/>
       <c r="I220" s="358"/>
       <c r="J220" s="55">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>0</v>
       </c>
       <c r="K220" s="358"/>
       <c r="L220" s="55">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>0</v>
       </c>
       <c r="M220" s="56" t="e">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N220" s="57" t="e">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O220" s="57" t="e">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P220" s="58" t="e">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q220" s="367"/>
       <c r="R220" s="59" t="e">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S220" s="346"/>
@@ -19980,33 +19976,33 @@
       <c r="H221" s="358"/>
       <c r="I221" s="358"/>
       <c r="J221" s="55">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>0</v>
       </c>
       <c r="K221" s="358"/>
       <c r="L221" s="55">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>0</v>
       </c>
       <c r="M221" s="56" t="e">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N221" s="57" t="e">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O221" s="57" t="e">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P221" s="58" t="e">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q221" s="367"/>
       <c r="R221" s="59" t="e">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S221" s="346"/>
@@ -20029,33 +20025,33 @@
       <c r="H222" s="358"/>
       <c r="I222" s="358"/>
       <c r="J222" s="55">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>0</v>
       </c>
       <c r="K222" s="358"/>
       <c r="L222" s="55">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>0</v>
       </c>
       <c r="M222" s="56" t="e">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N222" s="57" t="e">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O222" s="57" t="e">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P222" s="58" t="e">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q222" s="367"/>
       <c r="R222" s="59" t="e">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S222" s="94"/>
@@ -20075,30 +20071,30 @@
       <c r="H223" s="358"/>
       <c r="I223" s="358"/>
       <c r="J223" s="55">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>0</v>
       </c>
       <c r="K223" s="358"/>
       <c r="L223" s="55"/>
       <c r="M223" s="56" t="e">
-        <f t="shared" ref="M223" si="172">L223/K223</f>
+        <f t="shared" ref="M223" si="173">L223/K223</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N223" s="57" t="e">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O223" s="57" t="e">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P223" s="58" t="e">
-        <f t="shared" ref="P223" si="173">IF(ABS(O223)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P223" si="174">IF(ABS(O223)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q223" s="367"/>
       <c r="R223" s="59" t="e">
-        <f t="shared" ref="R223" si="174">IF(P223="O","O",IF(Q223="O","O","X"))</f>
+        <f t="shared" ref="R223" si="175">IF(P223="O","O",IF(Q223="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S223" s="94"/>
@@ -20118,33 +20114,33 @@
       <c r="H224" s="358"/>
       <c r="I224" s="358"/>
       <c r="J224" s="55">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>0</v>
       </c>
       <c r="K224" s="358"/>
       <c r="L224" s="55">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>0</v>
       </c>
       <c r="M224" s="56" t="e">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N224" s="57" t="e">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O224" s="57" t="e">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P224" s="58" t="e">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q224" s="367"/>
       <c r="R224" s="59" t="e">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S224" s="129"/>
@@ -20179,7 +20175,7 @@
         <v>0</v>
       </c>
       <c r="M225" s="333" t="e">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N225" s="47"/>
@@ -20336,7 +20332,7 @@
         <v>0</v>
       </c>
       <c r="M229" s="333" t="e">
-        <f t="shared" ref="M229:M259" si="175">L229/K229</f>
+        <f t="shared" ref="M229:M259" si="176">L229/K229</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N229" s="47"/>
@@ -20366,33 +20362,33 @@
       <c r="H230" s="366"/>
       <c r="I230" s="366"/>
       <c r="J230" s="55">
-        <f t="shared" ref="J230:J256" si="176">G230+H230-I230</f>
+        <f t="shared" ref="J230:J256" si="177">G230+H230-I230</f>
         <v>0</v>
       </c>
       <c r="K230" s="358"/>
       <c r="L230" s="55">
-        <f t="shared" ref="L230:L258" si="177">J230-K230</f>
+        <f t="shared" ref="L230:L258" si="178">J230-K230</f>
         <v>0</v>
       </c>
       <c r="M230" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N230" s="57" t="e">
-        <f t="shared" ref="N230:N258" si="178">G230/$N$12</f>
+        <f t="shared" ref="N230:N258" si="179">G230/$N$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O230" s="57" t="e">
-        <f t="shared" ref="O230:O258" si="179">G230*12/CurMonths/$O$12</f>
+        <f t="shared" ref="O230:O258" si="180">G230*12/CurMonths/$O$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P230" s="58" t="e">
-        <f t="shared" ref="P230:P258" si="180">IF(ABS(O230)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P230:P258" si="181">IF(ABS(O230)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q230" s="367"/>
       <c r="R230" s="59" t="e">
-        <f t="shared" ref="R230:R258" si="181">IF(P230="O","O",IF(Q230="O","O","X"))</f>
+        <f t="shared" ref="R230:R258" si="182">IF(P230="O","O",IF(Q230="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S230" s="347"/>
@@ -20417,33 +20413,33 @@
       <c r="H231" s="366"/>
       <c r="I231" s="366"/>
       <c r="J231" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K231" s="369"/>
       <c r="L231" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M231" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N231" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O231" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P231" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q231" s="367"/>
       <c r="R231" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S231" s="133"/>
@@ -20468,33 +20464,33 @@
       <c r="H232" s="366"/>
       <c r="I232" s="366"/>
       <c r="J232" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K232" s="369"/>
       <c r="L232" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M232" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N232" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O232" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P232" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q232" s="367"/>
       <c r="R232" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S232" s="129"/>
@@ -20519,33 +20515,33 @@
       <c r="H233" s="366"/>
       <c r="I233" s="366"/>
       <c r="J233" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K233" s="369"/>
       <c r="L233" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M233" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N233" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O233" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P233" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q233" s="367"/>
       <c r="R233" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S233" s="94"/>
@@ -20570,33 +20566,33 @@
       <c r="H234" s="366"/>
       <c r="I234" s="366"/>
       <c r="J234" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K234" s="369"/>
       <c r="L234" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M234" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N234" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O234" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P234" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q234" s="367"/>
       <c r="R234" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S234" s="94"/>
@@ -20621,33 +20617,33 @@
       <c r="H235" s="366"/>
       <c r="I235" s="366"/>
       <c r="J235" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K235" s="369"/>
       <c r="L235" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M235" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N235" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O235" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P235" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q235" s="367"/>
       <c r="R235" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S235" s="336"/>
@@ -20669,33 +20665,33 @@
       <c r="H236" s="366"/>
       <c r="I236" s="366"/>
       <c r="J236" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K236" s="369"/>
       <c r="L236" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M236" s="56" t="e">
-        <f t="shared" ref="M236" si="182">L236/K236</f>
+        <f t="shared" ref="M236" si="183">L236/K236</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N236" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O236" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P236" s="58" t="e">
-        <f t="shared" ref="P236" si="183">IF(ABS(O236)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P236" si="184">IF(ABS(O236)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q236" s="367"/>
       <c r="R236" s="59" t="e">
-        <f t="shared" ref="R236" si="184">IF(P236="O","O",IF(Q236="O","O","X"))</f>
+        <f t="shared" ref="R236" si="185">IF(P236="O","O",IF(Q236="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S236" s="94"/>
@@ -20717,33 +20713,33 @@
       <c r="H237" s="366"/>
       <c r="I237" s="366"/>
       <c r="J237" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K237" s="369"/>
       <c r="L237" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M237" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N237" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O237" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P237" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q237" s="367"/>
       <c r="R237" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S237" s="94"/>
@@ -20765,33 +20761,33 @@
       <c r="H238" s="366"/>
       <c r="I238" s="366"/>
       <c r="J238" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K238" s="369"/>
       <c r="L238" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M238" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N238" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O238" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P238" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q238" s="367"/>
       <c r="R238" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S238" s="94"/>
@@ -20813,33 +20809,33 @@
       <c r="H239" s="366"/>
       <c r="I239" s="366"/>
       <c r="J239" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K239" s="369"/>
       <c r="L239" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M239" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N239" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O239" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P239" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q239" s="367"/>
       <c r="R239" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S239" s="94"/>
@@ -20861,33 +20857,33 @@
       <c r="H240" s="366"/>
       <c r="I240" s="366"/>
       <c r="J240" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K240" s="369"/>
       <c r="L240" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M240" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N240" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O240" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P240" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q240" s="367"/>
       <c r="R240" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S240" s="336"/>
@@ -20909,33 +20905,33 @@
       <c r="H241" s="366"/>
       <c r="I241" s="366"/>
       <c r="J241" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K241" s="369"/>
       <c r="L241" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M241" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N241" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O241" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P241" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q241" s="367"/>
       <c r="R241" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S241" s="336"/>
@@ -20957,33 +20953,33 @@
       <c r="H242" s="366"/>
       <c r="I242" s="366"/>
       <c r="J242" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K242" s="369"/>
       <c r="L242" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M242" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N242" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O242" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P242" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q242" s="367"/>
       <c r="R242" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S242" s="336"/>
@@ -21005,33 +21001,33 @@
       <c r="H243" s="366"/>
       <c r="I243" s="366"/>
       <c r="J243" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K243" s="369"/>
       <c r="L243" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M243" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N243" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O243" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P243" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q243" s="367"/>
       <c r="R243" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S243" s="129"/>
@@ -21053,33 +21049,33 @@
       <c r="H244" s="366"/>
       <c r="I244" s="366"/>
       <c r="J244" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K244" s="369"/>
       <c r="L244" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M244" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N244" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O244" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P244" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q244" s="367"/>
       <c r="R244" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S244" s="133"/>
@@ -21101,33 +21097,33 @@
       <c r="H245" s="366"/>
       <c r="I245" s="366"/>
       <c r="J245" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K245" s="369"/>
       <c r="L245" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M245" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N245" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O245" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P245" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q245" s="367"/>
       <c r="R245" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S245" s="133"/>
@@ -21149,33 +21145,33 @@
       <c r="H246" s="366"/>
       <c r="I246" s="366"/>
       <c r="J246" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K246" s="369"/>
       <c r="L246" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M246" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N246" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O246" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P246" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q246" s="367"/>
       <c r="R246" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S246" s="94"/>
@@ -21197,33 +21193,33 @@
       <c r="H247" s="366"/>
       <c r="I247" s="366"/>
       <c r="J247" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K247" s="369"/>
       <c r="L247" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M247" s="56" t="e">
-        <f t="shared" ref="M247" si="185">L247/K247</f>
+        <f t="shared" ref="M247" si="186">L247/K247</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N247" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O247" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P247" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q247" s="367"/>
       <c r="R247" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S247" s="94"/>
@@ -21245,33 +21241,33 @@
       <c r="H248" s="366"/>
       <c r="I248" s="366"/>
       <c r="J248" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K248" s="369"/>
       <c r="L248" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M248" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N248" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O248" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P248" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q248" s="367"/>
       <c r="R248" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S248" s="133"/>
@@ -21293,33 +21289,33 @@
       <c r="H249" s="366"/>
       <c r="I249" s="366"/>
       <c r="J249" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K249" s="369"/>
       <c r="L249" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M249" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N249" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O249" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P249" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q249" s="367"/>
       <c r="R249" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S249" s="133"/>
@@ -21344,33 +21340,33 @@
       <c r="H250" s="366"/>
       <c r="I250" s="366"/>
       <c r="J250" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K250" s="369"/>
       <c r="L250" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M250" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N250" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O250" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P250" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q250" s="367"/>
       <c r="R250" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S250" s="94"/>
@@ -21395,33 +21391,33 @@
       <c r="H251" s="366"/>
       <c r="I251" s="366"/>
       <c r="J251" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K251" s="369"/>
       <c r="L251" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M251" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N251" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O251" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P251" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q251" s="367"/>
       <c r="R251" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S251" s="94"/>
@@ -21446,33 +21442,33 @@
       <c r="H252" s="366"/>
       <c r="I252" s="366"/>
       <c r="J252" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K252" s="369"/>
       <c r="L252" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M252" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N252" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O252" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P252" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q252" s="367"/>
       <c r="R252" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S252" s="94"/>
@@ -21497,33 +21493,33 @@
       <c r="H253" s="366"/>
       <c r="I253" s="366"/>
       <c r="J253" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K253" s="369"/>
       <c r="L253" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M253" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N253" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O253" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P253" s="58" t="e">
-        <f t="shared" ref="P253" si="186">IF(ABS(O253)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P253" si="187">IF(ABS(O253)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q253" s="367"/>
       <c r="R253" s="59" t="e">
-        <f t="shared" ref="R253" si="187">IF(P253="O","O",IF(Q253="O","O","X"))</f>
+        <f t="shared" ref="R253" si="188">IF(P253="O","O",IF(Q253="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S253" s="94"/>
@@ -21545,33 +21541,33 @@
       <c r="H254" s="366"/>
       <c r="I254" s="366"/>
       <c r="J254" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K254" s="369"/>
       <c r="L254" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M254" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N254" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O254" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P254" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q254" s="367"/>
       <c r="R254" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S254" s="94"/>
@@ -21596,33 +21592,33 @@
       <c r="H255" s="366"/>
       <c r="I255" s="366"/>
       <c r="J255" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K255" s="369"/>
       <c r="L255" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M255" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N255" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O255" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P255" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q255" s="367"/>
       <c r="R255" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S255" s="94"/>
@@ -21644,33 +21640,33 @@
       <c r="H256" s="366"/>
       <c r="I256" s="366"/>
       <c r="J256" s="55">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="K256" s="369"/>
       <c r="L256" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M256" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N256" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O256" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P256" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q256" s="367"/>
       <c r="R256" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S256" s="94"/>
@@ -21694,28 +21690,28 @@
       <c r="J257" s="55"/>
       <c r="K257" s="358"/>
       <c r="L257" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M257" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N257" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O257" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P257" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q257" s="367"/>
       <c r="R257" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S257" s="94"/>
@@ -21739,28 +21735,28 @@
       <c r="J258" s="55"/>
       <c r="K258" s="370"/>
       <c r="L258" s="55">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="M258" s="56" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N258" s="57" t="e">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O258" s="57" t="e">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P258" s="58" t="e">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q258" s="367"/>
       <c r="R258" s="59" t="e">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S258" s="94"/>
@@ -21798,7 +21794,7 @@
         <v>0</v>
       </c>
       <c r="M259" s="333" t="e">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N259" s="47"/>
@@ -21921,7 +21917,7 @@
         <v>0</v>
       </c>
       <c r="M262" s="333" t="e">
-        <f t="shared" ref="M262:M315" si="188">L262/K262</f>
+        <f t="shared" ref="M262:M315" si="189">L262/K262</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N262" s="47"/>
@@ -21951,33 +21947,33 @@
       <c r="H263" s="366"/>
       <c r="I263" s="366"/>
       <c r="J263" s="93">
-        <f t="shared" ref="J263:J275" si="189">G263-H263+I263</f>
+        <f t="shared" ref="J263:J275" si="190">G263-H263+I263</f>
         <v>0</v>
       </c>
       <c r="K263" s="369"/>
       <c r="L263" s="55">
-        <f t="shared" ref="L263:L275" si="190">J263-K263</f>
+        <f t="shared" ref="L263:L275" si="191">J263-K263</f>
         <v>0</v>
       </c>
       <c r="M263" s="56" t="e">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N263" s="57" t="e">
-        <f t="shared" ref="N263:N275" si="191">G263/$N$12</f>
+        <f t="shared" ref="N263:N275" si="192">G263/$N$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O263" s="57" t="e">
-        <f t="shared" ref="O263:O275" si="192">G263*12/CurMonths/$O$12</f>
+        <f t="shared" ref="O263:O275" si="193">G263*12/CurMonths/$O$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P263" s="58" t="e">
-        <f t="shared" ref="P263:P275" si="193">IF(ABS(O263)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P263:P275" si="194">IF(ABS(O263)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q263" s="367"/>
       <c r="R263" s="59" t="e">
-        <f t="shared" ref="R263:R275" si="194">IF(P263="O","O",IF(Q263="O","O","X"))</f>
+        <f t="shared" ref="R263:R275" si="195">IF(P263="O","O",IF(Q263="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S263" s="94"/>
@@ -22002,33 +21998,33 @@
       <c r="H264" s="366"/>
       <c r="I264" s="366"/>
       <c r="J264" s="93">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="K264" s="369"/>
       <c r="L264" s="55">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0</v>
       </c>
       <c r="M264" s="56" t="e">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N264" s="57" t="e">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O264" s="57" t="e">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P264" s="58" t="e">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q264" s="367"/>
       <c r="R264" s="59" t="e">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S264" s="94"/>
@@ -22050,33 +22046,33 @@
       <c r="H265" s="366"/>
       <c r="I265" s="366"/>
       <c r="J265" s="93">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="K265" s="369"/>
       <c r="L265" s="55">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0</v>
       </c>
       <c r="M265" s="56" t="e">
-        <f t="shared" ref="M265:M275" si="195">L265/K265</f>
+        <f t="shared" ref="M265:M275" si="196">L265/K265</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N265" s="57" t="e">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O265" s="57" t="e">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P265" s="58" t="e">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q265" s="367"/>
       <c r="R265" s="59" t="e">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S265" s="94"/>
@@ -22098,33 +22094,33 @@
       <c r="H266" s="366"/>
       <c r="I266" s="366"/>
       <c r="J266" s="93">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="K266" s="369"/>
       <c r="L266" s="55">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0</v>
       </c>
       <c r="M266" s="56" t="e">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N266" s="57" t="e">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O266" s="57" t="e">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P266" s="58" t="e">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q266" s="367"/>
       <c r="R266" s="59" t="e">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S266" s="94"/>
@@ -22146,33 +22142,33 @@
       <c r="H267" s="366"/>
       <c r="I267" s="366"/>
       <c r="J267" s="93">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="K267" s="369"/>
       <c r="L267" s="55">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0</v>
       </c>
       <c r="M267" s="56" t="e">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N267" s="57" t="e">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O267" s="57" t="e">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P267" s="58" t="e">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q267" s="367"/>
       <c r="R267" s="59" t="e">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S267" s="94"/>
@@ -22194,33 +22190,33 @@
       <c r="H268" s="366"/>
       <c r="I268" s="366"/>
       <c r="J268" s="93">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="K268" s="369"/>
       <c r="L268" s="55">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0</v>
       </c>
       <c r="M268" s="56" t="e">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N268" s="57" t="e">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O268" s="57" t="e">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P268" s="58" t="e">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q268" s="367"/>
       <c r="R268" s="59" t="e">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S268" s="94"/>
@@ -22242,33 +22238,33 @@
       <c r="H269" s="366"/>
       <c r="I269" s="366"/>
       <c r="J269" s="93">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="K269" s="369"/>
       <c r="L269" s="55">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0</v>
       </c>
       <c r="M269" s="56" t="e">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N269" s="57" t="e">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O269" s="57" t="e">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P269" s="58" t="e">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q269" s="367"/>
       <c r="R269" s="59" t="e">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S269" s="94"/>
@@ -22290,33 +22286,33 @@
       <c r="H270" s="366"/>
       <c r="I270" s="366"/>
       <c r="J270" s="93">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="K270" s="369"/>
       <c r="L270" s="55">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0</v>
       </c>
       <c r="M270" s="56" t="e">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N270" s="57" t="e">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O270" s="57" t="e">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P270" s="58" t="e">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q270" s="367"/>
       <c r="R270" s="59" t="e">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S270" s="94"/>
@@ -22338,33 +22334,33 @@
       <c r="H271" s="366"/>
       <c r="I271" s="366"/>
       <c r="J271" s="93">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="K271" s="369"/>
       <c r="L271" s="55">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0</v>
       </c>
       <c r="M271" s="56" t="e">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N271" s="57" t="e">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O271" s="57" t="e">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P271" s="58" t="e">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q271" s="367"/>
       <c r="R271" s="59" t="e">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S271" s="94"/>
@@ -22386,33 +22382,33 @@
       <c r="H272" s="366"/>
       <c r="I272" s="366"/>
       <c r="J272" s="93">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="K272" s="369"/>
       <c r="L272" s="55">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0</v>
       </c>
       <c r="M272" s="56" t="e">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N272" s="57" t="e">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O272" s="57" t="e">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P272" s="58" t="e">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q272" s="367"/>
       <c r="R272" s="59" t="e">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S272" s="94"/>
@@ -22434,33 +22430,33 @@
       <c r="H273" s="366"/>
       <c r="I273" s="366"/>
       <c r="J273" s="93">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="K273" s="369"/>
       <c r="L273" s="55">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0</v>
       </c>
       <c r="M273" s="56" t="e">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N273" s="57" t="e">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O273" s="57" t="e">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P273" s="58" t="e">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q273" s="367"/>
       <c r="R273" s="59" t="e">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S273" s="94"/>
@@ -22482,33 +22478,33 @@
       <c r="H274" s="366"/>
       <c r="I274" s="366"/>
       <c r="J274" s="93">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="K274" s="369"/>
       <c r="L274" s="55">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0</v>
       </c>
       <c r="M274" s="56" t="e">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N274" s="57" t="e">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O274" s="57" t="e">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P274" s="58" t="e">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q274" s="367"/>
       <c r="R274" s="59" t="e">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S274" s="94"/>
@@ -22530,33 +22526,33 @@
       <c r="H275" s="366"/>
       <c r="I275" s="366"/>
       <c r="J275" s="93">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="K275" s="369"/>
       <c r="L275" s="55">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0</v>
       </c>
       <c r="M275" s="56" t="e">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N275" s="57" t="e">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O275" s="57" t="e">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P275" s="58" t="e">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q275" s="367"/>
       <c r="R275" s="59" t="e">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S275" s="94"/>
@@ -22591,7 +22587,7 @@
         <v>0</v>
       </c>
       <c r="M276" s="333" t="e">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N276" s="56"/>
@@ -22618,33 +22614,33 @@
       <c r="H277" s="366"/>
       <c r="I277" s="366"/>
       <c r="J277" s="93">
-        <f t="shared" ref="J277:J286" si="196">G277-H277+I277</f>
+        <f t="shared" ref="J277:J286" si="197">G277-H277+I277</f>
         <v>0</v>
       </c>
       <c r="K277" s="369"/>
       <c r="L277" s="55">
-        <f t="shared" ref="L277:L286" si="197">J277-K277</f>
+        <f t="shared" ref="L277:L286" si="198">J277-K277</f>
         <v>0</v>
       </c>
       <c r="M277" s="56" t="e">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N277" s="57" t="e">
-        <f t="shared" ref="N277:N286" si="198">G277/$N$12</f>
+        <f t="shared" ref="N277:N286" si="199">G277/$N$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O277" s="57" t="e">
-        <f t="shared" ref="O277:O286" si="199">G277*12/CurMonths/$O$12</f>
+        <f t="shared" ref="O277:O286" si="200">G277*12/CurMonths/$O$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P277" s="58" t="e">
-        <f t="shared" ref="P277:P286" si="200">IF(ABS(O277)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P277:P286" si="201">IF(ABS(O277)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q277" s="367"/>
       <c r="R277" s="59" t="e">
-        <f t="shared" ref="R277:R286" si="201">IF(P277="O","O",IF(Q277="O","O","X"))</f>
+        <f t="shared" ref="R277:R286" si="202">IF(P277="O","O",IF(Q277="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S277" s="94"/>
@@ -22669,33 +22665,33 @@
       <c r="H278" s="366"/>
       <c r="I278" s="366"/>
       <c r="J278" s="93">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0</v>
       </c>
       <c r="K278" s="369"/>
       <c r="L278" s="55">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>0</v>
       </c>
       <c r="M278" s="56" t="e">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N278" s="57" t="e">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O278" s="57" t="e">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P278" s="58" t="e">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q278" s="367"/>
       <c r="R278" s="59" t="e">
-        <f t="shared" si="201"/>
+        <f t="shared" si="202"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S278" s="94"/>
@@ -22717,33 +22713,33 @@
       <c r="H279" s="366"/>
       <c r="I279" s="366"/>
       <c r="J279" s="93">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0</v>
       </c>
       <c r="K279" s="369"/>
       <c r="L279" s="55">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>0</v>
       </c>
       <c r="M279" s="56" t="e">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N279" s="57" t="e">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O279" s="57" t="e">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P279" s="58" t="e">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q279" s="367"/>
       <c r="R279" s="59" t="e">
-        <f t="shared" si="201"/>
+        <f t="shared" si="202"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S279" s="94"/>
@@ -22765,33 +22761,33 @@
       <c r="H280" s="366"/>
       <c r="I280" s="366"/>
       <c r="J280" s="93">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0</v>
       </c>
       <c r="K280" s="369"/>
       <c r="L280" s="55">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>0</v>
       </c>
       <c r="M280" s="56" t="e">
-        <f t="shared" ref="M280:M286" si="202">L280/K280</f>
+        <f t="shared" ref="M280:M286" si="203">L280/K280</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N280" s="57" t="e">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O280" s="57" t="e">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P280" s="58" t="e">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q280" s="367"/>
       <c r="R280" s="59" t="e">
-        <f t="shared" si="201"/>
+        <f t="shared" si="202"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S280" s="94"/>
@@ -22813,33 +22809,33 @@
       <c r="H281" s="366"/>
       <c r="I281" s="366"/>
       <c r="J281" s="93">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0</v>
       </c>
       <c r="K281" s="369"/>
       <c r="L281" s="55">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>0</v>
       </c>
       <c r="M281" s="56" t="e">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N281" s="57" t="e">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O281" s="57" t="e">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P281" s="58" t="e">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q281" s="367"/>
       <c r="R281" s="59" t="e">
-        <f t="shared" si="201"/>
+        <f t="shared" si="202"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S281" s="94"/>
@@ -22861,33 +22857,33 @@
       <c r="H282" s="366"/>
       <c r="I282" s="366"/>
       <c r="J282" s="93">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0</v>
       </c>
       <c r="K282" s="369"/>
       <c r="L282" s="55">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>0</v>
       </c>
       <c r="M282" s="56" t="e">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N282" s="57" t="e">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O282" s="57" t="e">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P282" s="58" t="e">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q282" s="367"/>
       <c r="R282" s="59" t="e">
-        <f t="shared" si="201"/>
+        <f t="shared" si="202"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S282" s="94"/>
@@ -22909,33 +22905,33 @@
       <c r="H283" s="366"/>
       <c r="I283" s="366"/>
       <c r="J283" s="93">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0</v>
       </c>
       <c r="K283" s="369"/>
       <c r="L283" s="55">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>0</v>
       </c>
       <c r="M283" s="56" t="e">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N283" s="57" t="e">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O283" s="57" t="e">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P283" s="58" t="e">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q283" s="367"/>
       <c r="R283" s="59" t="e">
-        <f t="shared" si="201"/>
+        <f t="shared" si="202"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S283" s="94"/>
@@ -22960,33 +22956,33 @@
         <v>0</v>
       </c>
       <c r="J284" s="93">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0</v>
       </c>
       <c r="K284" s="369"/>
       <c r="L284" s="55">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>0</v>
       </c>
       <c r="M284" s="56" t="e">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N284" s="57" t="e">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O284" s="57" t="e">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P284" s="58" t="e">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q284" s="367"/>
       <c r="R284" s="59" t="e">
-        <f t="shared" si="201"/>
+        <f t="shared" si="202"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S284" s="94"/>
@@ -23008,33 +23004,33 @@
       <c r="H285" s="366"/>
       <c r="I285" s="366"/>
       <c r="J285" s="93">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0</v>
       </c>
       <c r="K285" s="369"/>
       <c r="L285" s="55">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>0</v>
       </c>
       <c r="M285" s="56" t="e">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N285" s="57" t="e">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O285" s="57" t="e">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P285" s="58" t="e">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q285" s="367"/>
       <c r="R285" s="59" t="e">
-        <f t="shared" si="201"/>
+        <f t="shared" si="202"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S285" s="94"/>
@@ -23056,33 +23052,33 @@
       <c r="H286" s="366"/>
       <c r="I286" s="366"/>
       <c r="J286" s="93">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0</v>
       </c>
       <c r="K286" s="369"/>
       <c r="L286" s="55">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>0</v>
       </c>
       <c r="M286" s="56" t="e">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N286" s="57" t="e">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O286" s="57" t="e">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P286" s="58" t="e">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q286" s="367"/>
       <c r="R286" s="59" t="e">
-        <f t="shared" si="201"/>
+        <f t="shared" si="202"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S286" s="94"/>
@@ -23117,7 +23113,7 @@
         <v>0</v>
       </c>
       <c r="M287" s="333" t="e">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N287" s="47"/>
@@ -23147,33 +23143,33 @@
       <c r="H288" s="366"/>
       <c r="I288" s="366"/>
       <c r="J288" s="55">
-        <f t="shared" ref="J288:J300" si="203">G288+H288-I288</f>
+        <f t="shared" ref="J288:J300" si="204">G288+H288-I288</f>
         <v>0</v>
       </c>
       <c r="K288" s="369"/>
       <c r="L288" s="55">
-        <f t="shared" ref="L288:L300" si="204">J288-K288</f>
+        <f t="shared" ref="L288:L300" si="205">J288-K288</f>
         <v>0</v>
       </c>
       <c r="M288" s="56" t="e">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N288" s="57" t="e">
-        <f t="shared" ref="N288:N300" si="205">G288/$N$12</f>
+        <f t="shared" ref="N288:N300" si="206">G288/$N$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O288" s="57" t="e">
-        <f t="shared" ref="O288:O300" si="206">G288*12/CurMonths/$O$12</f>
+        <f t="shared" ref="O288:O300" si="207">G288*12/CurMonths/$O$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P288" s="58" t="e">
-        <f t="shared" ref="P288:P300" si="207">IF(ABS(O288)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P288:P300" si="208">IF(ABS(O288)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q288" s="367"/>
       <c r="R288" s="59" t="e">
-        <f t="shared" ref="R288:R300" si="208">IF(P288="O","O",IF(Q288="O","O","X"))</f>
+        <f t="shared" ref="R288:R300" si="209">IF(P288="O","O",IF(Q288="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S288" s="94"/>
@@ -23195,33 +23191,33 @@
       <c r="H289" s="366"/>
       <c r="I289" s="366"/>
       <c r="J289" s="55">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="K289" s="369"/>
       <c r="L289" s="55">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0</v>
       </c>
       <c r="M289" s="56" t="e">
-        <f t="shared" ref="M289:M300" si="209">L289/K289</f>
+        <f t="shared" ref="M289:M300" si="210">L289/K289</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N289" s="57" t="e">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O289" s="57" t="e">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P289" s="58" t="e">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q289" s="367"/>
       <c r="R289" s="59" t="e">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S289" s="343"/>
@@ -23243,33 +23239,33 @@
       <c r="H290" s="366"/>
       <c r="I290" s="366"/>
       <c r="J290" s="55">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="K290" s="369"/>
       <c r="L290" s="55">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0</v>
       </c>
       <c r="M290" s="56" t="e">
-        <f t="shared" si="209"/>
+        <f t="shared" si="210"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N290" s="57" t="e">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O290" s="57" t="e">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P290" s="58" t="e">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q290" s="367"/>
       <c r="R290" s="59" t="e">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S290" s="343"/>
@@ -23291,33 +23287,33 @@
       <c r="H291" s="366"/>
       <c r="I291" s="366"/>
       <c r="J291" s="55">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="K291" s="369"/>
       <c r="L291" s="55">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0</v>
       </c>
       <c r="M291" s="56" t="e">
-        <f t="shared" si="209"/>
+        <f t="shared" si="210"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N291" s="57" t="e">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O291" s="57" t="e">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P291" s="58" t="e">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q291" s="367"/>
       <c r="R291" s="59" t="e">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S291" s="343"/>
@@ -23339,33 +23335,33 @@
       <c r="H292" s="366"/>
       <c r="I292" s="366"/>
       <c r="J292" s="55">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="K292" s="369"/>
       <c r="L292" s="55">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0</v>
       </c>
       <c r="M292" s="56" t="e">
-        <f t="shared" si="209"/>
+        <f t="shared" si="210"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N292" s="57" t="e">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O292" s="57" t="e">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P292" s="58" t="e">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q292" s="367"/>
       <c r="R292" s="59" t="e">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S292" s="343"/>
@@ -23387,33 +23383,33 @@
       <c r="H293" s="366"/>
       <c r="I293" s="366"/>
       <c r="J293" s="55">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="K293" s="369"/>
       <c r="L293" s="55">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0</v>
       </c>
       <c r="M293" s="56" t="e">
-        <f t="shared" si="209"/>
+        <f t="shared" si="210"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N293" s="57" t="e">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O293" s="57" t="e">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P293" s="58" t="e">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q293" s="367"/>
       <c r="R293" s="59" t="e">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S293" s="343"/>
@@ -23435,33 +23431,33 @@
       <c r="H294" s="366"/>
       <c r="I294" s="366"/>
       <c r="J294" s="55">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="K294" s="369"/>
       <c r="L294" s="55">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0</v>
       </c>
       <c r="M294" s="56" t="e">
-        <f t="shared" si="209"/>
+        <f t="shared" si="210"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N294" s="57" t="e">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O294" s="57" t="e">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P294" s="58" t="e">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q294" s="367"/>
       <c r="R294" s="59" t="e">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S294" s="343"/>
@@ -23483,33 +23479,33 @@
       <c r="H295" s="366"/>
       <c r="I295" s="366"/>
       <c r="J295" s="55">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="K295" s="369"/>
       <c r="L295" s="55">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0</v>
       </c>
       <c r="M295" s="56" t="e">
-        <f t="shared" si="209"/>
+        <f t="shared" si="210"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N295" s="57" t="e">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O295" s="57" t="e">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P295" s="58" t="e">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q295" s="367"/>
       <c r="R295" s="59" t="e">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S295" s="343"/>
@@ -23531,33 +23527,33 @@
       <c r="H296" s="366"/>
       <c r="I296" s="366"/>
       <c r="J296" s="55">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="K296" s="369"/>
       <c r="L296" s="55">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0</v>
       </c>
       <c r="M296" s="56" t="e">
-        <f t="shared" si="209"/>
+        <f t="shared" si="210"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N296" s="57" t="e">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O296" s="57" t="e">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P296" s="58" t="e">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q296" s="367"/>
       <c r="R296" s="59" t="e">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S296" s="343"/>
@@ -23579,33 +23575,33 @@
       <c r="H297" s="366"/>
       <c r="I297" s="366"/>
       <c r="J297" s="55">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="K297" s="369"/>
       <c r="L297" s="55">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0</v>
       </c>
       <c r="M297" s="56" t="e">
-        <f t="shared" si="209"/>
+        <f t="shared" si="210"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N297" s="57" t="e">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O297" s="57" t="e">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P297" s="58" t="e">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q297" s="367"/>
       <c r="R297" s="59" t="e">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S297" s="343"/>
@@ -23627,33 +23623,33 @@
       <c r="H298" s="366"/>
       <c r="I298" s="366"/>
       <c r="J298" s="55">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="K298" s="369"/>
       <c r="L298" s="55">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0</v>
       </c>
       <c r="M298" s="56" t="e">
-        <f t="shared" si="209"/>
+        <f t="shared" si="210"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N298" s="57" t="e">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O298" s="57" t="e">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P298" s="58" t="e">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q298" s="367"/>
       <c r="R298" s="59" t="e">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S298" s="343"/>
@@ -23675,33 +23671,33 @@
       <c r="H299" s="366"/>
       <c r="I299" s="366"/>
       <c r="J299" s="55">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="K299" s="369"/>
       <c r="L299" s="55">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0</v>
       </c>
       <c r="M299" s="56" t="e">
-        <f t="shared" si="209"/>
+        <f t="shared" si="210"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N299" s="57" t="e">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O299" s="57" t="e">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P299" s="58" t="e">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q299" s="367"/>
       <c r="R299" s="59" t="e">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S299" s="343"/>
@@ -23723,33 +23719,33 @@
       <c r="H300" s="366"/>
       <c r="I300" s="366"/>
       <c r="J300" s="55">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="K300" s="369"/>
       <c r="L300" s="55">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0</v>
       </c>
       <c r="M300" s="56" t="e">
-        <f t="shared" si="209"/>
+        <f t="shared" si="210"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N300" s="57" t="e">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O300" s="57" t="e">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P300" s="58" t="e">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q300" s="367"/>
       <c r="R300" s="59" t="e">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S300" s="343"/>
@@ -23787,7 +23783,7 @@
         <v>0</v>
       </c>
       <c r="M301" s="333" t="e">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N301" s="56"/>
@@ -23814,33 +23810,33 @@
       <c r="H302" s="366"/>
       <c r="I302" s="366"/>
       <c r="J302" s="55">
-        <f t="shared" ref="J302:J314" si="210">G302+H302-I302</f>
+        <f t="shared" ref="J302:J314" si="211">G302+H302-I302</f>
         <v>0</v>
       </c>
       <c r="K302" s="369"/>
       <c r="L302" s="55">
-        <f t="shared" ref="L302:L313" si="211">J302-K302</f>
+        <f t="shared" ref="L302:L313" si="212">J302-K302</f>
         <v>0</v>
       </c>
       <c r="M302" s="56" t="e">
-        <f t="shared" ref="M302:M313" si="212">L302/K302</f>
+        <f t="shared" ref="M302:M313" si="213">L302/K302</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N302" s="57" t="e">
-        <f t="shared" ref="N302:N314" si="213">G302/$N$12</f>
+        <f t="shared" ref="N302:N314" si="214">G302/$N$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O302" s="57" t="e">
-        <f t="shared" ref="O302:O314" si="214">G302*12/CurMonths/$O$12</f>
+        <f t="shared" ref="O302:O314" si="215">G302*12/CurMonths/$O$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P302" s="58" t="e">
-        <f t="shared" ref="P302:P313" si="215">IF(ABS(O302)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P302:P313" si="216">IF(ABS(O302)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q302" s="367"/>
       <c r="R302" s="59" t="e">
-        <f t="shared" ref="R302:R313" si="216">IF(P302="O","O",IF(Q302="O","O","X"))</f>
+        <f t="shared" ref="R302:R313" si="217">IF(P302="O","O",IF(Q302="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S302" s="94"/>
@@ -23865,33 +23861,33 @@
       <c r="H303" s="366"/>
       <c r="I303" s="366"/>
       <c r="J303" s="55">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>0</v>
       </c>
       <c r="K303" s="369"/>
       <c r="L303" s="55">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>0</v>
       </c>
       <c r="M303" s="56" t="e">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N303" s="57" t="e">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O303" s="57" t="e">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P303" s="58" t="e">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q303" s="367"/>
       <c r="R303" s="59" t="e">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S303" s="94"/>
@@ -23913,33 +23909,33 @@
       <c r="H304" s="366"/>
       <c r="I304" s="366"/>
       <c r="J304" s="55">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>0</v>
       </c>
       <c r="K304" s="369"/>
       <c r="L304" s="55">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>0</v>
       </c>
       <c r="M304" s="56" t="e">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N304" s="57" t="e">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O304" s="57" t="e">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P304" s="58" t="e">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q304" s="367"/>
       <c r="R304" s="59" t="e">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S304" s="94"/>
@@ -23961,33 +23957,33 @@
       <c r="H305" s="366"/>
       <c r="I305" s="366"/>
       <c r="J305" s="55">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>0</v>
       </c>
       <c r="K305" s="369"/>
       <c r="L305" s="55">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>0</v>
       </c>
       <c r="M305" s="56" t="e">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N305" s="57" t="e">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O305" s="57" t="e">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P305" s="58" t="e">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q305" s="367"/>
       <c r="R305" s="59" t="e">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S305" s="94"/>
@@ -24009,33 +24005,33 @@
       <c r="H306" s="366"/>
       <c r="I306" s="366"/>
       <c r="J306" s="55">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>0</v>
       </c>
       <c r="K306" s="369"/>
       <c r="L306" s="55">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>0</v>
       </c>
       <c r="M306" s="56" t="e">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N306" s="57" t="e">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O306" s="57" t="e">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P306" s="58" t="e">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q306" s="367"/>
       <c r="R306" s="59" t="e">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S306" s="94"/>
@@ -24057,33 +24053,33 @@
       <c r="H307" s="366"/>
       <c r="I307" s="366"/>
       <c r="J307" s="55">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>0</v>
       </c>
       <c r="K307" s="369"/>
       <c r="L307" s="55">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>0</v>
       </c>
       <c r="M307" s="56" t="e">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N307" s="57" t="e">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O307" s="57" t="e">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P307" s="58" t="e">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q307" s="367"/>
       <c r="R307" s="59" t="e">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S307" s="94"/>
@@ -24105,33 +24101,33 @@
       <c r="H308" s="366"/>
       <c r="I308" s="366"/>
       <c r="J308" s="55">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>0</v>
       </c>
       <c r="K308" s="369"/>
       <c r="L308" s="55">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>0</v>
       </c>
       <c r="M308" s="56" t="e">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N308" s="57" t="e">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O308" s="57" t="e">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P308" s="58" t="e">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q308" s="367"/>
       <c r="R308" s="59" t="e">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S308" s="94"/>
@@ -24153,33 +24149,33 @@
       <c r="H309" s="366"/>
       <c r="I309" s="366"/>
       <c r="J309" s="55">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>0</v>
       </c>
       <c r="K309" s="369"/>
       <c r="L309" s="55">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>0</v>
       </c>
       <c r="M309" s="56" t="e">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N309" s="57" t="e">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O309" s="57" t="e">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P309" s="58" t="e">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q309" s="367"/>
       <c r="R309" s="59" t="e">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S309" s="94"/>
@@ -24201,33 +24197,33 @@
       <c r="H310" s="366"/>
       <c r="I310" s="366"/>
       <c r="J310" s="55">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>0</v>
       </c>
       <c r="K310" s="369"/>
       <c r="L310" s="55">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>0</v>
       </c>
       <c r="M310" s="56" t="e">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N310" s="57" t="e">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O310" s="57" t="e">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P310" s="58" t="e">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q310" s="367"/>
       <c r="R310" s="59" t="e">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S310" s="94"/>
@@ -24249,33 +24245,33 @@
       <c r="H311" s="366"/>
       <c r="I311" s="366"/>
       <c r="J311" s="55">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>0</v>
       </c>
       <c r="K311" s="369"/>
       <c r="L311" s="55">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>0</v>
       </c>
       <c r="M311" s="56" t="e">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N311" s="57" t="e">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O311" s="57" t="e">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P311" s="58" t="e">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q311" s="367"/>
       <c r="R311" s="59" t="e">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S311" s="94"/>
@@ -24297,33 +24293,33 @@
       <c r="H312" s="366"/>
       <c r="I312" s="366"/>
       <c r="J312" s="55">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>0</v>
       </c>
       <c r="K312" s="369"/>
       <c r="L312" s="55">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>0</v>
       </c>
       <c r="M312" s="56" t="e">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N312" s="57" t="e">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O312" s="57" t="e">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P312" s="58" t="e">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q312" s="367"/>
       <c r="R312" s="59" t="e">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S312" s="94"/>
@@ -24345,33 +24341,33 @@
       <c r="H313" s="366"/>
       <c r="I313" s="366"/>
       <c r="J313" s="55">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>0</v>
       </c>
       <c r="K313" s="369"/>
       <c r="L313" s="55">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>0</v>
       </c>
       <c r="M313" s="56" t="e">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N313" s="57" t="e">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O313" s="57" t="e">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P313" s="58" t="e">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q313" s="367"/>
       <c r="R313" s="59" t="e">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S313" s="94"/>
@@ -24393,33 +24389,33 @@
       <c r="H314" s="366"/>
       <c r="I314" s="366"/>
       <c r="J314" s="55">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>0</v>
       </c>
       <c r="K314" s="369"/>
       <c r="L314" s="55">
-        <f t="shared" ref="L314" si="217">J314-K314</f>
+        <f t="shared" ref="L314" si="218">J314-K314</f>
         <v>0</v>
       </c>
       <c r="M314" s="56" t="e">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N314" s="57" t="e">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O314" s="57" t="e">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P314" s="58" t="e">
-        <f t="shared" ref="P314" si="218">IF(ABS(O314)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P314" si="219">IF(ABS(O314)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q314" s="367"/>
       <c r="R314" s="59" t="e">
-        <f t="shared" ref="R314" si="219">IF(P314="O","O",IF(Q314="O","O","X"))</f>
+        <f t="shared" ref="R314" si="220">IF(P314="O","O",IF(Q314="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S314" s="94"/>
@@ -24454,7 +24450,7 @@
         <v>0</v>
       </c>
       <c r="M315" s="333" t="e">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N315" s="47"/>
@@ -24835,7 +24831,7 @@
         <v>0</v>
       </c>
       <c r="M324" s="56" t="e">
-        <f t="shared" ref="M324:M327" si="220">L324/K324</f>
+        <f t="shared" ref="M324:M327" si="221">L324/K324</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N324" s="57" t="e">
@@ -24847,12 +24843,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="P324" s="58" t="e">
-        <f t="shared" ref="P324:P327" si="221">IF(ABS(O324)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P324:P327" si="222">IF(ABS(O324)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q324" s="367"/>
       <c r="R324" s="59" t="e">
-        <f t="shared" ref="R324:R327" si="222">IF(P324="O","O",IF(Q324="O","O","X"))</f>
+        <f t="shared" ref="R324:R327" si="223">IF(P324="O","O",IF(Q324="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S324" s="348"/>
@@ -24883,7 +24879,7 @@
         <v>0</v>
       </c>
       <c r="M325" s="56" t="e">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N325" s="57" t="e">
@@ -24895,12 +24891,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="P325" s="58" t="e">
-        <f t="shared" si="221"/>
+        <f t="shared" si="222"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q325" s="367"/>
       <c r="R325" s="59" t="e">
-        <f t="shared" si="222"/>
+        <f t="shared" si="223"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S325" s="348"/>
@@ -24929,7 +24925,7 @@
         <v>0</v>
       </c>
       <c r="M326" s="56" t="e">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N326" s="57" t="e">
@@ -24941,12 +24937,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="P326" s="58" t="e">
-        <f t="shared" si="221"/>
+        <f t="shared" si="222"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q326" s="367"/>
       <c r="R326" s="59" t="e">
-        <f t="shared" si="222"/>
+        <f t="shared" si="223"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S326" s="348"/>
@@ -24975,7 +24971,7 @@
         <v>0</v>
       </c>
       <c r="M327" s="56" t="e">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N327" s="57" t="e">
@@ -24987,12 +24983,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="P327" s="58" t="e">
-        <f t="shared" si="221"/>
+        <f t="shared" si="222"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q327" s="367"/>
       <c r="R327" s="59" t="e">
-        <f t="shared" si="222"/>
+        <f t="shared" si="223"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S327" s="348"/>
@@ -25246,7 +25242,7 @@
         <v>0</v>
       </c>
       <c r="M334" s="333" t="e">
-        <f t="shared" ref="M334:M373" si="223">L334/K334</f>
+        <f t="shared" ref="M334:M373" si="224">L334/K334</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N334" s="47"/>
@@ -25274,33 +25270,33 @@
       <c r="H335" s="358"/>
       <c r="I335" s="358"/>
       <c r="J335" s="55">
-        <f t="shared" ref="J335:J340" si="224">G335+H335-I335</f>
+        <f t="shared" ref="J335:J340" si="225">G335+H335-I335</f>
         <v>0</v>
       </c>
       <c r="K335" s="358"/>
       <c r="L335" s="55">
-        <f t="shared" ref="L335:L340" si="225">J335-K335</f>
+        <f t="shared" ref="L335:L340" si="226">J335-K335</f>
         <v>0</v>
       </c>
       <c r="M335" s="56" t="e">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N335" s="123" t="e">
-        <f t="shared" ref="N335:N340" si="226">G335/$N$12</f>
+        <f t="shared" ref="N335:N340" si="227">G335/$N$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O335" s="57" t="e">
-        <f t="shared" ref="O335:O340" si="227">G335*12/CurMonths/$O$12</f>
+        <f t="shared" ref="O335:O340" si="228">G335*12/CurMonths/$O$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P335" s="124" t="e">
-        <f t="shared" ref="P335:P351" si="228">IF(ABS(O335)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P335:P351" si="229">IF(ABS(O335)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q335" s="376"/>
       <c r="R335" s="124" t="e">
-        <f t="shared" ref="R335:R339" si="229">IF(P335="O","O",IF(Q335="O","O","X"))</f>
+        <f t="shared" ref="R335:R339" si="230">IF(P335="O","O",IF(Q335="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S335" s="129"/>
@@ -25323,33 +25319,33 @@
       <c r="H336" s="358"/>
       <c r="I336" s="358"/>
       <c r="J336" s="55">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>0</v>
       </c>
       <c r="K336" s="358"/>
       <c r="L336" s="55">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>0</v>
       </c>
       <c r="M336" s="56" t="e">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N336" s="123" t="e">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O336" s="57" t="e">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P336" s="124" t="e">
-        <f t="shared" si="228"/>
+        <f t="shared" si="229"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q336" s="376"/>
       <c r="R336" s="124" t="e">
-        <f t="shared" si="229"/>
+        <f t="shared" si="230"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S336" s="133"/>
@@ -25369,33 +25365,33 @@
       <c r="H337" s="358"/>
       <c r="I337" s="358"/>
       <c r="J337" s="55">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>0</v>
       </c>
       <c r="K337" s="358"/>
       <c r="L337" s="55">
-        <f t="shared" ref="L337" si="230">J337-K337</f>
+        <f t="shared" ref="L337" si="231">J337-K337</f>
         <v>0</v>
       </c>
       <c r="M337" s="56" t="e">
-        <f t="shared" ref="M337" si="231">L337/K337</f>
+        <f t="shared" ref="M337" si="232">L337/K337</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N337" s="123" t="e">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O337" s="57" t="e">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P337" s="124" t="e">
-        <f t="shared" ref="P337" si="232">IF(ABS(O337)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P337" si="233">IF(ABS(O337)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q337" s="376"/>
       <c r="R337" s="124" t="e">
-        <f t="shared" ref="R337" si="233">IF(P337="O","O",IF(Q337="O","O","X"))</f>
+        <f t="shared" ref="R337" si="234">IF(P337="O","O",IF(Q337="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S337" s="133"/>
@@ -25415,28 +25411,28 @@
       <c r="H338" s="358"/>
       <c r="I338" s="358"/>
       <c r="J338" s="55">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>0</v>
       </c>
       <c r="K338" s="358"/>
       <c r="L338" s="55">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>0</v>
       </c>
       <c r="M338" s="56" t="e">
-        <f t="shared" ref="M338" si="234">L338/K338</f>
+        <f t="shared" ref="M338" si="235">L338/K338</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N338" s="123" t="e">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O338" s="57" t="e">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P338" s="124" t="e">
-        <f t="shared" ref="P338" si="235">IF(ABS(O338)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P338" si="236">IF(ABS(O338)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q338" s="376"/>
@@ -25461,33 +25457,33 @@
       <c r="H339" s="358"/>
       <c r="I339" s="358"/>
       <c r="J339" s="55">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>0</v>
       </c>
       <c r="K339" s="358"/>
       <c r="L339" s="55">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>0</v>
       </c>
       <c r="M339" s="56" t="e">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N339" s="123" t="e">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O339" s="57" t="e">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P339" s="124" t="e">
-        <f t="shared" si="228"/>
+        <f t="shared" si="229"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q339" s="376"/>
       <c r="R339" s="124" t="e">
-        <f t="shared" si="229"/>
+        <f t="shared" si="230"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S339" s="94"/>
@@ -25507,28 +25503,28 @@
       <c r="H340" s="377"/>
       <c r="I340" s="377"/>
       <c r="J340" s="332">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>0</v>
       </c>
       <c r="K340" s="377"/>
       <c r="L340" s="332">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>0</v>
       </c>
       <c r="M340" s="333" t="e">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N340" s="123" t="e">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O340" s="292" t="e">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P340" s="124" t="e">
-        <f t="shared" si="228"/>
+        <f t="shared" si="229"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q340" s="376"/>
@@ -25568,7 +25564,7 @@
         <v>0</v>
       </c>
       <c r="M341" s="333" t="e">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N341" s="47"/>
@@ -25596,33 +25592,33 @@
       <c r="H342" s="358"/>
       <c r="I342" s="358"/>
       <c r="J342" s="55">
-        <f t="shared" ref="J342:J347" si="236">G342+H342-I342</f>
+        <f t="shared" ref="J342:J347" si="237">G342+H342-I342</f>
         <v>0</v>
       </c>
       <c r="K342" s="358"/>
       <c r="L342" s="55">
-        <f t="shared" ref="L342:L344" si="237">J342-K342</f>
+        <f t="shared" ref="L342:L344" si="238">J342-K342</f>
         <v>0</v>
       </c>
       <c r="M342" s="56" t="e">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N342" s="123" t="e">
-        <f t="shared" ref="N342:N347" si="238">G342/$N$12</f>
+        <f t="shared" ref="N342:N347" si="239">G342/$N$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O342" s="57" t="e">
-        <f t="shared" ref="O342:O347" si="239">G342*12/CurMonths/$O$12</f>
+        <f t="shared" ref="O342:O347" si="240">G342*12/CurMonths/$O$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P342" s="124" t="e">
-        <f t="shared" si="228"/>
+        <f t="shared" si="229"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q342" s="376"/>
       <c r="R342" s="124" t="e">
-        <f t="shared" ref="R342:R344" si="240">IF(P342="O","O",IF(Q342="O","O","X"))</f>
+        <f t="shared" ref="R342:R344" si="241">IF(P342="O","O",IF(Q342="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S342" s="94"/>
@@ -25645,33 +25641,33 @@
       <c r="H343" s="358"/>
       <c r="I343" s="358"/>
       <c r="J343" s="55">
-        <f t="shared" si="236"/>
+        <f t="shared" si="237"/>
         <v>0</v>
       </c>
       <c r="K343" s="358"/>
       <c r="L343" s="55">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>0</v>
       </c>
       <c r="M343" s="56" t="e">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N343" s="123" t="e">
-        <f t="shared" si="238"/>
+        <f t="shared" si="239"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O343" s="57" t="e">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P343" s="124" t="e">
-        <f t="shared" si="228"/>
+        <f t="shared" si="229"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q343" s="376"/>
       <c r="R343" s="124" t="e">
-        <f t="shared" si="240"/>
+        <f t="shared" si="241"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S343" s="94"/>
@@ -25691,33 +25687,33 @@
       <c r="H344" s="358"/>
       <c r="I344" s="358"/>
       <c r="J344" s="55">
-        <f t="shared" si="236"/>
+        <f t="shared" si="237"/>
         <v>0</v>
       </c>
       <c r="K344" s="358"/>
       <c r="L344" s="55">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>0</v>
       </c>
       <c r="M344" s="56" t="e">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N344" s="123" t="e">
-        <f t="shared" si="238"/>
+        <f t="shared" si="239"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O344" s="57" t="e">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P344" s="124" t="e">
-        <f t="shared" si="228"/>
+        <f t="shared" si="229"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q344" s="376"/>
       <c r="R344" s="124" t="e">
-        <f t="shared" si="240"/>
+        <f t="shared" si="241"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S344" s="133"/>
@@ -25737,33 +25733,33 @@
       <c r="H345" s="358"/>
       <c r="I345" s="358"/>
       <c r="J345" s="55">
-        <f t="shared" si="236"/>
+        <f t="shared" si="237"/>
         <v>0</v>
       </c>
       <c r="K345" s="358"/>
       <c r="L345" s="55">
-        <f t="shared" ref="L345:L347" si="241">J345-K345</f>
+        <f t="shared" ref="L345:L347" si="242">J345-K345</f>
         <v>0</v>
       </c>
       <c r="M345" s="56" t="e">
-        <f t="shared" ref="M345:M347" si="242">L345/K345</f>
+        <f t="shared" ref="M345:M347" si="243">L345/K345</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N345" s="123" t="e">
-        <f t="shared" si="238"/>
+        <f t="shared" si="239"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O345" s="292" t="e">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P345" s="124" t="e">
-        <f t="shared" ref="P345:P347" si="243">IF(ABS(O345)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P345:P347" si="244">IF(ABS(O345)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q345" s="376"/>
       <c r="R345" s="124" t="e">
-        <f t="shared" ref="R345:R347" si="244">IF(P345="O","O",IF(Q345="O","O","X"))</f>
+        <f t="shared" ref="R345:R347" si="245">IF(P345="O","O",IF(Q345="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S345" s="133"/>
@@ -25783,33 +25779,33 @@
       <c r="H346" s="358"/>
       <c r="I346" s="358"/>
       <c r="J346" s="55">
-        <f t="shared" si="236"/>
+        <f t="shared" si="237"/>
         <v>0</v>
       </c>
       <c r="K346" s="358"/>
       <c r="L346" s="55">
-        <f t="shared" si="241"/>
+        <f t="shared" si="242"/>
         <v>0</v>
       </c>
       <c r="M346" s="56" t="e">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N346" s="123" t="e">
-        <f t="shared" si="238"/>
+        <f t="shared" si="239"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O346" s="292" t="e">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P346" s="124" t="e">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q346" s="376"/>
       <c r="R346" s="124" t="e">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S346" s="133"/>
@@ -25829,33 +25825,33 @@
       <c r="H347" s="358"/>
       <c r="I347" s="358"/>
       <c r="J347" s="55">
-        <f t="shared" si="236"/>
+        <f t="shared" si="237"/>
         <v>0</v>
       </c>
       <c r="K347" s="358"/>
       <c r="L347" s="55">
-        <f t="shared" si="241"/>
+        <f t="shared" si="242"/>
         <v>0</v>
       </c>
       <c r="M347" s="56" t="e">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N347" s="123" t="e">
-        <f t="shared" si="238"/>
+        <f t="shared" si="239"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O347" s="292" t="e">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P347" s="124" t="e">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q347" s="376"/>
       <c r="R347" s="124" t="e">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S347" s="133"/>
@@ -25893,7 +25889,7 @@
         <v>0</v>
       </c>
       <c r="M348" s="333" t="e">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N348" s="47"/>
@@ -25921,33 +25917,33 @@
       <c r="H349" s="358"/>
       <c r="I349" s="358"/>
       <c r="J349" s="55">
-        <f t="shared" ref="J349:J367" si="245">G349+H349-I349</f>
+        <f t="shared" ref="J349:J367" si="246">G349+H349-I349</f>
         <v>0</v>
       </c>
       <c r="K349" s="358"/>
       <c r="L349" s="55">
-        <f t="shared" ref="L349:L373" si="246">J349-K349</f>
+        <f t="shared" ref="L349:L373" si="247">J349-K349</f>
         <v>0</v>
       </c>
       <c r="M349" s="56" t="e">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N349" s="123" t="e">
-        <f t="shared" ref="N349:N367" si="247">G349/$N$12</f>
+        <f t="shared" ref="N349:N367" si="248">G349/$N$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O349" s="57" t="e">
-        <f t="shared" ref="O349:O367" si="248">G349*12/CurMonths/$O$12</f>
+        <f t="shared" ref="O349:O367" si="249">G349*12/CurMonths/$O$12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P349" s="124" t="e">
-        <f t="shared" si="228"/>
+        <f t="shared" si="229"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q349" s="376"/>
       <c r="R349" s="124" t="e">
-        <f t="shared" ref="R349:R351" si="249">IF(P349="O","O",IF(Q349="O","O","X"))</f>
+        <f t="shared" ref="R349:R351" si="250">IF(P349="O","O",IF(Q349="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S349" s="94"/>
@@ -25970,33 +25966,33 @@
       <c r="H350" s="358"/>
       <c r="I350" s="358"/>
       <c r="J350" s="55">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K350" s="358"/>
       <c r="L350" s="55">
-        <f t="shared" si="246"/>
+        <f t="shared" si="247"/>
         <v>0</v>
       </c>
       <c r="M350" s="56" t="e">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N350" s="123" t="e">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O350" s="57" t="e">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P350" s="124" t="e">
-        <f t="shared" si="228"/>
+        <f t="shared" si="229"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q350" s="376"/>
       <c r="R350" s="124" t="e">
-        <f t="shared" si="249"/>
+        <f t="shared" si="250"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S350" s="94"/>
@@ -26019,33 +26015,33 @@
       <c r="H351" s="358"/>
       <c r="I351" s="358"/>
       <c r="J351" s="55">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K351" s="358"/>
       <c r="L351" s="55">
-        <f t="shared" si="246"/>
+        <f t="shared" si="247"/>
         <v>0</v>
       </c>
       <c r="M351" s="56" t="e">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N351" s="123" t="e">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O351" s="57" t="e">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P351" s="124" t="e">
-        <f t="shared" si="228"/>
+        <f t="shared" si="229"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q351" s="376"/>
       <c r="R351" s="124" t="e">
-        <f t="shared" si="249"/>
+        <f t="shared" si="250"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S351" s="94"/>
@@ -26065,33 +26061,33 @@
       <c r="H352" s="358"/>
       <c r="I352" s="358"/>
       <c r="J352" s="55">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K352" s="358"/>
       <c r="L352" s="55">
-        <f t="shared" si="246"/>
+        <f t="shared" si="247"/>
         <v>0</v>
       </c>
       <c r="M352" s="56" t="e">
-        <f t="shared" ref="M352:M353" si="250">L352/K352</f>
+        <f t="shared" ref="M352:M353" si="251">L352/K352</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N352" s="123" t="e">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O352" s="57" t="e">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P352" s="124" t="e">
-        <f t="shared" ref="P352:P353" si="251">IF(ABS(O352)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P352:P353" si="252">IF(ABS(O352)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q352" s="376"/>
       <c r="R352" s="124" t="e">
-        <f t="shared" ref="R352:R353" si="252">IF(P352="O","O",IF(Q352="O","O","X"))</f>
+        <f t="shared" ref="R352:R353" si="253">IF(P352="O","O",IF(Q352="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S352" s="94"/>
@@ -26111,33 +26107,33 @@
       <c r="H353" s="358"/>
       <c r="I353" s="358"/>
       <c r="J353" s="55">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K353" s="358"/>
       <c r="L353" s="55">
-        <f t="shared" si="246"/>
+        <f t="shared" si="247"/>
         <v>0</v>
       </c>
       <c r="M353" s="56" t="e">
-        <f t="shared" si="250"/>
+        <f t="shared" si="251"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N353" s="123" t="e">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O353" s="57" t="e">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P353" s="124" t="e">
-        <f t="shared" si="251"/>
+        <f t="shared" si="252"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q353" s="376"/>
       <c r="R353" s="124" t="e">
-        <f t="shared" si="252"/>
+        <f t="shared" si="253"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S353" s="94"/>
@@ -26157,33 +26153,33 @@
       <c r="H354" s="358"/>
       <c r="I354" s="358"/>
       <c r="J354" s="55">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K354" s="358"/>
       <c r="L354" s="55">
-        <f t="shared" ref="L354:L367" si="253">J354-K354</f>
+        <f t="shared" ref="L354:L367" si="254">J354-K354</f>
         <v>0</v>
       </c>
       <c r="M354" s="56" t="e">
-        <f t="shared" ref="M354:M367" si="254">L354/K354</f>
+        <f t="shared" ref="M354:M367" si="255">L354/K354</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N354" s="123" t="e">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O354" s="57" t="e">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P354" s="124" t="e">
-        <f t="shared" ref="P354:P367" si="255">IF(ABS(O354)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P354:P367" si="256">IF(ABS(O354)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q354" s="376"/>
       <c r="R354" s="124" t="e">
-        <f t="shared" ref="R354:R367" si="256">IF(P354="O","O",IF(Q354="O","O","X"))</f>
+        <f t="shared" ref="R354:R367" si="257">IF(P354="O","O",IF(Q354="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S354" s="94"/>
@@ -26203,33 +26199,33 @@
       <c r="H355" s="358"/>
       <c r="I355" s="358"/>
       <c r="J355" s="55">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K355" s="358"/>
       <c r="L355" s="55">
-        <f t="shared" si="253"/>
+        <f t="shared" si="254"/>
         <v>0</v>
       </c>
       <c r="M355" s="56" t="e">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N355" s="123" t="e">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O355" s="57" t="e">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P355" s="124" t="e">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q355" s="376"/>
       <c r="R355" s="124" t="e">
-        <f t="shared" si="256"/>
+        <f t="shared" si="257"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S355" s="94"/>
@@ -26249,33 +26245,33 @@
       <c r="H356" s="358"/>
       <c r="I356" s="358"/>
       <c r="J356" s="55">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K356" s="358"/>
       <c r="L356" s="55">
-        <f t="shared" si="253"/>
+        <f t="shared" si="254"/>
         <v>0</v>
       </c>
       <c r="M356" s="56" t="e">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N356" s="123" t="e">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O356" s="57" t="e">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P356" s="124" t="e">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q356" s="376"/>
       <c r="R356" s="124" t="e">
-        <f t="shared" si="256"/>
+        <f t="shared" si="257"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S356" s="94"/>
@@ -26295,33 +26291,33 @@
       <c r="H357" s="358"/>
       <c r="I357" s="358"/>
       <c r="J357" s="55">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K357" s="358"/>
       <c r="L357" s="55">
-        <f t="shared" si="253"/>
+        <f t="shared" si="254"/>
         <v>0</v>
       </c>
       <c r="M357" s="56" t="e">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N357" s="123" t="e">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O357" s="57" t="e">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P357" s="124" t="e">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q357" s="376"/>
       <c r="R357" s="124" t="e">
-        <f t="shared" si="256"/>
+        <f t="shared" si="257"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S357" s="94"/>
@@ -26341,33 +26337,33 @@
       <c r="H358" s="358"/>
       <c r="I358" s="358"/>
       <c r="J358" s="55">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K358" s="358"/>
       <c r="L358" s="55">
-        <f t="shared" si="253"/>
+        <f t="shared" si="254"/>
         <v>0</v>
       </c>
       <c r="M358" s="56" t="e">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N358" s="123" t="e">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O358" s="57" t="e">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P358" s="124" t="e">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q358" s="376"/>
       <c r="R358" s="124" t="e">
-        <f t="shared" si="256"/>
+        <f t="shared" si="257"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S358" s="94"/>
@@ -26387,33 +26383,33 @@
       <c r="H359" s="358"/>
       <c r="I359" s="358"/>
       <c r="J359" s="55">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K359" s="358"/>
       <c r="L359" s="55">
-        <f t="shared" si="253"/>
+        <f t="shared" si="254"/>
         <v>0</v>
       </c>
       <c r="M359" s="56" t="e">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N359" s="123" t="e">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O359" s="57" t="e">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P359" s="124" t="e">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q359" s="376"/>
       <c r="R359" s="124" t="e">
-        <f t="shared" si="256"/>
+        <f t="shared" si="257"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S359" s="94"/>
@@ -26433,33 +26429,33 @@
       <c r="H360" s="358"/>
       <c r="I360" s="358"/>
       <c r="J360" s="55">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K360" s="358"/>
       <c r="L360" s="55">
-        <f t="shared" si="253"/>
+        <f t="shared" si="254"/>
         <v>0</v>
       </c>
       <c r="M360" s="56" t="e">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N360" s="123" t="e">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O360" s="57" t="e">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P360" s="124" t="e">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q360" s="376"/>
       <c r="R360" s="124" t="e">
-        <f t="shared" si="256"/>
+        <f t="shared" si="257"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S360" s="94"/>
@@ -26479,33 +26475,33 @@
       <c r="H361" s="358"/>
       <c r="I361" s="358"/>
       <c r="J361" s="55">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K361" s="358"/>
       <c r="L361" s="55">
-        <f t="shared" si="253"/>
+        <f t="shared" si="254"/>
         <v>0</v>
       </c>
       <c r="M361" s="56" t="e">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N361" s="123" t="e">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O361" s="57" t="e">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P361" s="124" t="e">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q361" s="376"/>
       <c r="R361" s="124" t="e">
-        <f t="shared" si="256"/>
+        <f t="shared" si="257"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S361" s="94"/>
@@ -26525,33 +26521,33 @@
       <c r="H362" s="358"/>
       <c r="I362" s="358"/>
       <c r="J362" s="55">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K362" s="358"/>
       <c r="L362" s="55">
-        <f t="shared" si="253"/>
+        <f t="shared" si="254"/>
         <v>0</v>
       </c>
       <c r="M362" s="56" t="e">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N362" s="123" t="e">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O362" s="57" t="e">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P362" s="124" t="e">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q362" s="376"/>
       <c r="R362" s="124" t="e">
-        <f t="shared" si="256"/>
+        <f t="shared" si="257"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S362" s="94"/>
@@ -26571,33 +26567,33 @@
       <c r="H363" s="358"/>
       <c r="I363" s="358"/>
       <c r="J363" s="55">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K363" s="358"/>
       <c r="L363" s="55">
-        <f t="shared" si="253"/>
+        <f t="shared" si="254"/>
         <v>0</v>
       </c>
       <c r="M363" s="56" t="e">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N363" s="123" t="e">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O363" s="57" t="e">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P363" s="124" t="e">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q363" s="376"/>
       <c r="R363" s="124" t="e">
-        <f t="shared" si="256"/>
+        <f t="shared" si="257"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S363" s="94"/>
@@ -26617,33 +26613,33 @@
       <c r="H364" s="358"/>
       <c r="I364" s="358"/>
       <c r="J364" s="55">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K364" s="358"/>
       <c r="L364" s="55">
-        <f t="shared" si="253"/>
+        <f t="shared" si="254"/>
         <v>0</v>
       </c>
       <c r="M364" s="56" t="e">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N364" s="123" t="e">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O364" s="57" t="e">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P364" s="124" t="e">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q364" s="376"/>
       <c r="R364" s="124" t="e">
-        <f t="shared" si="256"/>
+        <f t="shared" si="257"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S364" s="94"/>
@@ -26663,33 +26659,33 @@
       <c r="H365" s="358"/>
       <c r="I365" s="358"/>
       <c r="J365" s="55">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K365" s="358"/>
       <c r="L365" s="55">
-        <f t="shared" si="253"/>
+        <f t="shared" si="254"/>
         <v>0</v>
       </c>
       <c r="M365" s="56" t="e">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N365" s="123" t="e">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O365" s="57" t="e">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P365" s="124" t="e">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q365" s="376"/>
       <c r="R365" s="124" t="e">
-        <f t="shared" si="256"/>
+        <f t="shared" si="257"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S365" s="94"/>
@@ -26709,33 +26705,33 @@
       <c r="H366" s="358"/>
       <c r="I366" s="358"/>
       <c r="J366" s="55">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K366" s="358"/>
       <c r="L366" s="55">
-        <f t="shared" si="253"/>
+        <f t="shared" si="254"/>
         <v>0</v>
       </c>
       <c r="M366" s="56" t="e">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N366" s="123" t="e">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O366" s="57" t="e">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P366" s="124" t="e">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q366" s="376"/>
       <c r="R366" s="124" t="e">
-        <f t="shared" si="256"/>
+        <f t="shared" si="257"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S366" s="94"/>
@@ -26755,33 +26751,33 @@
       <c r="H367" s="358"/>
       <c r="I367" s="358"/>
       <c r="J367" s="55">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K367" s="358"/>
       <c r="L367" s="55">
-        <f t="shared" si="253"/>
+        <f t="shared" si="254"/>
         <v>0</v>
       </c>
       <c r="M367" s="56" t="e">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N367" s="123" t="e">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O367" s="57" t="e">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P367" s="124" t="e">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q367" s="376"/>
       <c r="R367" s="124" t="e">
-        <f t="shared" si="256"/>
+        <f t="shared" si="257"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S367" s="94"/>
@@ -26815,11 +26811,11 @@
         <v>0</v>
       </c>
       <c r="L368" s="332">
-        <f t="shared" si="246"/>
+        <f t="shared" si="247"/>
         <v>0</v>
       </c>
       <c r="M368" s="333" t="e">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N368" s="47"/>
@@ -26852,11 +26848,11 @@
       </c>
       <c r="K369" s="368"/>
       <c r="L369" s="65">
-        <f t="shared" si="246"/>
+        <f t="shared" si="247"/>
         <v>0</v>
       </c>
       <c r="M369" s="47" t="e">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N369" s="47"/>
@@ -26881,16 +26877,16 @@
       <c r="H370" s="368"/>
       <c r="I370" s="368"/>
       <c r="J370" s="65">
-        <f t="shared" ref="J370" si="257">G370+H370-I370</f>
+        <f t="shared" ref="J370" si="258">G370+H370-I370</f>
         <v>0</v>
       </c>
       <c r="K370" s="368"/>
       <c r="L370" s="65">
-        <f t="shared" ref="L370" si="258">J370-K370</f>
+        <f t="shared" ref="L370" si="259">J370-K370</f>
         <v>0</v>
       </c>
       <c r="M370" s="47" t="e">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N370" s="47" t="e">
@@ -26902,12 +26898,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="P370" s="47" t="e">
-        <f t="shared" ref="P370" si="259">IF(ABS(O370)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P370" si="260">IF(ABS(O370)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q370" s="378"/>
       <c r="R370" s="47" t="e">
-        <f t="shared" ref="R370" si="260">IF(P370="O","O",IF(Q370="O","O","X"))</f>
+        <f t="shared" ref="R370" si="261">IF(P370="O","O",IF(Q370="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S370" s="325"/>
@@ -26935,11 +26931,11 @@
       </c>
       <c r="K371" s="372"/>
       <c r="L371" s="65">
-        <f t="shared" si="246"/>
+        <f t="shared" si="247"/>
         <v>0</v>
       </c>
       <c r="M371" s="47" t="e">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N371" s="47"/>
@@ -26972,11 +26968,11 @@
       </c>
       <c r="K372" s="368"/>
       <c r="L372" s="65">
-        <f t="shared" si="246"/>
+        <f t="shared" si="247"/>
         <v>0</v>
       </c>
       <c r="M372" s="47" t="e">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N372" s="123" t="e">
@@ -26988,12 +26984,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="P372" s="124" t="e">
-        <f t="shared" ref="P372" si="261">IF(ABS(O372)&gt;100%,"O","X")</f>
+        <f t="shared" ref="P372" si="262">IF(ABS(O372)&gt;100%,"O","X")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q372" s="376"/>
       <c r="R372" s="124" t="e">
-        <f t="shared" ref="R372" si="262">IF(P372="O","O",IF(Q372="O","O","X"))</f>
+        <f t="shared" ref="R372" si="263">IF(P372="O","O",IF(Q372="O","O","X"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S372" s="325"/>
@@ -27024,11 +27020,11 @@
         <v>0</v>
       </c>
       <c r="L373" s="332">
-        <f t="shared" si="246"/>
+        <f t="shared" si="247"/>
         <v>0</v>
       </c>
       <c r="M373" s="333" t="e">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N373" s="47"/>
@@ -27829,11 +27825,11 @@
         <v>0</v>
       </c>
       <c r="I402" s="55">
-        <f t="shared" ref="I402:I403" si="263">G402-H402</f>
+        <f t="shared" ref="I402:I403" si="264">G402-H402</f>
         <v>0</v>
       </c>
       <c r="J402" s="286" t="e">
-        <f t="shared" ref="J402:J403" si="264">I402/H402</f>
+        <f t="shared" ref="J402:J403" si="265">I402/H402</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K402" s="248"/>
@@ -27866,11 +27862,11 @@
         <v>0</v>
       </c>
       <c r="I403" s="55">
-        <f t="shared" si="263"/>
+        <f t="shared" si="264"/>
         <v>0</v>
       </c>
       <c r="J403" s="286" t="e">
-        <f t="shared" si="264"/>
+        <f t="shared" si="265"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K403" s="248"/>
@@ -29633,11 +29629,11 @@
         <v>0</v>
       </c>
       <c r="I463" s="55">
-        <f t="shared" ref="I463:I470" si="265">G463-H463</f>
+        <f t="shared" ref="I463:I470" si="266">G463-H463</f>
         <v>0</v>
       </c>
       <c r="J463" s="260" t="e">
-        <f t="shared" ref="J463:J472" si="266">I463/H463</f>
+        <f t="shared" ref="J463:J472" si="267">I463/H463</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K463" s="261"/>
@@ -29670,11 +29666,11 @@
         <v>0</v>
       </c>
       <c r="I464" s="55">
-        <f t="shared" si="265"/>
+        <f t="shared" si="266"/>
         <v>0</v>
       </c>
       <c r="J464" s="260" t="e">
-        <f t="shared" si="266"/>
+        <f t="shared" si="267"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K464" s="261"/>
@@ -29707,11 +29703,11 @@
         <v>0</v>
       </c>
       <c r="I465" s="55">
-        <f t="shared" si="265"/>
+        <f t="shared" si="266"/>
         <v>0</v>
       </c>
       <c r="J465" s="260" t="e">
-        <f t="shared" ref="J465:J470" si="267">I465/H465</f>
+        <f t="shared" ref="J465:J470" si="268">I465/H465</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K465" s="261"/>
@@ -29744,11 +29740,11 @@
         <v>0</v>
       </c>
       <c r="I466" s="55">
-        <f t="shared" si="265"/>
+        <f t="shared" si="266"/>
         <v>0</v>
       </c>
       <c r="J466" s="260" t="e">
-        <f t="shared" si="267"/>
+        <f t="shared" si="268"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K466" s="261"/>
@@ -29781,11 +29777,11 @@
         <v>0</v>
       </c>
       <c r="I467" s="55">
-        <f t="shared" si="265"/>
+        <f t="shared" si="266"/>
         <v>0</v>
       </c>
       <c r="J467" s="260" t="e">
-        <f t="shared" si="267"/>
+        <f t="shared" si="268"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K467" s="261"/>
@@ -29818,11 +29814,11 @@
         <v>0</v>
       </c>
       <c r="I468" s="55">
-        <f t="shared" si="265"/>
+        <f t="shared" si="266"/>
         <v>0</v>
       </c>
       <c r="J468" s="260" t="e">
-        <f t="shared" si="267"/>
+        <f t="shared" si="268"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K468" s="261"/>
@@ -29855,11 +29851,11 @@
         <v>0</v>
       </c>
       <c r="I469" s="55">
-        <f t="shared" si="265"/>
+        <f t="shared" si="266"/>
         <v>0</v>
       </c>
       <c r="J469" s="260" t="e">
-        <f t="shared" si="267"/>
+        <f t="shared" si="268"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K469" s="261"/>
@@ -29892,11 +29888,11 @@
         <v>0</v>
       </c>
       <c r="I470" s="55">
-        <f t="shared" si="265"/>
+        <f t="shared" si="266"/>
         <v>0</v>
       </c>
       <c r="J470" s="260" t="e">
-        <f t="shared" si="267"/>
+        <f t="shared" si="268"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K470" s="261"/>
@@ -29933,7 +29929,7 @@
         <v>0</v>
       </c>
       <c r="J471" s="260" t="e">
-        <f t="shared" si="266"/>
+        <f t="shared" si="267"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K471" s="261"/>
@@ -29970,7 +29966,7 @@
         <v>0</v>
       </c>
       <c r="J472" s="260" t="e">
-        <f t="shared" si="266"/>
+        <f t="shared" si="267"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K472" s="261"/>
@@ -30238,7 +30234,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I482" s="259" t="e">
-        <f t="shared" ref="I482:I487" si="268">G482-H482</f>
+        <f t="shared" ref="I482:I487" si="269">G482-H482</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J482" s="260" t="e">
@@ -30272,7 +30268,7 @@
       </c>
       <c r="H483" s="382"/>
       <c r="I483" s="259">
-        <f t="shared" si="268"/>
+        <f t="shared" si="269"/>
         <v>0</v>
       </c>
       <c r="J483" s="260" t="e">
@@ -30309,7 +30305,7 @@
         <v>0</v>
       </c>
       <c r="I484" s="259">
-        <f t="shared" si="268"/>
+        <f t="shared" si="269"/>
         <v>0</v>
       </c>
       <c r="J484" s="260" t="e">
@@ -30346,7 +30342,7 @@
         <v>0</v>
       </c>
       <c r="I485" s="259">
-        <f t="shared" si="268"/>
+        <f t="shared" si="269"/>
         <v>0</v>
       </c>
       <c r="J485" s="260" t="e">
@@ -30383,7 +30379,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I486" s="262" t="e">
-        <f t="shared" si="268"/>
+        <f t="shared" si="269"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J486" s="260"/>
@@ -30417,7 +30413,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I487" s="262" t="e">
-        <f t="shared" si="268"/>
+        <f t="shared" si="269"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J487" s="260"/>
@@ -30582,7 +30578,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I493" s="259" t="e">
-        <f t="shared" ref="I493:I498" si="269">G493-H493</f>
+        <f t="shared" ref="I493:I498" si="270">G493-H493</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J493" s="260" t="e">
@@ -30616,7 +30612,7 @@
       </c>
       <c r="H494" s="371"/>
       <c r="I494" s="259">
-        <f t="shared" si="269"/>
+        <f t="shared" si="270"/>
         <v>0</v>
       </c>
       <c r="J494" s="260" t="e">
@@ -30653,7 +30649,7 @@
         <v>0</v>
       </c>
       <c r="I495" s="259">
-        <f t="shared" si="269"/>
+        <f t="shared" si="270"/>
         <v>0</v>
       </c>
       <c r="J495" s="260" t="e">
@@ -30690,7 +30686,7 @@
         <v>0</v>
       </c>
       <c r="I496" s="259">
-        <f t="shared" si="269"/>
+        <f t="shared" si="270"/>
         <v>0</v>
       </c>
       <c r="J496" s="260" t="e">
@@ -30727,7 +30723,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I497" s="262" t="e">
-        <f t="shared" si="269"/>
+        <f t="shared" si="270"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J497" s="259"/>
@@ -30761,7 +30757,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I498" s="262" t="e">
-        <f t="shared" si="269"/>
+        <f t="shared" si="270"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J498" s="259"/>
@@ -30926,7 +30922,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I504" s="259" t="e">
-        <f t="shared" ref="I504:I509" si="270">G504-H504</f>
+        <f t="shared" ref="I504:I509" si="271">G504-H504</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J504" s="260" t="e">
@@ -30960,7 +30956,7 @@
       </c>
       <c r="H505" s="371"/>
       <c r="I505" s="259">
-        <f t="shared" si="270"/>
+        <f t="shared" si="271"/>
         <v>0</v>
       </c>
       <c r="J505" s="260" t="e">
@@ -30997,7 +30993,7 @@
         <v>0</v>
       </c>
       <c r="I506" s="259">
-        <f t="shared" si="270"/>
+        <f t="shared" si="271"/>
         <v>0</v>
       </c>
       <c r="J506" s="260" t="e">
@@ -31034,7 +31030,7 @@
         <v>0</v>
       </c>
       <c r="I507" s="259">
-        <f t="shared" si="270"/>
+        <f t="shared" si="271"/>
         <v>0</v>
       </c>
       <c r="J507" s="260" t="e">
@@ -31071,7 +31067,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I508" s="262" t="e">
-        <f t="shared" si="270"/>
+        <f t="shared" si="271"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J508" s="259"/>
@@ -31105,7 +31101,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I509" s="262" t="e">
-        <f t="shared" si="270"/>
+        <f t="shared" si="271"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J509" s="259"/>
@@ -31293,7 +31289,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I516" s="259" t="e">
-        <f t="shared" ref="I516:I521" si="271">G516-H516</f>
+        <f t="shared" ref="I516:I521" si="272">G516-H516</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J516" s="260" t="e">
@@ -31327,7 +31323,7 @@
       </c>
       <c r="H517" s="382"/>
       <c r="I517" s="259">
-        <f t="shared" si="271"/>
+        <f t="shared" si="272"/>
         <v>0</v>
       </c>
       <c r="J517" s="260" t="e">
@@ -31364,7 +31360,7 @@
         <v>0</v>
       </c>
       <c r="I518" s="259">
-        <f t="shared" si="271"/>
+        <f t="shared" si="272"/>
         <v>0</v>
       </c>
       <c r="J518" s="260" t="e">
@@ -31401,7 +31397,7 @@
         <v>0</v>
       </c>
       <c r="I519" s="259">
-        <f t="shared" si="271"/>
+        <f t="shared" si="272"/>
         <v>0</v>
       </c>
       <c r="J519" s="260" t="e">
@@ -31438,7 +31434,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I520" s="262" t="e">
-        <f t="shared" si="271"/>
+        <f t="shared" si="272"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J520" s="259"/>
@@ -31472,7 +31468,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I521" s="262" t="e">
-        <f t="shared" si="271"/>
+        <f t="shared" si="272"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J521" s="259"/>
